--- a/polytech/StTableur_Polytech_Lyon_Info.xlsx
+++ b/polytech/StTableur_Polytech_Lyon_Info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\__julien__\Ecole\Polytech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1656A514-EDA7-4E77-9050-5433E446A9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E627538-29D4-449B-8109-EECC90A7DE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2166B340-63E7-40DE-94EE-C7BDCE76DCA3}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="187">
   <si>
     <t>Il y a un onglet par semestre pour les FISE et pour les FISA.</t>
   </si>
@@ -626,22 +626,28 @@
     <t>TP3</t>
   </si>
   <si>
+    <t>Développement de la Performance</t>
+  </si>
+  <si>
+    <t>Veuillez rentrer des valeurs seulement dans les cases grises.</t>
+  </si>
+  <si>
     <t>Rapport</t>
   </si>
   <si>
-    <t>Développement de la Performance</t>
-  </si>
-  <si>
     <t>Présentation</t>
   </si>
   <si>
-    <t>Oral</t>
-  </si>
-  <si>
-    <t>Écrit</t>
-  </si>
-  <si>
-    <t>Veuillez rentrer des valeurs seulement dans les cases grises.</t>
+    <t>TP Green IT</t>
+  </si>
+  <si>
+    <t>TP Industrie 4.0</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>Compétences</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1479,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1778,34 +1784,295 @@
     <xf numFmtId="0" fontId="14" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1814,244 +2081,25 @@
     <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2072,30 +2120,21 @@
     <xf numFmtId="0" fontId="14" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2108,13 +2147,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2124,18 +2166,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2801,110 +2831,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="172" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
     </row>
     <row r="2" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="173" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
+      <c r="B2" s="173"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
+      <c r="G2" s="173"/>
     </row>
     <row r="3" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="102" t="s">
+      <c r="A3" s="167" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="167"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="167"/>
+      <c r="F3" s="167"/>
+      <c r="G3" s="167"/>
     </row>
     <row r="4" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="105"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
+      <c r="A4" s="168"/>
+      <c r="B4" s="168"/>
+      <c r="C4" s="168"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="168"/>
+      <c r="F4" s="168"/>
+      <c r="G4" s="168"/>
     </row>
     <row r="5" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
+      <c r="A5" s="167" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="167"/>
+      <c r="C5" s="167"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="167"/>
+      <c r="F5" s="167"/>
+      <c r="G5" s="167"/>
     </row>
     <row r="6" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="102" t="s">
-        <v>184</v>
-      </c>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
+      <c r="A6" s="167" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" s="167"/>
+      <c r="C6" s="167"/>
+      <c r="D6" s="167"/>
+      <c r="E6" s="167"/>
+      <c r="F6" s="167"/>
+      <c r="G6" s="167"/>
     </row>
     <row r="7" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="102" t="s">
+      <c r="A7" s="167" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="102"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
+      <c r="B7" s="167"/>
+      <c r="C7" s="167"/>
+      <c r="D7" s="167"/>
+      <c r="E7" s="167"/>
+      <c r="F7" s="167"/>
+      <c r="G7" s="167"/>
     </row>
     <row r="8" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="102" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="102"/>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
-      <c r="E8" s="102"/>
-      <c r="F8" s="102"/>
-      <c r="G8" s="102"/>
+      <c r="A8" s="167" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="167"/>
+      <c r="C8" s="167"/>
+      <c r="D8" s="167"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="167"/>
     </row>
     <row r="9" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="105"/>
-      <c r="B9" s="105"/>
-      <c r="C9" s="105"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
+      <c r="A9" s="168"/>
+      <c r="B9" s="168"/>
+      <c r="C9" s="168"/>
+      <c r="D9" s="168"/>
+      <c r="E9" s="168"/>
+      <c r="F9" s="168"/>
+      <c r="G9" s="168"/>
     </row>
     <row r="10" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="107" t="s">
+      <c r="A10" s="170" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="107"/>
-      <c r="C10" s="107"/>
-      <c r="D10" s="107"/>
-      <c r="E10" s="107"/>
-      <c r="F10" s="107"/>
-      <c r="G10" s="107"/>
+      <c r="B10" s="170"/>
+      <c r="C10" s="170"/>
+      <c r="D10" s="170"/>
+      <c r="E10" s="170"/>
+      <c r="F10" s="170"/>
+      <c r="G10" s="170"/>
     </row>
     <row r="11" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="42" t="s">
@@ -2946,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="77">
-        <f>IF(COUNTA(E13)=0,S8_FISE!E35,E13)</f>
+        <f>IF(COUNTA(E13)=0,S8_FISE!E42,E13)</f>
         <v>0</v>
       </c>
       <c r="F12" s="77">
@@ -2970,24 +3000,24 @@
       <c r="G13" s="92"/>
     </row>
     <row r="14" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="105"/>
-      <c r="B14" s="105"/>
-      <c r="C14" s="105"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="105"/>
+      <c r="A14" s="168"/>
+      <c r="B14" s="168"/>
+      <c r="C14" s="168"/>
+      <c r="D14" s="168"/>
+      <c r="E14" s="168"/>
+      <c r="F14" s="168"/>
+      <c r="G14" s="168"/>
     </row>
     <row r="15" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="108" t="s">
+      <c r="A15" s="171" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="108"/>
-      <c r="C15" s="108"/>
-      <c r="D15" s="108"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="108"/>
+      <c r="B15" s="171"/>
+      <c r="C15" s="171"/>
+      <c r="D15" s="171"/>
+      <c r="E15" s="171"/>
+      <c r="F15" s="171"/>
+      <c r="G15" s="171"/>
     </row>
     <row r="16" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42" t="s">
@@ -3041,24 +3071,24 @@
       <c r="G18" s="92"/>
     </row>
     <row r="19" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="105"/>
-      <c r="B19" s="105"/>
-      <c r="C19" s="105"/>
-      <c r="D19" s="105"/>
-      <c r="E19" s="105"/>
-      <c r="F19" s="105"/>
-      <c r="G19" s="105"/>
+      <c r="A19" s="168"/>
+      <c r="B19" s="168"/>
+      <c r="C19" s="168"/>
+      <c r="D19" s="168"/>
+      <c r="E19" s="168"/>
+      <c r="F19" s="168"/>
+      <c r="G19" s="168"/>
     </row>
     <row r="20" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="106" t="s">
+      <c r="A20" s="169" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="106"/>
-      <c r="C20" s="106"/>
-      <c r="D20" s="106"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="106"/>
-      <c r="G20" s="106"/>
+      <c r="B20" s="169"/>
+      <c r="C20" s="169"/>
+      <c r="D20" s="169"/>
+      <c r="E20" s="169"/>
+      <c r="F20" s="169"/>
+      <c r="G20" s="169"/>
     </row>
     <row r="21" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42" t="s">
@@ -3127,6 +3157,11 @@
     <row r="1048575" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A20:G20"/>
@@ -3136,11 +3171,6 @@
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <conditionalFormatting sqref="B22:G22">
     <cfRule type="cellIs" dxfId="39" priority="28" operator="equal">
@@ -3226,7 +3256,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="4" id="{0544457F-4531-4F9B-8236-88453F06CDCC}">
-            <xm:f>IF(COUNTA(E13)=0,S8_FISE!$H$35="Valide",E13&gt;=10)</xm:f>
+            <xm:f>IF(COUNTA(E13)=0,S8_FISE!$H$42="Valide",E13&gt;=10)</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3291,31 +3321,31 @@
       <c r="B1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="145" t="s">
+      <c r="C1" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="146"/>
-      <c r="E1" s="149" t="s">
+      <c r="D1" s="122"/>
+      <c r="E1" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="150"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="147" t="s">
+      <c r="F1" s="124"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="190" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="148"/>
+      <c r="I1" s="191"/>
     </row>
     <row r="2" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="109" t="s">
+      <c r="A2" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="199" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="114">
+      <c r="C2" s="131">
         <v>8</v>
       </c>
-      <c r="D2" s="124">
+      <c r="D2" s="151">
         <v>4</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -3326,21 +3356,21 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G2" s="93"/>
-      <c r="H2" s="135">
+      <c r="H2" s="118">
         <f>G2*F2+G3*F3+G4*F4+G5*F5+G6*F6+G7*F7</f>
         <v>0</v>
       </c>
-      <c r="I2" s="133">
+      <c r="I2" s="134">
         <f>(H2*D2+H8*D8+H10*D10)/C2</f>
         <v>0</v>
       </c>
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="110"/>
-      <c r="B3" s="113"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="125"/>
+      <c r="A3" s="127"/>
+      <c r="B3" s="200"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="107"/>
       <c r="E3" s="11" t="s">
         <v>124</v>
       </c>
@@ -3349,15 +3379,15 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G3" s="93"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="144"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="135"/>
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="110"/>
-      <c r="B4" s="113"/>
-      <c r="C4" s="115"/>
-      <c r="D4" s="125"/>
+      <c r="A4" s="127"/>
+      <c r="B4" s="200"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="107"/>
       <c r="E4" s="11" t="s">
         <v>104</v>
       </c>
@@ -3366,15 +3396,15 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G4" s="93"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="144"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="135"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="110"/>
-      <c r="B5" s="113"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="125"/>
+      <c r="A5" s="127"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="107"/>
       <c r="E5" s="11" t="s">
         <v>31</v>
       </c>
@@ -3383,15 +3413,15 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G5" s="93"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="144"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="135"/>
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="110"/>
-      <c r="B6" s="113"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="125"/>
+      <c r="A6" s="127"/>
+      <c r="B6" s="200"/>
+      <c r="C6" s="132"/>
+      <c r="D6" s="107"/>
       <c r="E6" s="11" t="s">
         <v>106</v>
       </c>
@@ -3400,15 +3430,15 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G6" s="93"/>
-      <c r="H6" s="127"/>
-      <c r="I6" s="144"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="135"/>
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="110"/>
-      <c r="B7" s="113"/>
-      <c r="C7" s="115"/>
-      <c r="D7" s="125"/>
+      <c r="A7" s="127"/>
+      <c r="B7" s="200"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="107"/>
       <c r="E7" s="11" t="s">
         <v>122</v>
       </c>
@@ -3417,17 +3447,17 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G7" s="93"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="144"/>
+      <c r="H7" s="119"/>
+      <c r="I7" s="135"/>
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="110"/>
-      <c r="B8" s="117" t="s">
+      <c r="A8" s="127"/>
+      <c r="B8" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="115"/>
-      <c r="D8" s="125">
+      <c r="C8" s="132"/>
+      <c r="D8" s="107">
         <v>1</v>
       </c>
       <c r="E8" s="23" t="s">
@@ -3437,17 +3467,17 @@
         <v>0.1</v>
       </c>
       <c r="G8" s="94"/>
-      <c r="H8" s="127">
+      <c r="H8" s="119">
         <f>G8*F8+G9*F9</f>
         <v>0</v>
       </c>
-      <c r="I8" s="144"/>
+      <c r="I8" s="135"/>
     </row>
     <row r="9" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="110"/>
-      <c r="B9" s="117"/>
-      <c r="C9" s="115"/>
-      <c r="D9" s="125"/>
+      <c r="A9" s="127"/>
+      <c r="B9" s="130"/>
+      <c r="C9" s="132"/>
+      <c r="D9" s="107"/>
       <c r="E9" s="12" t="s">
         <v>102</v>
       </c>
@@ -3455,16 +3485,16 @@
         <v>0.9</v>
       </c>
       <c r="G9" s="95"/>
-      <c r="H9" s="127"/>
-      <c r="I9" s="144"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="135"/>
     </row>
     <row r="10" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="110"/>
-      <c r="B10" s="117" t="s">
+      <c r="A10" s="127"/>
+      <c r="B10" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="125">
+      <c r="C10" s="132"/>
+      <c r="D10" s="107">
         <v>3</v>
       </c>
       <c r="E10" s="16" t="s">
@@ -3474,17 +3504,17 @@
         <v>0.5</v>
       </c>
       <c r="G10" s="93"/>
-      <c r="H10" s="127">
+      <c r="H10" s="119">
         <f>G10*F10+G11*F11</f>
         <v>0</v>
       </c>
-      <c r="I10" s="144"/>
+      <c r="I10" s="135"/>
     </row>
     <row r="11" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="111"/>
-      <c r="B11" s="123"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="126"/>
+      <c r="A11" s="128"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="133"/>
+      <c r="D11" s="108"/>
       <c r="E11" s="17" t="s">
         <v>102</v>
       </c>
@@ -3492,20 +3522,20 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="96"/>
-      <c r="H11" s="130"/>
-      <c r="I11" s="134"/>
+      <c r="H11" s="164"/>
+      <c r="I11" s="136"/>
     </row>
     <row r="12" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="118" t="s">
+      <c r="A12" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="120" t="s">
+      <c r="B12" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="121">
+      <c r="C12" s="117">
         <v>5</v>
       </c>
-      <c r="D12" s="131">
+      <c r="D12" s="116">
         <v>4</v>
       </c>
       <c r="E12" s="16" t="s">
@@ -3515,20 +3545,20 @@
         <v>0.25</v>
       </c>
       <c r="G12" s="93"/>
-      <c r="H12" s="127">
+      <c r="H12" s="119">
         <f>G12*F12+G13*F13+G14*F14+G15*F15</f>
         <v>0</v>
       </c>
-      <c r="I12" s="133">
+      <c r="I12" s="134">
         <f>(H12*D12+H16*D16)/C12</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="118"/>
-      <c r="B13" s="120"/>
-      <c r="C13" s="121"/>
-      <c r="D13" s="131"/>
+      <c r="A13" s="120"/>
+      <c r="B13" s="114"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="116"/>
       <c r="E13" s="16" t="s">
         <v>89</v>
       </c>
@@ -3536,14 +3566,14 @@
         <v>0.25</v>
       </c>
       <c r="G13" s="93"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="144"/>
+      <c r="H13" s="119"/>
+      <c r="I13" s="135"/>
     </row>
     <row r="14" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="118"/>
-      <c r="B14" s="120"/>
-      <c r="C14" s="121"/>
-      <c r="D14" s="131"/>
+      <c r="A14" s="120"/>
+      <c r="B14" s="114"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="116"/>
       <c r="E14" s="16" t="s">
         <v>101</v>
       </c>
@@ -3551,14 +3581,14 @@
         <v>0.25</v>
       </c>
       <c r="G14" s="93"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="144"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="135"/>
     </row>
     <row r="15" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="118"/>
-      <c r="B15" s="120"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="131"/>
+      <c r="A15" s="120"/>
+      <c r="B15" s="114"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="116"/>
       <c r="E15" s="16" t="s">
         <v>102</v>
       </c>
@@ -3566,16 +3596,16 @@
         <v>0.25</v>
       </c>
       <c r="G15" s="93"/>
-      <c r="H15" s="127"/>
-      <c r="I15" s="144"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="135"/>
     </row>
     <row r="16" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="118"/>
-      <c r="B16" s="120" t="s">
+      <c r="A16" s="120"/>
+      <c r="B16" s="114" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="121"/>
-      <c r="D16" s="131">
+      <c r="C16" s="117"/>
+      <c r="D16" s="116">
         <v>1</v>
       </c>
       <c r="E16" s="15" t="s">
@@ -3585,17 +3615,17 @@
         <v>0.4</v>
       </c>
       <c r="G16" s="94"/>
-      <c r="H16" s="127">
+      <c r="H16" s="119">
         <f>G16*F16+G17*F17</f>
         <v>0</v>
       </c>
-      <c r="I16" s="144"/>
+      <c r="I16" s="135"/>
     </row>
     <row r="17" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="119"/>
-      <c r="B17" s="155"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="132"/>
+      <c r="A17" s="201"/>
+      <c r="B17" s="162"/>
+      <c r="C17" s="157"/>
+      <c r="D17" s="163"/>
       <c r="E17" s="17" t="s">
         <v>102</v>
       </c>
@@ -3603,20 +3633,20 @@
         <v>0.6</v>
       </c>
       <c r="G17" s="95"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="134"/>
+      <c r="H17" s="164"/>
+      <c r="I17" s="136"/>
     </row>
     <row r="18" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="159" t="s">
+      <c r="A18" s="138" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="152" t="s">
+      <c r="B18" s="165" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="141">
+      <c r="C18" s="156">
         <v>5</v>
       </c>
-      <c r="D18" s="143">
+      <c r="D18" s="115">
         <v>1</v>
       </c>
       <c r="E18" s="15" t="s">
@@ -3626,20 +3656,20 @@
         <v>0.6</v>
       </c>
       <c r="G18" s="97"/>
-      <c r="H18" s="135">
+      <c r="H18" s="118">
         <f>G18*F18+G19*F19</f>
         <v>0</v>
       </c>
-      <c r="I18" s="133">
+      <c r="I18" s="134">
         <f>(H18*D18+H20*D20+H22*D22)/C18</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="160"/>
-      <c r="B19" s="153"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="131"/>
+      <c r="A19" s="139"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="116"/>
       <c r="E19" s="16" t="s">
         <v>95</v>
       </c>
@@ -3647,16 +3677,16 @@
         <v>0.4</v>
       </c>
       <c r="G19" s="93"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="144"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="135"/>
     </row>
     <row r="20" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="160"/>
-      <c r="B20" s="153" t="s">
+      <c r="A20" s="139"/>
+      <c r="B20" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="121"/>
-      <c r="D20" s="131">
+      <c r="C20" s="117"/>
+      <c r="D20" s="116">
         <v>2</v>
       </c>
       <c r="E20" s="15" t="s">
@@ -3666,17 +3696,17 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="94"/>
-      <c r="H20" s="127">
+      <c r="H20" s="119">
         <f>G20*F20+G21*F21</f>
         <v>0</v>
       </c>
-      <c r="I20" s="144"/>
+      <c r="I20" s="135"/>
     </row>
     <row r="21" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="160"/>
-      <c r="B21" s="153"/>
-      <c r="C21" s="121"/>
-      <c r="D21" s="131"/>
+      <c r="A21" s="139"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="116"/>
       <c r="E21" s="17" t="s">
         <v>102</v>
       </c>
@@ -3684,16 +3714,16 @@
         <v>0.5</v>
       </c>
       <c r="G21" s="95"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="144"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="135"/>
     </row>
     <row r="22" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="160"/>
-      <c r="B22" s="153" t="s">
+      <c r="A22" s="139"/>
+      <c r="B22" s="111" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="121"/>
-      <c r="D22" s="131">
+      <c r="C22" s="117"/>
+      <c r="D22" s="116">
         <v>2</v>
       </c>
       <c r="E22" s="16" t="s">
@@ -3703,17 +3733,17 @@
         <v>0.4</v>
       </c>
       <c r="G22" s="93"/>
-      <c r="H22" s="127">
+      <c r="H22" s="119">
         <f>G22*F22+G23*F23+G24*F24</f>
         <v>0</v>
       </c>
-      <c r="I22" s="144"/>
+      <c r="I22" s="135"/>
     </row>
     <row r="23" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="160"/>
-      <c r="B23" s="153"/>
-      <c r="C23" s="121"/>
-      <c r="D23" s="131"/>
+      <c r="A23" s="139"/>
+      <c r="B23" s="111"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="116"/>
       <c r="E23" s="16" t="s">
         <v>98</v>
       </c>
@@ -3721,14 +3751,14 @@
         <v>0.3</v>
       </c>
       <c r="G23" s="93"/>
-      <c r="H23" s="127"/>
-      <c r="I23" s="144"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="135"/>
     </row>
     <row r="24" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="161"/>
-      <c r="B24" s="154"/>
-      <c r="C24" s="122"/>
-      <c r="D24" s="132"/>
+      <c r="A24" s="174"/>
+      <c r="B24" s="112"/>
+      <c r="C24" s="157"/>
+      <c r="D24" s="163"/>
       <c r="E24" s="17" t="s">
         <v>99</v>
       </c>
@@ -3736,20 +3766,20 @@
         <v>0.3</v>
       </c>
       <c r="G24" s="96"/>
-      <c r="H24" s="130"/>
-      <c r="I24" s="134"/>
+      <c r="H24" s="164"/>
+      <c r="I24" s="136"/>
     </row>
     <row r="25" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="174" t="s">
+      <c r="A25" s="183" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="177" t="s">
+      <c r="B25" s="186" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="142">
+      <c r="C25" s="105">
         <v>4</v>
       </c>
-      <c r="D25" s="125">
+      <c r="D25" s="107">
         <v>2</v>
       </c>
       <c r="E25" s="16" t="s">
@@ -3759,20 +3789,20 @@
         <v>0.4</v>
       </c>
       <c r="G25" s="93"/>
-      <c r="H25" s="127">
+      <c r="H25" s="119">
         <f>F25*G25+F26*G26</f>
         <v>0</v>
       </c>
-      <c r="I25" s="133">
+      <c r="I25" s="134">
         <f>(H25*D25+H27*D27)/C25</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="175"/>
-      <c r="B26" s="178"/>
-      <c r="C26" s="179"/>
-      <c r="D26" s="180"/>
+      <c r="A26" s="184"/>
+      <c r="B26" s="187"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="188"/>
       <c r="E26" s="16" t="s">
         <v>102</v>
       </c>
@@ -3780,16 +3810,16 @@
         <v>0.6</v>
       </c>
       <c r="G26" s="93"/>
-      <c r="H26" s="127"/>
-      <c r="I26" s="144"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="135"/>
     </row>
     <row r="27" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="175"/>
-      <c r="B27" s="156" t="s">
+      <c r="A27" s="184"/>
+      <c r="B27" s="189" t="s">
         <v>127</v>
       </c>
-      <c r="C27" s="179"/>
-      <c r="D27" s="131">
+      <c r="C27" s="106"/>
+      <c r="D27" s="116">
         <v>2</v>
       </c>
       <c r="E27" s="15" t="s">
@@ -3799,17 +3829,17 @@
         <v>0.4</v>
       </c>
       <c r="G27" s="94"/>
-      <c r="H27" s="127">
+      <c r="H27" s="119">
         <f>F27*G27+F28*G28</f>
         <v>0</v>
       </c>
-      <c r="I27" s="144"/>
+      <c r="I27" s="135"/>
     </row>
     <row r="28" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="176"/>
-      <c r="B28" s="156"/>
-      <c r="C28" s="166"/>
-      <c r="D28" s="131"/>
+      <c r="A28" s="185"/>
+      <c r="B28" s="189"/>
+      <c r="C28" s="179"/>
+      <c r="D28" s="116"/>
       <c r="E28" s="17" t="s">
         <v>102</v>
       </c>
@@ -3817,17 +3847,17 @@
         <v>0.6</v>
       </c>
       <c r="G28" s="95"/>
-      <c r="H28" s="127"/>
-      <c r="I28" s="134"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="136"/>
     </row>
     <row r="29" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="170" t="s">
+      <c r="A29" s="145" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="172">
+      <c r="C29" s="104">
         <v>3</v>
       </c>
       <c r="D29" s="14">
@@ -3844,17 +3874,17 @@
         <f>G29*F29</f>
         <v>0</v>
       </c>
-      <c r="I29" s="133">
+      <c r="I29" s="134">
         <f>(H29*D29+H30*D30)/C29</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="171"/>
+      <c r="A30" s="146"/>
       <c r="B30" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="173"/>
+      <c r="C30" s="147"/>
       <c r="D30" s="22">
         <v>1</v>
       </c>
@@ -3869,19 +3899,19 @@
         <f>G30*F30</f>
         <v>0</v>
       </c>
-      <c r="I30" s="134"/>
+      <c r="I30" s="136"/>
     </row>
     <row r="31" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="136" t="s">
+      <c r="A31" s="192" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="139" t="s">
+      <c r="B31" s="195" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="141">
+      <c r="C31" s="156">
         <v>4</v>
       </c>
-      <c r="D31" s="143">
+      <c r="D31" s="115">
         <v>2</v>
       </c>
       <c r="E31" s="16" t="s">
@@ -3891,20 +3921,20 @@
         <v>0.75</v>
       </c>
       <c r="G31" s="93"/>
-      <c r="H31" s="135">
+      <c r="H31" s="118">
         <f>G31*F31+G32*F32</f>
         <v>0</v>
       </c>
-      <c r="I31" s="133">
+      <c r="I31" s="134">
         <f>(H31*D31+H33*D33+H35*D35)/C31</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="137"/>
-      <c r="B32" s="140"/>
-      <c r="C32" s="121"/>
-      <c r="D32" s="131"/>
+      <c r="A32" s="193"/>
+      <c r="B32" s="196"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="116"/>
       <c r="E32" s="16" t="s">
         <v>148</v>
       </c>
@@ -3912,16 +3942,16 @@
         <v>0.25</v>
       </c>
       <c r="G32" s="93"/>
-      <c r="H32" s="127"/>
-      <c r="I32" s="144"/>
+      <c r="H32" s="119"/>
+      <c r="I32" s="135"/>
     </row>
     <row r="33" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="137"/>
-      <c r="B33" s="140" t="s">
+      <c r="A33" s="193"/>
+      <c r="B33" s="196" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="121"/>
-      <c r="D33" s="131">
+      <c r="C33" s="117"/>
+      <c r="D33" s="116">
         <v>1.5</v>
       </c>
       <c r="E33" s="15" t="s">
@@ -3931,17 +3961,17 @@
         <v>0.5</v>
       </c>
       <c r="G33" s="94"/>
-      <c r="H33" s="127">
+      <c r="H33" s="119">
         <f>G33*F33+G34*F34</f>
         <v>0</v>
       </c>
-      <c r="I33" s="144"/>
+      <c r="I33" s="135"/>
     </row>
     <row r="34" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="137"/>
-      <c r="B34" s="140"/>
-      <c r="C34" s="121"/>
-      <c r="D34" s="131"/>
+      <c r="A34" s="193"/>
+      <c r="B34" s="196"/>
+      <c r="C34" s="117"/>
+      <c r="D34" s="116"/>
       <c r="E34" s="17" t="s">
         <v>94</v>
       </c>
@@ -3949,15 +3979,15 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="95"/>
-      <c r="H34" s="127"/>
-      <c r="I34" s="144"/>
+      <c r="H34" s="119"/>
+      <c r="I34" s="135"/>
     </row>
     <row r="35" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="138"/>
+      <c r="A35" s="194"/>
       <c r="B35" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="142"/>
+      <c r="C35" s="105"/>
       <c r="D35" s="9">
         <v>0.5</v>
       </c>
@@ -3972,19 +4002,19 @@
         <f>G35*F35</f>
         <v>0</v>
       </c>
-      <c r="I35" s="134"/>
+      <c r="I35" s="136"/>
     </row>
     <row r="36" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="162" t="s">
+      <c r="A36" s="175" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="164" t="s">
+      <c r="B36" s="177" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="166">
-        <v>1</v>
-      </c>
-      <c r="D36" s="128">
+      <c r="C36" s="179">
+        <v>1</v>
+      </c>
+      <c r="D36" s="197">
         <v>1</v>
       </c>
       <c r="E36" s="15" t="s">
@@ -3994,20 +4024,20 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="97"/>
-      <c r="H36" s="135">
+      <c r="H36" s="118">
         <f>G36*F36+G37*F37</f>
         <v>0</v>
       </c>
-      <c r="I36" s="133">
+      <c r="I36" s="134">
         <f>(H36*D36)/C36</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="163"/>
-      <c r="B37" s="165"/>
-      <c r="C37" s="142"/>
-      <c r="D37" s="129"/>
+      <c r="A37" s="176"/>
+      <c r="B37" s="178"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="198"/>
       <c r="E37" s="17" t="s">
         <v>92</v>
       </c>
@@ -4015,30 +4045,30 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="96"/>
-      <c r="H37" s="130"/>
-      <c r="I37" s="134"/>
+      <c r="H37" s="164"/>
+      <c r="I37" s="136"/>
     </row>
     <row r="38" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="167" t="s">
+      <c r="A38" s="180" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="168"/>
-      <c r="C38" s="169">
+      <c r="B38" s="181"/>
+      <c r="C38" s="182">
         <f>SUM(C2:C36)</f>
         <v>30</v>
       </c>
-      <c r="D38" s="167"/>
-      <c r="E38" s="149">
+      <c r="D38" s="180"/>
+      <c r="E38" s="123">
         <f>(I2*C2+I12*C12+I18*C18+I25*C25+I29*C29+I31*C31+I36*C36)/C38</f>
         <v>0</v>
       </c>
-      <c r="F38" s="150"/>
-      <c r="G38" s="150"/>
-      <c r="H38" s="157" t="str">
+      <c r="F38" s="124"/>
+      <c r="G38" s="124"/>
+      <c r="H38" s="143" t="str">
         <f>IF(OR(I2&lt;10,I12&lt;10,I18&lt;10,I25&lt;10,I29&lt;10,I31&lt;10,I36&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I38" s="158"/>
+      <c r="I38" s="144"/>
     </row>
     <row r="39" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H39" s="62"/>
@@ -4046,6 +4076,57 @@
     </row>
   </sheetData>
   <mergeCells count="67">
+    <mergeCell ref="A2:A11"/>
+    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="C2:C11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="C12:C17"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D2:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="I31:I35"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C24"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="I12:I17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="I2:I11"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="I18:I24"/>
+    <mergeCell ref="B20:B21"/>
     <mergeCell ref="E38:G38"/>
     <mergeCell ref="H38:I38"/>
     <mergeCell ref="A18:A24"/>
@@ -4062,57 +4143,6 @@
     <mergeCell ref="C25:C28"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="I25:I28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="I18:I24"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C24"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="I12:I17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="I2:I11"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="I31:I35"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="D2:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="D12:D15"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="A2:A11"/>
-    <mergeCell ref="B2:B7"/>
-    <mergeCell ref="C2:C11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="C12:C17"/>
-    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <conditionalFormatting sqref="H38">
     <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
@@ -4160,31 +4190,31 @@
       <c r="B1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="145" t="s">
+      <c r="C1" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="146"/>
-      <c r="E1" s="149" t="s">
+      <c r="D1" s="122"/>
+      <c r="E1" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="150"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="192" t="s">
+      <c r="F1" s="124"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="202" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="193"/>
+      <c r="I1" s="203"/>
     </row>
     <row r="2" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="109" t="s">
+      <c r="A2" s="126" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="199" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="114">
+      <c r="C2" s="131">
         <v>7</v>
       </c>
-      <c r="D2" s="124">
+      <c r="D2" s="151">
         <v>2</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -4194,21 +4224,21 @@
         <v>0.5</v>
       </c>
       <c r="G2" s="93"/>
-      <c r="H2" s="135">
+      <c r="H2" s="118">
         <f>G2*F2+G3*F3</f>
         <v>0</v>
       </c>
-      <c r="I2" s="133">
+      <c r="I2" s="134">
         <f>(H2*D2+H4*D4+H6*D6)/C2</f>
         <v>0</v>
       </c>
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="110"/>
-      <c r="B3" s="113"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="125"/>
+      <c r="A3" s="127"/>
+      <c r="B3" s="200"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="107"/>
       <c r="E3" s="11" t="s">
         <v>102</v>
       </c>
@@ -4216,17 +4246,17 @@
         <v>0.5</v>
       </c>
       <c r="G3" s="93"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="144"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="135"/>
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="110"/>
-      <c r="B4" s="117" t="s">
+      <c r="A4" s="127"/>
+      <c r="B4" s="130" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="115"/>
-      <c r="D4" s="125">
+      <c r="C4" s="132"/>
+      <c r="D4" s="107">
         <v>2</v>
       </c>
       <c r="E4" s="23" t="s">
@@ -4236,17 +4266,17 @@
         <v>0.5</v>
       </c>
       <c r="G4" s="94"/>
-      <c r="H4" s="127">
+      <c r="H4" s="119">
         <f>G4*F4+G5*F5</f>
         <v>0</v>
       </c>
-      <c r="I4" s="144"/>
+      <c r="I4" s="135"/>
     </row>
     <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="110"/>
-      <c r="B5" s="117"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="125"/>
+      <c r="A5" s="127"/>
+      <c r="B5" s="130"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="107"/>
       <c r="E5" s="12" t="s">
         <v>99</v>
       </c>
@@ -4254,16 +4284,16 @@
         <v>0.5</v>
       </c>
       <c r="G5" s="95"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="144"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="135"/>
     </row>
     <row r="6" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="110"/>
-      <c r="B6" s="117" t="s">
+      <c r="A6" s="127"/>
+      <c r="B6" s="130" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="115"/>
-      <c r="D6" s="125">
+      <c r="C6" s="132"/>
+      <c r="D6" s="107">
         <v>3</v>
       </c>
       <c r="E6" s="16" t="s">
@@ -4273,17 +4303,17 @@
         <v>0.33333333333333337</v>
       </c>
       <c r="G6" s="93"/>
-      <c r="H6" s="127">
+      <c r="H6" s="119">
         <f>G6*F6+G7*F7</f>
         <v>0</v>
       </c>
-      <c r="I6" s="144"/>
+      <c r="I6" s="135"/>
     </row>
     <row r="7" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="111"/>
-      <c r="B7" s="123"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="126"/>
+      <c r="A7" s="128"/>
+      <c r="B7" s="137"/>
+      <c r="C7" s="133"/>
+      <c r="D7" s="108"/>
       <c r="E7" s="17" t="s">
         <v>102</v>
       </c>
@@ -4291,20 +4321,20 @@
         <v>0.66666666666666674</v>
       </c>
       <c r="G7" s="96"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="134"/>
+      <c r="H7" s="164"/>
+      <c r="I7" s="136"/>
     </row>
     <row r="8" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="118" t="s">
+      <c r="A8" s="120" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="120" t="s">
+      <c r="B8" s="114" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="121">
+      <c r="C8" s="117">
         <v>3</v>
       </c>
-      <c r="D8" s="131">
+      <c r="D8" s="116">
         <v>2</v>
       </c>
       <c r="E8" s="15" t="s">
@@ -4314,20 +4344,20 @@
         <v>0.4</v>
       </c>
       <c r="G8" s="94"/>
-      <c r="H8" s="127">
+      <c r="H8" s="119">
         <f>G8*F8+G9*F9</f>
         <v>0</v>
       </c>
-      <c r="I8" s="133">
+      <c r="I8" s="134">
         <f>(H8*D8+H10*D10)/C8</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="118"/>
-      <c r="B9" s="120"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="131"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="114"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="116"/>
       <c r="E9" s="17" t="s">
         <v>102</v>
       </c>
@@ -4335,15 +4365,15 @@
         <v>0.6</v>
       </c>
       <c r="G9" s="95"/>
-      <c r="H9" s="127"/>
-      <c r="I9" s="144"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="135"/>
     </row>
     <row r="10" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="118"/>
+      <c r="A10" s="120"/>
       <c r="B10" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="C10" s="121"/>
+      <c r="C10" s="117"/>
       <c r="D10" s="20">
         <v>1</v>
       </c>
@@ -4358,20 +4388,20 @@
         <f>G10*F10</f>
         <v>0</v>
       </c>
-      <c r="I10" s="144"/>
+      <c r="I10" s="135"/>
       <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="159" t="s">
+      <c r="A11" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B11" s="152" t="s">
+      <c r="B11" s="165" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="141">
+      <c r="C11" s="156">
         <v>5</v>
       </c>
-      <c r="D11" s="143">
+      <c r="D11" s="115">
         <v>2</v>
       </c>
       <c r="E11" s="15" t="s">
@@ -4381,21 +4411,21 @@
         <v>0.4</v>
       </c>
       <c r="G11" s="97"/>
-      <c r="H11" s="135">
+      <c r="H11" s="118">
         <f>G11*F11+G12*F12+G13*F13+G14*F14</f>
         <v>0</v>
       </c>
-      <c r="I11" s="133">
+      <c r="I11" s="134">
         <f>(H11*D11+H15*D15+H18*D18+H21*D21)/C11</f>
         <v>0</v>
       </c>
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="160"/>
-      <c r="B12" s="153"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="131"/>
+      <c r="A12" s="139"/>
+      <c r="B12" s="111"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="116"/>
       <c r="E12" s="16" t="s">
         <v>114</v>
       </c>
@@ -4403,15 +4433,15 @@
         <v>0.2</v>
       </c>
       <c r="G12" s="93"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="144"/>
+      <c r="H12" s="119"/>
+      <c r="I12" s="135"/>
       <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="160"/>
-      <c r="B13" s="153"/>
-      <c r="C13" s="121"/>
-      <c r="D13" s="131"/>
+      <c r="A13" s="139"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="116"/>
       <c r="E13" s="16" t="s">
         <v>115</v>
       </c>
@@ -4419,15 +4449,15 @@
         <v>0.2</v>
       </c>
       <c r="G13" s="93"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="144"/>
+      <c r="H13" s="119"/>
+      <c r="I13" s="135"/>
       <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="160"/>
-      <c r="B14" s="153"/>
-      <c r="C14" s="121"/>
-      <c r="D14" s="131"/>
+      <c r="A14" s="139"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="116"/>
       <c r="E14" s="16" t="s">
         <v>116</v>
       </c>
@@ -4435,17 +4465,17 @@
         <v>0.2</v>
       </c>
       <c r="G14" s="93"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="144"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="135"/>
       <c r="K14" s="3"/>
     </row>
     <row r="15" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="160"/>
-      <c r="B15" s="153" t="s">
+      <c r="A15" s="139"/>
+      <c r="B15" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="121"/>
-      <c r="D15" s="131">
+      <c r="C15" s="117"/>
+      <c r="D15" s="116">
         <v>1</v>
       </c>
       <c r="E15" s="15" t="s">
@@ -4455,18 +4485,18 @@
         <v>0.1</v>
       </c>
       <c r="G15" s="94"/>
-      <c r="H15" s="127">
+      <c r="H15" s="119">
         <f>G15*F15+G16*F16+G17*F17</f>
         <v>0</v>
       </c>
-      <c r="I15" s="144"/>
+      <c r="I15" s="135"/>
       <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="160"/>
-      <c r="B16" s="153"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="131"/>
+      <c r="A16" s="139"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="116"/>
       <c r="E16" s="16" t="s">
         <v>89</v>
       </c>
@@ -4474,15 +4504,15 @@
         <v>0.3</v>
       </c>
       <c r="G16" s="98"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="144"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="135"/>
       <c r="K16" s="3"/>
     </row>
     <row r="17" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="160"/>
-      <c r="B17" s="153"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="131"/>
+      <c r="A17" s="139"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="116"/>
       <c r="E17" s="17" t="s">
         <v>118</v>
       </c>
@@ -4490,17 +4520,17 @@
         <v>0.6</v>
       </c>
       <c r="G17" s="95"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="144"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="135"/>
       <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="160"/>
-      <c r="B18" s="153" t="s">
+      <c r="A18" s="139"/>
+      <c r="B18" s="111" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="121"/>
-      <c r="D18" s="131">
+      <c r="C18" s="117"/>
+      <c r="D18" s="116">
         <v>1</v>
       </c>
       <c r="E18" s="15" t="s">
@@ -4510,18 +4540,18 @@
         <v>0.2</v>
       </c>
       <c r="G18" s="94"/>
-      <c r="H18" s="127">
+      <c r="H18" s="119">
         <f>G18*F18+G19*F19+G20*F20</f>
         <v>0</v>
       </c>
-      <c r="I18" s="144"/>
+      <c r="I18" s="135"/>
       <c r="K18" s="3"/>
     </row>
     <row r="19" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="160"/>
-      <c r="B19" s="153"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="131"/>
+      <c r="A19" s="139"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="116"/>
       <c r="E19" s="16" t="s">
         <v>98</v>
       </c>
@@ -4529,15 +4559,15 @@
         <v>0.3</v>
       </c>
       <c r="G19" s="98"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="144"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="135"/>
       <c r="K19" s="3"/>
     </row>
     <row r="20" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="160"/>
-      <c r="B20" s="153"/>
-      <c r="C20" s="121"/>
-      <c r="D20" s="131"/>
+      <c r="A20" s="139"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="116"/>
       <c r="E20" s="17" t="s">
         <v>99</v>
       </c>
@@ -4545,17 +4575,17 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="95"/>
-      <c r="H20" s="127"/>
-      <c r="I20" s="144"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="135"/>
       <c r="K20" s="3"/>
     </row>
     <row r="21" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="160"/>
-      <c r="B21" s="153" t="s">
+      <c r="A21" s="139"/>
+      <c r="B21" s="111" t="s">
         <v>132</v>
       </c>
-      <c r="C21" s="121"/>
-      <c r="D21" s="131">
+      <c r="C21" s="117"/>
+      <c r="D21" s="116">
         <v>1</v>
       </c>
       <c r="E21" s="16" t="s">
@@ -4565,18 +4595,18 @@
         <v>0.2</v>
       </c>
       <c r="G21" s="93"/>
-      <c r="H21" s="127">
+      <c r="H21" s="119">
         <f>G21*F21+G22*F22+G23*F23</f>
         <v>0</v>
       </c>
-      <c r="I21" s="144"/>
+      <c r="I21" s="135"/>
       <c r="K21" s="3"/>
     </row>
     <row r="22" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="160"/>
-      <c r="B22" s="153"/>
-      <c r="C22" s="121"/>
-      <c r="D22" s="131"/>
+      <c r="A22" s="139"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="116"/>
       <c r="E22" s="16" t="s">
         <v>119</v>
       </c>
@@ -4584,15 +4614,15 @@
         <v>0.4</v>
       </c>
       <c r="G22" s="93"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="144"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="135"/>
       <c r="K22" s="3"/>
     </row>
     <row r="23" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="161"/>
-      <c r="B23" s="191"/>
-      <c r="C23" s="122"/>
-      <c r="D23" s="132"/>
+      <c r="A23" s="174"/>
+      <c r="B23" s="205"/>
+      <c r="C23" s="157"/>
+      <c r="D23" s="163"/>
       <c r="E23" s="17" t="s">
         <v>120</v>
       </c>
@@ -4600,21 +4630,21 @@
         <v>0.4</v>
       </c>
       <c r="G23" s="96"/>
-      <c r="H23" s="130"/>
-      <c r="I23" s="134"/>
+      <c r="H23" s="164"/>
+      <c r="I23" s="136"/>
       <c r="K23" s="3"/>
     </row>
     <row r="24" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="174" t="s">
+      <c r="A24" s="183" t="s">
         <v>137</v>
       </c>
-      <c r="B24" s="177" t="s">
+      <c r="B24" s="186" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="142">
+      <c r="C24" s="105">
         <v>6</v>
       </c>
-      <c r="D24" s="125">
+      <c r="D24" s="107">
         <v>3</v>
       </c>
       <c r="E24" s="16" t="s">
@@ -4624,21 +4654,21 @@
         <v>0.2</v>
       </c>
       <c r="G24" s="93"/>
-      <c r="H24" s="127">
+      <c r="H24" s="119">
         <f>F24*G24+F25*G25+F26*G26</f>
         <v>0</v>
       </c>
-      <c r="I24" s="144">
+      <c r="I24" s="135">
         <f>(H24*D24+H27*D27)/C24</f>
         <v>0</v>
       </c>
       <c r="K24" s="3"/>
     </row>
     <row r="25" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="174"/>
-      <c r="B25" s="177"/>
-      <c r="C25" s="142"/>
-      <c r="D25" s="125"/>
+      <c r="A25" s="183"/>
+      <c r="B25" s="186"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="107"/>
       <c r="E25" s="16" t="s">
         <v>146</v>
       </c>
@@ -4646,15 +4676,15 @@
         <v>0.4</v>
       </c>
       <c r="G25" s="93"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="144"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="135"/>
       <c r="K25" s="3"/>
     </row>
     <row r="26" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="175"/>
-      <c r="B26" s="178"/>
-      <c r="C26" s="179"/>
-      <c r="D26" s="180"/>
+      <c r="A26" s="184"/>
+      <c r="B26" s="187"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="188"/>
       <c r="E26" s="16" t="s">
         <v>102</v>
       </c>
@@ -4662,17 +4692,17 @@
         <v>0.4</v>
       </c>
       <c r="G26" s="93"/>
-      <c r="H26" s="127"/>
-      <c r="I26" s="144"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="135"/>
       <c r="K26" s="3"/>
     </row>
     <row r="27" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="175"/>
-      <c r="B27" s="156" t="s">
+      <c r="A27" s="184"/>
+      <c r="B27" s="189" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="179"/>
-      <c r="D27" s="131">
+      <c r="C27" s="106"/>
+      <c r="D27" s="116">
         <v>3</v>
       </c>
       <c r="E27" s="15" t="s">
@@ -4683,18 +4713,18 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="G27" s="94"/>
-      <c r="H27" s="127">
+      <c r="H27" s="119">
         <f>F27*G27+F28*G28+F29*G29</f>
         <v>0</v>
       </c>
-      <c r="I27" s="144"/>
+      <c r="I27" s="135"/>
       <c r="K27" s="3"/>
     </row>
     <row r="28" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="176"/>
-      <c r="B28" s="156"/>
-      <c r="C28" s="166"/>
-      <c r="D28" s="131"/>
+      <c r="A28" s="185"/>
+      <c r="B28" s="189"/>
+      <c r="C28" s="179"/>
+      <c r="D28" s="116"/>
       <c r="E28" s="16" t="s">
         <v>112</v>
       </c>
@@ -4703,15 +4733,15 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="G28" s="98"/>
-      <c r="H28" s="127"/>
-      <c r="I28" s="144"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="135"/>
       <c r="K28" s="3"/>
     </row>
     <row r="29" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="176"/>
-      <c r="B29" s="156"/>
-      <c r="C29" s="166"/>
-      <c r="D29" s="131"/>
+      <c r="A29" s="185"/>
+      <c r="B29" s="189"/>
+      <c r="C29" s="179"/>
+      <c r="D29" s="116"/>
       <c r="E29" s="17" t="s">
         <v>102</v>
       </c>
@@ -4720,21 +4750,21 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="G29" s="95"/>
-      <c r="H29" s="127"/>
-      <c r="I29" s="144"/>
+      <c r="H29" s="119"/>
+      <c r="I29" s="135"/>
       <c r="K29" s="3"/>
     </row>
     <row r="30" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="187" t="s">
+      <c r="A30" s="102" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="189" t="s">
+      <c r="B30" s="160" t="s">
         <v>138</v>
       </c>
-      <c r="C30" s="141">
-        <v>1</v>
-      </c>
-      <c r="D30" s="124">
+      <c r="C30" s="156">
+        <v>1</v>
+      </c>
+      <c r="D30" s="151">
         <v>1</v>
       </c>
       <c r="E30" s="15" t="s">
@@ -4744,21 +4774,21 @@
         <v>0.5</v>
       </c>
       <c r="G30" s="97"/>
-      <c r="H30" s="135">
+      <c r="H30" s="118">
         <f>G30*F30+G31*F31</f>
         <v>0</v>
       </c>
-      <c r="I30" s="133">
+      <c r="I30" s="134">
         <f>(H30*D30)/C30</f>
         <v>0</v>
       </c>
       <c r="K30" s="3"/>
     </row>
     <row r="31" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="188"/>
-      <c r="B31" s="190"/>
-      <c r="C31" s="122"/>
-      <c r="D31" s="126"/>
+      <c r="A31" s="204"/>
+      <c r="B31" s="166"/>
+      <c r="C31" s="157"/>
+      <c r="D31" s="108"/>
       <c r="E31" s="17" t="s">
         <v>107</v>
       </c>
@@ -4766,18 +4796,18 @@
         <v>0.5</v>
       </c>
       <c r="G31" s="96"/>
-      <c r="H31" s="130"/>
-      <c r="I31" s="134"/>
+      <c r="H31" s="164"/>
+      <c r="I31" s="136"/>
       <c r="K31" s="3"/>
     </row>
     <row r="32" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="170" t="s">
+      <c r="A32" s="145" t="s">
         <v>35</v>
       </c>
       <c r="B32" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="172">
+      <c r="C32" s="104">
         <v>3</v>
       </c>
       <c r="D32" s="14">
@@ -4794,18 +4824,18 @@
         <f>G32*F32</f>
         <v>0</v>
       </c>
-      <c r="I32" s="133">
+      <c r="I32" s="134">
         <f>(H32*D32+H33*D33)/C32</f>
         <v>0</v>
       </c>
       <c r="K32" s="3"/>
     </row>
     <row r="33" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="171"/>
+      <c r="A33" s="146"/>
       <c r="B33" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="173"/>
+      <c r="C33" s="147"/>
       <c r="D33" s="22">
         <v>1</v>
       </c>
@@ -4820,20 +4850,20 @@
         <f>G33*F33</f>
         <v>0</v>
       </c>
-      <c r="I33" s="134"/>
+      <c r="I33" s="136"/>
       <c r="K33" s="3"/>
     </row>
     <row r="34" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="181" t="s">
+      <c r="A34" s="148" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="139" t="s">
+      <c r="B34" s="195" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="141">
+      <c r="C34" s="156">
         <v>4</v>
       </c>
-      <c r="D34" s="143">
+      <c r="D34" s="115">
         <v>1</v>
       </c>
       <c r="E34" s="15" t="s">
@@ -4843,21 +4873,21 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="97"/>
-      <c r="H34" s="135">
+      <c r="H34" s="118">
         <f>G34*F34+G35*F35</f>
         <v>0</v>
       </c>
-      <c r="I34" s="133">
+      <c r="I34" s="134">
         <f>(H34*D34+H36*D36+H38*D38)/C34</f>
         <v>0</v>
       </c>
       <c r="K34" s="3"/>
     </row>
     <row r="35" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="182"/>
-      <c r="B35" s="140"/>
-      <c r="C35" s="121"/>
-      <c r="D35" s="131"/>
+      <c r="A35" s="149"/>
+      <c r="B35" s="196"/>
+      <c r="C35" s="117"/>
+      <c r="D35" s="116"/>
       <c r="E35" s="16" t="s">
         <v>109</v>
       </c>
@@ -4865,17 +4895,17 @@
         <v>0.5</v>
       </c>
       <c r="G35" s="93"/>
-      <c r="H35" s="127"/>
-      <c r="I35" s="144"/>
+      <c r="H35" s="119"/>
+      <c r="I35" s="135"/>
       <c r="K35" s="3"/>
     </row>
     <row r="36" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="182"/>
-      <c r="B36" s="140" t="s">
+      <c r="A36" s="149"/>
+      <c r="B36" s="196" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="121"/>
-      <c r="D36" s="131">
+      <c r="C36" s="117"/>
+      <c r="D36" s="116">
         <v>2.5</v>
       </c>
       <c r="E36" s="15" t="s">
@@ -4885,18 +4915,18 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="94"/>
-      <c r="H36" s="127">
+      <c r="H36" s="119">
         <f>G36*F36+G37*F37</f>
         <v>0</v>
       </c>
-      <c r="I36" s="144"/>
+      <c r="I36" s="135"/>
       <c r="K36" s="3"/>
     </row>
     <row r="37" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="182"/>
-      <c r="B37" s="140"/>
-      <c r="C37" s="121"/>
-      <c r="D37" s="131"/>
+      <c r="A37" s="149"/>
+      <c r="B37" s="196"/>
+      <c r="C37" s="117"/>
+      <c r="D37" s="116"/>
       <c r="E37" s="17" t="s">
         <v>148</v>
       </c>
@@ -4904,16 +4934,16 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="95"/>
-      <c r="H37" s="127"/>
-      <c r="I37" s="144"/>
+      <c r="H37" s="119"/>
+      <c r="I37" s="135"/>
       <c r="K37" s="3"/>
     </row>
     <row r="38" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="183"/>
+      <c r="A38" s="150"/>
       <c r="B38" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="122"/>
+      <c r="C38" s="157"/>
       <c r="D38" s="22">
         <v>0.5</v>
       </c>
@@ -4928,7 +4958,7 @@
         <f>G38*F38</f>
         <v>0</v>
       </c>
-      <c r="I38" s="134"/>
+      <c r="I38" s="136"/>
       <c r="K38" s="3"/>
     </row>
     <row r="39" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -4962,26 +4992,26 @@
       <c r="K39" s="3"/>
     </row>
     <row r="40" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="184" t="s">
+      <c r="A40" s="140" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="185"/>
-      <c r="C40" s="184">
+      <c r="B40" s="141"/>
+      <c r="C40" s="140">
         <f>SUM(C2:C39)</f>
         <v>30</v>
       </c>
-      <c r="D40" s="186"/>
-      <c r="E40" s="149">
+      <c r="D40" s="142"/>
+      <c r="E40" s="123">
         <f>(I2*C2+I8*C8+I11*C11+I24*C24+I30*C30+I32*C32+I34*C34+I39*C39)/C40</f>
         <v>0</v>
       </c>
-      <c r="F40" s="150"/>
-      <c r="G40" s="150"/>
-      <c r="H40" s="157" t="str">
+      <c r="F40" s="124"/>
+      <c r="G40" s="124"/>
+      <c r="H40" s="143" t="str">
         <f>IF(OR(I2&lt;10,I8&lt;10,I11&lt;10,I24&lt;10,I30&lt;10,I32&lt;10,I34&lt;10,I39&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I40" s="158"/>
+      <c r="I40" s="144"/>
       <c r="K40" s="3"/>
     </row>
     <row r="41" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -4998,6 +5028,57 @@
     </row>
   </sheetData>
   <mergeCells count="67">
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="C24:C29"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="H27:H29"/>
+    <mergeCell ref="C11:C23"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="H11:H14"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="I34:I38"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="I24:I29"/>
+    <mergeCell ref="I11:I23"/>
     <mergeCell ref="A11:A23"/>
     <mergeCell ref="B11:B14"/>
     <mergeCell ref="E1:G1"/>
@@ -5014,57 +5095,6 @@
     <mergeCell ref="C2:C7"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="H18:H20"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="I24:I29"/>
-    <mergeCell ref="I11:I23"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="I34:I38"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C24:C29"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="H24:H26"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="H27:H29"/>
-    <mergeCell ref="C11:C23"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="H11:H14"/>
   </mergeCells>
   <conditionalFormatting sqref="H40">
     <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
@@ -5112,31 +5142,31 @@
       <c r="B1" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="200" t="s">
+      <c r="C1" s="206" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="201"/>
-      <c r="E1" s="149" t="s">
+      <c r="D1" s="207"/>
+      <c r="E1" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="150"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="149" t="s">
+      <c r="F1" s="124"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="123" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="151"/>
+      <c r="I1" s="125"/>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="194" t="s">
+      <c r="A2" s="208" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="197" t="s">
+      <c r="B2" s="211" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="114">
+      <c r="C2" s="131">
         <v>30</v>
       </c>
-      <c r="D2" s="143">
+      <c r="D2" s="115">
         <v>30</v>
       </c>
       <c r="E2" s="23" t="s">
@@ -5147,20 +5177,20 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="G2" s="88"/>
-      <c r="H2" s="135">
+      <c r="H2" s="118">
         <f>F2*G2+F3*G3+G4*F4</f>
         <v>0</v>
       </c>
-      <c r="I2" s="133">
+      <c r="I2" s="134">
         <f>(H2*D2)/C2</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="195"/>
-      <c r="B3" s="198"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="131"/>
+      <c r="A3" s="209"/>
+      <c r="B3" s="212"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="116"/>
       <c r="E3" s="11" t="s">
         <v>152</v>
       </c>
@@ -5169,14 +5199,14 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="G3" s="89"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="144"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="135"/>
     </row>
     <row r="4" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="196"/>
-      <c r="B4" s="199"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="132"/>
+      <c r="A4" s="210"/>
+      <c r="B4" s="213"/>
+      <c r="C4" s="133"/>
+      <c r="D4" s="163"/>
       <c r="E4" s="17" t="s">
         <v>153</v>
       </c>
@@ -5185,31 +5215,31 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="G4" s="95"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="134"/>
+      <c r="H4" s="164"/>
+      <c r="I4" s="136"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="143" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="158"/>
-      <c r="C5" s="157">
+      <c r="B5" s="144"/>
+      <c r="C5" s="143">
         <f>SUM(C2:C2)</f>
         <v>30</v>
       </c>
-      <c r="D5" s="158"/>
-      <c r="E5" s="149">
+      <c r="D5" s="144"/>
+      <c r="E5" s="123">
         <f>(I2*C2)/C5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="150"/>
-      <c r="G5" s="151"/>
-      <c r="H5" s="157" t="str">
+      <c r="F5" s="124"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="143" t="str">
         <f>IF(OR(I2&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I5" s="158"/>
+      <c r="I5" s="144"/>
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -5578,7 +5608,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA6D249-F910-483A-9894-B4C0568AF5EA}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.140625" defaultRowHeight="30.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="35.140625" style="3" customWidth="1"/>
@@ -5591,38 +5621,38 @@
     <col min="12" max="16384" width="12.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="145" t="s">
+      <c r="C1" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="146"/>
-      <c r="E1" s="149" t="s">
+      <c r="D1" s="122"/>
+      <c r="E1" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="150"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="149" t="s">
+      <c r="F1" s="124"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="123" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="151"/>
-    </row>
-    <row r="2" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="109" t="s">
+      <c r="I1" s="125"/>
+    </row>
+    <row r="2" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="126" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="205" t="s">
+      <c r="B2" s="129" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="114">
+      <c r="C2" s="131">
         <v>10</v>
       </c>
-      <c r="D2" s="143">
+      <c r="D2" s="115">
         <v>2</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -5633,21 +5663,21 @@
         <v>0.13333333333333333</v>
       </c>
       <c r="G2" s="93"/>
-      <c r="H2" s="135">
+      <c r="H2" s="118">
         <f>G2*F2+G3*F3+G4*F4+G5*F5</f>
         <v>0</v>
       </c>
-      <c r="I2" s="133">
-        <f>(H2*D2+H6*D6+H7*D7+H10*D10)/C2</f>
+      <c r="I2" s="134">
+        <f>(H2*D2+H6*D6+H8*D8+H11*D11)/C2</f>
         <v>0</v>
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="110"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="131"/>
+    <row r="3" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="127"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="116"/>
       <c r="E3" s="11" t="s">
         <v>99</v>
       </c>
@@ -5656,15 +5686,15 @@
         <v>0.31111111111111112</v>
       </c>
       <c r="G3" s="93"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="144"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="135"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="110"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="115"/>
-      <c r="D4" s="131"/>
+    <row r="4" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="127"/>
+      <c r="B4" s="130"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="116"/>
       <c r="E4" s="11" t="s">
         <v>175</v>
       </c>
@@ -5673,15 +5703,15 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="G4" s="93"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="144"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="135"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="110"/>
-      <c r="B5" s="117"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="131"/>
+    <row r="5" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="127"/>
+      <c r="B5" s="130"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="116"/>
       <c r="E5" s="11" t="s">
         <v>89</v>
       </c>
@@ -5690,264 +5720,240 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="G5" s="93"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="144"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="135"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="110"/>
-      <c r="B6" s="39" t="s">
+    <row r="6" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="127"/>
+      <c r="B6" s="130" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="115"/>
-      <c r="D6" s="20">
+      <c r="C6" s="132"/>
+      <c r="D6" s="107">
         <v>3</v>
       </c>
-      <c r="E6" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="24">
-        <v>1</v>
-      </c>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
       <c r="G6" s="94"/>
-      <c r="H6" s="11">
-        <f>G6*F6</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="144"/>
-    </row>
-    <row r="7" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="110"/>
-      <c r="B7" s="117" t="s">
+      <c r="H6" s="109">
+        <f>G6*F6+G7*F7</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="135"/>
+    </row>
+    <row r="7" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="127"/>
+      <c r="B7" s="130"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" s="26"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="135"/>
+    </row>
+    <row r="8" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="127"/>
+      <c r="B8" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="115"/>
-      <c r="D7" s="131">
+      <c r="C8" s="132"/>
+      <c r="D8" s="116">
         <v>3</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E8" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="F7" s="24"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="127">
-        <f>G7*F7+G8*F8+G9*F9</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="144"/>
-    </row>
-    <row r="8" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="110"/>
-      <c r="B8" s="117"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="11" t="s">
+      <c r="F8" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="G8" s="94"/>
+      <c r="H8" s="119">
+        <f>G8*F8+G9*F9+G10*F10</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="135"/>
+    </row>
+    <row r="9" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="127"/>
+      <c r="B9" s="130"/>
+      <c r="C9" s="132"/>
+      <c r="D9" s="116"/>
+      <c r="E9" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="F8" s="25"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="127"/>
-      <c r="I8" s="144"/>
-    </row>
-    <row r="9" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="110"/>
-      <c r="B9" s="117"/>
-      <c r="C9" s="115"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="17" t="s">
+      <c r="F9" s="25">
+        <v>0.4</v>
+      </c>
+      <c r="G9" s="98"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="135"/>
+    </row>
+    <row r="10" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="127"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="132"/>
+      <c r="D10" s="116"/>
+      <c r="E10" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="F9" s="26"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="127"/>
-      <c r="I9" s="144"/>
-    </row>
-    <row r="10" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="111"/>
-      <c r="B10" s="40" t="s">
+      <c r="F10" s="25">
+        <v>0.4</v>
+      </c>
+      <c r="G10" s="98"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="135"/>
+    </row>
+    <row r="11" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="127"/>
+      <c r="B11" s="130" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="116"/>
-      <c r="D10" s="22">
+      <c r="C11" s="132"/>
+      <c r="D11" s="107">
         <v>2</v>
       </c>
-      <c r="E10" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="26">
-        <v>1</v>
-      </c>
-      <c r="G10" s="96"/>
-      <c r="H10" s="12">
-        <f>G10*F10</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="134"/>
-    </row>
-    <row r="11" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="118" t="s">
+      <c r="E11" s="15"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="109">
+        <f>G11*F11+G12*F12</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="135"/>
+    </row>
+    <row r="12" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="128"/>
+      <c r="B12" s="137"/>
+      <c r="C12" s="133"/>
+      <c r="D12" s="108"/>
+      <c r="E12" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="26"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="136"/>
+    </row>
+    <row r="13" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="120" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="204" t="s">
+      <c r="B13" s="113" t="s">
         <v>155</v>
       </c>
-      <c r="C11" s="121">
+      <c r="C13" s="117">
         <v>4</v>
       </c>
-      <c r="D11" s="143">
+      <c r="D13" s="115">
         <v>2</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E13" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F13" s="24">
         <v>0.2</v>
       </c>
-      <c r="G11" s="94"/>
-      <c r="H11" s="135">
-        <f>G11*F11+G12*F12+G13*F13+G14*F14</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="133">
-        <f>(H11*D11+H15*D15)/C11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="118"/>
-      <c r="B12" s="120"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="16" t="s">
+      <c r="G13" s="94"/>
+      <c r="H13" s="118">
+        <f>G13*F13+G14*F14+G15*F15+G16*F16</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="134">
+        <f>(H13*D13+H17*D17)/C13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="120"/>
+      <c r="B14" s="114"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F14" s="25">
         <v>0.2</v>
       </c>
-      <c r="G12" s="98"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="144"/>
-    </row>
-    <row r="13" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="118"/>
-      <c r="B13" s="120"/>
-      <c r="C13" s="121"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="16" t="s">
+      <c r="G14" s="98"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="135"/>
+    </row>
+    <row r="15" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="120"/>
+      <c r="B15" s="114"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F15" s="25">
         <v>0.2</v>
       </c>
-      <c r="G13" s="98"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="144"/>
-    </row>
-    <row r="14" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="118"/>
-      <c r="B14" s="120"/>
-      <c r="C14" s="121"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="17" t="s">
+      <c r="G15" s="98"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="135"/>
+    </row>
+    <row r="16" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="120"/>
+      <c r="B16" s="114"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F16" s="26">
         <v>0.4</v>
       </c>
-      <c r="G14" s="95"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="144"/>
-    </row>
-    <row r="15" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="118"/>
-      <c r="B15" s="35" t="s">
+      <c r="G16" s="95"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="135"/>
+    </row>
+    <row r="17" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="120"/>
+      <c r="B17" s="114" t="s">
         <v>156</v>
       </c>
-      <c r="C15" s="121"/>
-      <c r="D15" s="20">
+      <c r="C17" s="117"/>
+      <c r="D17" s="116">
         <v>2</v>
       </c>
-      <c r="E15" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="25">
-        <v>1</v>
-      </c>
-      <c r="G15" s="93"/>
-      <c r="H15" s="11">
-        <f>G15*F15</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="144"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="159" t="s">
-        <v>157</v>
-      </c>
-      <c r="B16" s="152" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="141">
-        <v>5</v>
-      </c>
-      <c r="D16" s="143">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15" t="s">
+      <c r="E17" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="F16" s="24">
-        <v>0.1</v>
-      </c>
-      <c r="G16" s="97"/>
-      <c r="H16" s="135">
-        <f>G16*F16+G17*F17+G18*F18+G19*F19</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="133">
-        <f>(H16*D16+H20*D20+H23*D23)/C16</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="160"/>
-      <c r="B17" s="153"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="16" t="s">
-        <v>98</v>
-      </c>
       <c r="F17" s="25">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G17" s="93"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="144"/>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="160"/>
-      <c r="B18" s="153"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="131"/>
+      <c r="H17" s="119">
+        <f>G17*F17+G18*F18+G19*F19</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="135"/>
+    </row>
+    <row r="18" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="120"/>
+      <c r="B18" s="114"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="116"/>
       <c r="E18" s="16" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F18" s="25">
         <v>0.3</v>
       </c>
       <c r="G18" s="93"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="144"/>
-      <c r="K18" s="3"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="135"/>
     </row>
     <row r="19" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="160"/>
-      <c r="B19" s="153"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="131"/>
+      <c r="A19" s="120"/>
+      <c r="B19" s="162"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="163"/>
       <c r="E19" s="16" t="s">
         <v>102</v>
       </c>
@@ -5955,322 +5961,284 @@
         <v>0.4</v>
       </c>
       <c r="G19" s="93"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="144"/>
+      <c r="H19" s="164"/>
+      <c r="I19" s="135"/>
       <c r="K19" s="3"/>
     </row>
     <row r="20" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="160"/>
-      <c r="B20" s="153" t="s">
+      <c r="A20" s="138" t="s">
+        <v>157</v>
+      </c>
+      <c r="B20" s="165" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="156">
+        <v>5</v>
+      </c>
+      <c r="D20" s="115">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20" s="24">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="97"/>
+      <c r="H20" s="118">
+        <f>G20*F20+G21*F21+G22*F22+G23*F23</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="134">
+        <f>(H20*D20+H24*D24+H26*D26)/C20</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="139"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="116"/>
+      <c r="E21" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="G21" s="93"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="135"/>
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="139"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F22" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="G22" s="93"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="135"/>
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="139"/>
+      <c r="B23" s="111"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="25">
+        <v>0.4</v>
+      </c>
+      <c r="G23" s="93"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="135"/>
+      <c r="K23" s="3"/>
+    </row>
+    <row r="24" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="139"/>
+      <c r="B24" s="111" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="121"/>
-      <c r="D20" s="131">
+      <c r="C24" s="117"/>
+      <c r="D24" s="116">
         <v>2</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E24" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="F20" s="24"/>
-      <c r="G20" s="94"/>
-      <c r="H20" s="127">
-        <f>G20*F20+G21*F21+G22*F22</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="144"/>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="160"/>
-      <c r="B21" s="153"/>
-      <c r="C21" s="121"/>
-      <c r="D21" s="131"/>
-      <c r="E21" s="16" t="s">
+      <c r="F24" s="24"/>
+      <c r="G24" s="94"/>
+      <c r="H24" s="119">
+        <f>G24*F24+G25*F25</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="135"/>
+      <c r="K24" s="3"/>
+    </row>
+    <row r="25" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="139"/>
+      <c r="B25" s="111"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="116"/>
+      <c r="E25" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="25"/>
-      <c r="G21" s="98"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="144"/>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="160"/>
-      <c r="B22" s="153"/>
-      <c r="C22" s="121"/>
-      <c r="D22" s="131"/>
-      <c r="E22" s="17" t="s">
+      <c r="F25" s="25"/>
+      <c r="G25" s="98"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="135"/>
+      <c r="K25" s="3"/>
+    </row>
+    <row r="26" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="139"/>
+      <c r="B26" s="111" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="117"/>
+      <c r="D26" s="107">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="94"/>
+      <c r="H26" s="109">
+        <f>G26*F26+G27*F27</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="135"/>
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="139"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="95"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="135"/>
+      <c r="K27" s="3"/>
+    </row>
+    <row r="28" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="102" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" s="160" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="104">
+        <v>3</v>
+      </c>
+      <c r="D28" s="115">
+        <v>2</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F28" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="G28" s="98"/>
+      <c r="H28" s="118">
+        <f>F28*G28+G29*F29+G30*F30</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="134">
+        <f>(H28*D28+H31*D31)/C28</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="3"/>
+    </row>
+    <row r="29" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="103"/>
+      <c r="B29" s="161"/>
+      <c r="C29" s="105"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F29" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="G29" s="98"/>
+      <c r="H29" s="119"/>
+      <c r="I29" s="135"/>
+      <c r="K29" s="3"/>
+    </row>
+    <row r="30" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="103"/>
+      <c r="B30" s="161"/>
+      <c r="C30" s="105"/>
+      <c r="D30" s="116"/>
+      <c r="E30" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="F22" s="26"/>
-      <c r="G22" s="95"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="144"/>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="160"/>
-      <c r="B23" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="121"/>
-      <c r="D23" s="20">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="24">
-        <v>1</v>
-      </c>
-      <c r="G23" s="94"/>
-      <c r="H23" s="11">
-        <f>G23*F23</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="144"/>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="187" t="s">
-        <v>158</v>
-      </c>
-      <c r="B24" s="84" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="172">
-        <v>3</v>
-      </c>
-      <c r="D24" s="14">
-        <v>2</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" s="24">
-        <v>1</v>
-      </c>
-      <c r="G24" s="97"/>
-      <c r="H24" s="23">
-        <f>F24*G24</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="133">
-        <f>(H24*D24+H25*D25)/C24</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="203"/>
-      <c r="B25" s="85" t="s">
+      <c r="F30" s="26">
+        <v>0.4</v>
+      </c>
+      <c r="G30" s="95"/>
+      <c r="H30" s="119"/>
+      <c r="I30" s="135"/>
+      <c r="K30" s="3"/>
+    </row>
+    <row r="31" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="103"/>
+      <c r="B31" s="161" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="179"/>
-      <c r="D25" s="20">
-        <v>1</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="24">
-        <v>1</v>
-      </c>
-      <c r="G25" s="94"/>
-      <c r="H25" s="11">
-        <f>F25*G25</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="144"/>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="170" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="172">
-        <v>3</v>
-      </c>
-      <c r="D26" s="14">
-        <v>2</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" s="24">
-        <v>1</v>
-      </c>
-      <c r="G26" s="97"/>
-      <c r="H26" s="23">
-        <f>G26*F26</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="133">
-        <f>(H26*D26+H27*D27)/C26</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="171"/>
-      <c r="B27" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="173"/>
-      <c r="D27" s="22">
-        <v>1</v>
-      </c>
-      <c r="E27" s="54" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" s="55">
-        <v>1</v>
-      </c>
-      <c r="G27" s="99"/>
-      <c r="H27" s="12">
-        <f>G27*F27</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="134"/>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="181" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="69" t="s">
-        <v>159</v>
-      </c>
-      <c r="C28" s="124">
-        <v>4</v>
-      </c>
-      <c r="D28" s="19">
-        <v>1</v>
-      </c>
-      <c r="E28" s="54" t="s">
-        <v>181</v>
-      </c>
-      <c r="F28" s="55">
-        <v>1</v>
-      </c>
-      <c r="G28" s="99"/>
-      <c r="H28" s="23">
-        <f>G28*F28</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="133">
-        <f>(H28*D28+H29*D29+H31*D31+H33*D33)/C28</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="182"/>
-      <c r="B29" s="202" t="s">
-        <v>180</v>
-      </c>
-      <c r="C29" s="125"/>
-      <c r="D29" s="125">
-        <v>1.5</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="F29" s="24"/>
-      <c r="G29" s="94"/>
-      <c r="H29" s="127">
-        <f>G29*F29+G30*F30</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="144"/>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="182"/>
-      <c r="B30" s="202"/>
-      <c r="C30" s="125"/>
-      <c r="D30" s="125"/>
-      <c r="E30" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="F30" s="26"/>
-      <c r="G30" s="95"/>
-      <c r="H30" s="127"/>
-      <c r="I30" s="144"/>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="182"/>
-      <c r="B31" s="202" t="s">
-        <v>160</v>
-      </c>
-      <c r="C31" s="125"/>
-      <c r="D31" s="125">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>100</v>
-      </c>
+      <c r="C31" s="105"/>
+      <c r="D31" s="116">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15"/>
       <c r="F31" s="24"/>
       <c r="G31" s="94"/>
-      <c r="H31" s="127">
-        <f>G31*F31+G32*F32</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="144"/>
+      <c r="H31" s="119">
+        <f>G31*F31+F32*G32</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="135"/>
       <c r="K31" s="3"/>
     </row>
     <row r="32" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="182"/>
-      <c r="B32" s="202"/>
-      <c r="C32" s="125"/>
-      <c r="D32" s="125"/>
-      <c r="E32" s="17" t="s">
-        <v>179</v>
-      </c>
+      <c r="A32" s="103"/>
+      <c r="B32" s="166"/>
+      <c r="C32" s="106"/>
+      <c r="D32" s="163"/>
+      <c r="E32" s="17"/>
       <c r="F32" s="26"/>
       <c r="G32" s="95"/>
-      <c r="H32" s="127"/>
-      <c r="I32" s="144"/>
+      <c r="H32" s="164"/>
+      <c r="I32" s="135"/>
       <c r="K32" s="3"/>
     </row>
     <row r="33" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="183"/>
-      <c r="B33" s="71" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="126"/>
-      <c r="D33" s="22">
-        <v>0.5</v>
-      </c>
-      <c r="E33" s="17" t="s">
+      <c r="A33" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="104">
+        <v>3</v>
+      </c>
+      <c r="D33" s="14">
+        <v>2</v>
+      </c>
+      <c r="E33" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="F33" s="26">
-        <v>1</v>
-      </c>
-      <c r="G33" s="96"/>
-      <c r="H33" s="12">
-        <f>G33*F33</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="134"/>
+      <c r="F33" s="25">
+        <v>1</v>
+      </c>
+      <c r="G33" s="93"/>
+      <c r="H33" s="23">
+        <f t="shared" ref="H33:H39" si="0">G33*F33</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="134">
+        <f>(H33*D33+H34*D34)/C33</f>
+        <v>0</v>
+      </c>
       <c r="K33" s="3"/>
     </row>
     <row r="34" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="58" t="s">
-        <v>161</v>
-      </c>
-      <c r="C34" s="52">
-        <v>1</v>
-      </c>
-      <c r="D34" s="59">
+      <c r="A34" s="146"/>
+      <c r="B34" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="147"/>
+      <c r="D34" s="22">
         <v>1</v>
       </c>
       <c r="E34" s="54" t="s">
@@ -6279,102 +6247,281 @@
       <c r="F34" s="55">
         <v>1</v>
       </c>
-      <c r="G34" s="100"/>
-      <c r="H34" s="60">
-        <f>G34*F34</f>
-        <v>0</v>
-      </c>
-      <c r="I34" s="61">
-        <f>(H34*D34)/C34</f>
-        <v>0</v>
-      </c>
+      <c r="G34" s="99"/>
+      <c r="H34" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="136"/>
       <c r="K34" s="3"/>
     </row>
     <row r="35" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="184" t="s">
+      <c r="A35" s="148" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="69" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" s="151">
+        <v>4</v>
+      </c>
+      <c r="D35" s="19">
+        <v>1</v>
+      </c>
+      <c r="E35" s="54" t="s">
+        <v>182</v>
+      </c>
+      <c r="F35" s="55">
+        <v>1</v>
+      </c>
+      <c r="G35" s="99"/>
+      <c r="H35" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="134">
+        <f>(H35*D35+H36*D36+H37*D37+H39*D39)/C35</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="3"/>
+    </row>
+    <row r="36" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="149"/>
+      <c r="B36" s="70" t="s">
+        <v>179</v>
+      </c>
+      <c r="C36" s="107"/>
+      <c r="D36" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="E36" s="54" t="s">
+        <v>181</v>
+      </c>
+      <c r="F36" s="55">
+        <v>1</v>
+      </c>
+      <c r="G36" s="94"/>
+      <c r="H36" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="135"/>
+      <c r="K36" s="3"/>
+    </row>
+    <row r="37" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="149"/>
+      <c r="B37" s="159" t="s">
+        <v>160</v>
+      </c>
+      <c r="C37" s="107"/>
+      <c r="D37" s="116">
+        <v>1</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="F37" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="G37" s="94"/>
+      <c r="H37" s="119">
+        <f>G37*F37+G38*F38</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="135"/>
+      <c r="K37" s="3"/>
+    </row>
+    <row r="38" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="149"/>
+      <c r="B38" s="159"/>
+      <c r="C38" s="107"/>
+      <c r="D38" s="116"/>
+      <c r="E38" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="F38" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="G38" s="95"/>
+      <c r="H38" s="119"/>
+      <c r="I38" s="135"/>
+      <c r="K38" s="3"/>
+    </row>
+    <row r="39" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="150"/>
+      <c r="B39" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="108"/>
+      <c r="D39" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" s="25">
+        <v>1</v>
+      </c>
+      <c r="G39" s="98"/>
+      <c r="H39" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="136"/>
+      <c r="K39" s="3"/>
+    </row>
+    <row r="40" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="152" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="154" t="s">
+        <v>161</v>
+      </c>
+      <c r="C40" s="156">
+        <v>1</v>
+      </c>
+      <c r="D40" s="151">
+        <v>1</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F40" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="G40" s="94"/>
+      <c r="H40" s="158">
+        <f>G40*F40+G41*F41</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="134">
+        <f>(H40*D40)/C40</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="3"/>
+    </row>
+    <row r="41" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="153"/>
+      <c r="B41" s="155"/>
+      <c r="C41" s="157"/>
+      <c r="D41" s="108"/>
+      <c r="E41" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="F41" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="G41" s="95"/>
+      <c r="H41" s="110"/>
+      <c r="I41" s="136"/>
+      <c r="K41" s="3"/>
+    </row>
+    <row r="42" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="140" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="185"/>
-      <c r="C35" s="184">
-        <f>SUM(C2:C34)</f>
+      <c r="B42" s="141"/>
+      <c r="C42" s="140">
+        <f>SUM(C2:C40)</f>
         <v>30</v>
       </c>
-      <c r="D35" s="186"/>
-      <c r="E35" s="149">
-        <f>(I2*C2+I11*C11+I16*C16+I24*C24+I26*C26+I28*C28+I34*C34)/C35</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="150"/>
-      <c r="G35" s="150"/>
-      <c r="H35" s="157" t="str">
-        <f>IF(OR(I2&lt;10,I11&lt;10,I16&lt;10,I24&lt;10,I26&lt;10,I28&lt;10,I34&lt;10),"Valide pas","Valide")</f>
+      <c r="D42" s="142"/>
+      <c r="E42" s="123">
+        <f>(I2*C2+I13*C13+I20*C20+I28*C28+I33*C33+I35*C35+I40*C40)/C42</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="124"/>
+      <c r="G42" s="124"/>
+      <c r="H42" s="143" t="str">
+        <f>IF(OR(I2&lt;10,I13&lt;10,I20&lt;10,I28&lt;10,I33&lt;10,I35&lt;10,I40&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I35" s="158"/>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="36" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="62"/>
-      <c r="I36" s="62"/>
-      <c r="K36" s="3"/>
+      <c r="I42" s="144"/>
+      <c r="K42" s="3"/>
+    </row>
+    <row r="43" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="62"/>
+      <c r="I43" s="62"/>
+      <c r="K43" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="67">
+    <mergeCell ref="I28:I32"/>
+    <mergeCell ref="I13:I19"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="C20:C27"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A35:A39"/>
+    <mergeCell ref="C35:C39"/>
+    <mergeCell ref="I35:I39"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="I20:I27"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="A20:A27"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="A2:A12"/>
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C10"/>
+    <mergeCell ref="C2:C12"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="H2:H5"/>
-    <mergeCell ref="I2:I10"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="I11:I15"/>
-    <mergeCell ref="A16:A23"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="C16:C23"/>
-    <mergeCell ref="D16:D19"/>
-    <mergeCell ref="H16:H19"/>
-    <mergeCell ref="I16:I23"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="H20:H22"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="C28:C33"/>
-    <mergeCell ref="I28:I33"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="C11:C15"/>
-    <mergeCell ref="H11:H14"/>
+    <mergeCell ref="I2:I12"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A28:A32"/>
+    <mergeCell ref="C28:C32"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="C13:C19"/>
+    <mergeCell ref="H13:H16"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="H20:H23"/>
   </mergeCells>
-  <conditionalFormatting sqref="H35">
+  <conditionalFormatting sqref="H42">
     <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"Valide pas"</formula>
     </cfRule>
@@ -6382,7 +6529,7 @@
       <formula>"Valide"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I34 E35">
+  <conditionalFormatting sqref="I2:I40 E42">
     <cfRule type="cellIs" dxfId="17" priority="3" operator="lessThan">
       <formula>10</formula>
     </cfRule>
@@ -6420,28 +6567,28 @@
       <c r="B1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="145" t="s">
+      <c r="C1" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="146"/>
-      <c r="E1" s="149" t="s">
+      <c r="D1" s="122"/>
+      <c r="E1" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="150"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="192" t="s">
+      <c r="F1" s="124"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="202" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="193"/>
+      <c r="I1" s="203"/>
     </row>
     <row r="2" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="109" t="s">
+      <c r="A2" s="126" t="s">
         <v>65</v>
       </c>
       <c r="B2" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="114">
+      <c r="C2" s="131">
         <v>6</v>
       </c>
       <c r="D2" s="14">
@@ -6458,18 +6605,18 @@
         <f>G2*F2</f>
         <v>0</v>
       </c>
-      <c r="I2" s="133">
+      <c r="I2" s="134">
         <f>(H2*D2+H3*D3+H4*D4+H5*D5)/C2</f>
         <v>0</v>
       </c>
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="110"/>
+      <c r="A3" s="127"/>
       <c r="B3" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="115"/>
+      <c r="C3" s="132"/>
       <c r="D3" s="3">
         <v>1</v>
       </c>
@@ -6484,14 +6631,14 @@
         <f t="shared" ref="H3:H25" si="0">G3*F3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="144"/>
+      <c r="I3" s="135"/>
     </row>
     <row r="4" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="110"/>
+      <c r="A4" s="127"/>
       <c r="B4" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="115"/>
+      <c r="C4" s="132"/>
       <c r="D4" s="3">
         <v>2</v>
       </c>
@@ -6506,14 +6653,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I4" s="144"/>
+      <c r="I4" s="135"/>
     </row>
     <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="111"/>
+      <c r="A5" s="128"/>
       <c r="B5" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="116"/>
+      <c r="C5" s="133"/>
       <c r="D5" s="22">
         <v>2</v>
       </c>
@@ -6528,16 +6675,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="134"/>
+      <c r="I5" s="136"/>
     </row>
     <row r="6" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="120" t="s">
         <v>68</v>
       </c>
       <c r="B6" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="121">
+      <c r="C6" s="117">
         <v>4</v>
       </c>
       <c r="D6" s="3">
@@ -6554,17 +6701,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="133">
+      <c r="I6" s="134">
         <f>(H6*D6+H7*D7+H8*D8+H9*D9)/C6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="118"/>
+      <c r="A7" s="120"/>
       <c r="B7" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="121"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="3">
         <v>1</v>
       </c>
@@ -6579,14 +6726,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="144"/>
+      <c r="I7" s="135"/>
     </row>
     <row r="8" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="118"/>
+      <c r="A8" s="120"/>
       <c r="B8" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="121"/>
+      <c r="C8" s="117"/>
       <c r="D8" s="3">
         <v>1</v>
       </c>
@@ -6601,14 +6748,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="144"/>
+      <c r="I8" s="135"/>
     </row>
     <row r="9" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="118"/>
+      <c r="A9" s="120"/>
       <c r="B9" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="121"/>
+      <c r="C9" s="117"/>
       <c r="D9" s="3">
         <v>1</v>
       </c>
@@ -6623,17 +6770,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="134"/>
+      <c r="I9" s="136"/>
       <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="159" t="s">
+      <c r="A10" s="138" t="s">
         <v>164</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="C10" s="141">
+      <c r="C10" s="156">
         <v>2</v>
       </c>
       <c r="D10" s="19">
@@ -6650,18 +6797,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="133">
+      <c r="I10" s="134">
         <f>(H10*D10+H11*D11)/C10</f>
         <v>0</v>
       </c>
       <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="161"/>
+      <c r="A11" s="174"/>
       <c r="B11" s="81" t="s">
         <v>167</v>
       </c>
-      <c r="C11" s="122"/>
+      <c r="C11" s="157"/>
       <c r="D11" s="21">
         <v>1</v>
       </c>
@@ -6676,17 +6823,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="134"/>
+      <c r="I11" s="136"/>
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="174" t="s">
+      <c r="A12" s="183" t="s">
         <v>166</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="206">
+      <c r="C12" s="214">
         <v>6</v>
       </c>
       <c r="D12" s="20">
@@ -6703,18 +6850,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="144">
+      <c r="I12" s="135">
         <f>(H12*D12+H13*D13+H14*D14)/C12</f>
         <v>0</v>
       </c>
       <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="174"/>
+      <c r="A13" s="183"/>
       <c r="B13" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="C13" s="206"/>
+      <c r="C13" s="214"/>
       <c r="D13" s="20">
         <v>2</v>
       </c>
@@ -6729,15 +6876,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="144"/>
+      <c r="I13" s="135"/>
       <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="175"/>
+      <c r="A14" s="184"/>
       <c r="B14" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="207"/>
+      <c r="C14" s="215"/>
       <c r="D14" s="21">
         <v>2</v>
       </c>
@@ -6752,17 +6899,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="144"/>
+      <c r="I14" s="135"/>
       <c r="K14" s="3"/>
     </row>
     <row r="15" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="187" t="s">
+      <c r="A15" s="102" t="s">
         <v>169</v>
       </c>
       <c r="B15" s="84" t="s">
         <v>170</v>
       </c>
-      <c r="C15" s="141">
+      <c r="C15" s="156">
         <v>4</v>
       </c>
       <c r="D15" s="14">
@@ -6779,18 +6926,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="133">
+      <c r="I15" s="134">
         <f>(H15*D15+H16*D16+H17*D17)/C15</f>
         <v>0</v>
       </c>
       <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="203"/>
+      <c r="A16" s="103"/>
       <c r="B16" s="101" t="s">
         <v>171</v>
       </c>
-      <c r="C16" s="121"/>
+      <c r="C16" s="117"/>
       <c r="D16" s="3">
         <v>1</v>
       </c>
@@ -6805,15 +6952,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="144"/>
+      <c r="I16" s="135"/>
       <c r="K16" s="3"/>
     </row>
     <row r="17" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="188"/>
+      <c r="A17" s="204"/>
       <c r="B17" s="85" t="s">
         <v>172</v>
       </c>
-      <c r="C17" s="122"/>
+      <c r="C17" s="157"/>
       <c r="D17" s="22">
         <v>1</v>
       </c>
@@ -6828,17 +6975,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="134"/>
+      <c r="I17" s="136"/>
       <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="170" t="s">
+      <c r="A18" s="145" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="172">
+      <c r="C18" s="104">
         <v>3</v>
       </c>
       <c r="D18" s="14">
@@ -6855,18 +7002,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18" s="133">
+      <c r="I18" s="134">
         <f>(H18*D18+H19*D19)/C18</f>
         <v>0</v>
       </c>
       <c r="K18" s="3"/>
     </row>
     <row r="19" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="171"/>
+      <c r="A19" s="146"/>
       <c r="B19" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="173"/>
+      <c r="C19" s="147"/>
       <c r="D19" s="22">
         <v>1</v>
       </c>
@@ -6881,17 +7028,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="134"/>
+      <c r="I19" s="136"/>
       <c r="K19" s="3"/>
     </row>
     <row r="20" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="181" t="s">
+      <c r="A20" s="148" t="s">
         <v>38</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="C20" s="141">
+      <c r="C20" s="156">
         <v>4</v>
       </c>
       <c r="D20" s="14">
@@ -6908,18 +7055,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="133">
+      <c r="I20" s="134">
         <f>(H20*D20+H21*D21+H22*D22+H23*D23+H24*D24)/C20</f>
         <v>0</v>
       </c>
       <c r="K20" s="3"/>
     </row>
     <row r="21" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="182"/>
+      <c r="A21" s="149"/>
       <c r="B21" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="121"/>
+      <c r="C21" s="117"/>
       <c r="D21" s="3">
         <v>1</v>
       </c>
@@ -6934,15 +7081,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I21" s="144"/>
+      <c r="I21" s="135"/>
       <c r="K21" s="3"/>
     </row>
     <row r="22" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="182"/>
+      <c r="A22" s="149"/>
       <c r="B22" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="121"/>
+      <c r="C22" s="117"/>
       <c r="D22" s="3">
         <v>1</v>
       </c>
@@ -6957,15 +7104,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="144"/>
+      <c r="I22" s="135"/>
       <c r="K22" s="3"/>
     </row>
     <row r="23" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="182"/>
+      <c r="A23" s="149"/>
       <c r="B23" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="121"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="3">
         <v>1</v>
       </c>
@@ -6980,15 +7127,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I23" s="144"/>
+      <c r="I23" s="135"/>
       <c r="K23" s="3"/>
     </row>
     <row r="24" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="183"/>
+      <c r="A24" s="150"/>
       <c r="B24" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="122"/>
+      <c r="C24" s="157"/>
       <c r="D24" s="22">
         <v>0.5</v>
       </c>
@@ -7003,7 +7150,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I24" s="134"/>
+      <c r="I24" s="136"/>
       <c r="K24" s="3"/>
     </row>
     <row r="25" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -7037,26 +7184,26 @@
       <c r="K25" s="3"/>
     </row>
     <row r="26" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="184" t="s">
+      <c r="A26" s="140" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="185"/>
-      <c r="C26" s="184">
+      <c r="B26" s="141"/>
+      <c r="C26" s="140">
         <f>SUM(C2:C25)</f>
         <v>30</v>
       </c>
-      <c r="D26" s="186"/>
-      <c r="E26" s="149">
+      <c r="D26" s="142"/>
+      <c r="E26" s="123">
         <f>(I2*C2+I6*C6+I10*C10+I12*C12+I15*C15+I18*C18+I20*C20+I25*C25)/C26</f>
         <v>0</v>
       </c>
-      <c r="F26" s="150"/>
-      <c r="G26" s="150"/>
-      <c r="H26" s="157" t="str">
+      <c r="F26" s="124"/>
+      <c r="G26" s="124"/>
+      <c r="H26" s="143" t="str">
         <f>IF(OR(I2&lt;10,I6&lt;10,I10&lt;10,I12&lt;10,I15&lt;10,I18&lt;10,I20&lt;10,I25&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I26" s="158"/>
+      <c r="I26" s="144"/>
       <c r="K26" s="3"/>
     </row>
     <row r="27" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -7073,21 +7220,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="I2:I5"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="I12:I14"/>
-    <mergeCell ref="I6:I9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="C6:C9"/>
     <mergeCell ref="I15:I17"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="C26:D26"/>
@@ -7101,6 +7233,21 @@
     <mergeCell ref="A20:A24"/>
     <mergeCell ref="C20:C24"/>
     <mergeCell ref="I20:I24"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="I6:I9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="I2:I5"/>
   </mergeCells>
   <conditionalFormatting sqref="H26">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -7148,19 +7295,19 @@
       <c r="B1" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="200" t="s">
+      <c r="C1" s="206" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="201"/>
-      <c r="E1" s="149" t="s">
+      <c r="D1" s="207"/>
+      <c r="E1" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="150"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="149" t="s">
+      <c r="F1" s="124"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="123" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="151"/>
+      <c r="I1" s="125"/>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="86" t="s">
@@ -7192,26 +7339,26 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="143" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="157">
+      <c r="B3" s="144"/>
+      <c r="C3" s="143">
         <f>SUM(C2:C2)</f>
         <v>30</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="149">
+      <c r="D3" s="144"/>
+      <c r="E3" s="123">
         <f>(I2*C2)/C3</f>
         <v>0</v>
       </c>
-      <c r="F3" s="150"/>
-      <c r="G3" s="151"/>
-      <c r="H3" s="157" t="str">
+      <c r="F3" s="124"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="143" t="str">
         <f>IF(OR(I2&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I3" s="158"/>
+      <c r="I3" s="144"/>
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -7594,31 +7741,31 @@
       <c r="B1" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="212" t="s">
+      <c r="C1" s="216" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="213"/>
-      <c r="E1" s="149" t="s">
+      <c r="D1" s="217"/>
+      <c r="E1" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="150"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="214" t="s">
+      <c r="F1" s="124"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="218" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="193"/>
+      <c r="I1" s="203"/>
     </row>
     <row r="2" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="109" t="s">
+      <c r="A2" s="126" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="205" t="s">
+      <c r="B2" s="129" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="114">
+      <c r="C2" s="131">
         <v>8</v>
       </c>
-      <c r="D2" s="124">
+      <c r="D2" s="151">
         <v>4</v>
       </c>
       <c r="E2" s="23" t="s">
@@ -7628,21 +7775,21 @@
         <v>0.2</v>
       </c>
       <c r="G2" s="97"/>
-      <c r="H2" s="135">
+      <c r="H2" s="118">
         <f>G2*F2+G3*F3+G4*F4+G5*F5+G6*F6</f>
         <v>0</v>
       </c>
-      <c r="I2" s="133">
+      <c r="I2" s="134">
         <f>(H2*D2+H7*D7+H8*D8)/C2</f>
         <v>0</v>
       </c>
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="110"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="125"/>
+      <c r="A3" s="127"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="107"/>
       <c r="E3" s="11" t="s">
         <v>124</v>
       </c>
@@ -7650,15 +7797,15 @@
         <v>0.2</v>
       </c>
       <c r="G3" s="93"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="144"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="135"/>
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="110"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="115"/>
-      <c r="D4" s="125"/>
+      <c r="A4" s="127"/>
+      <c r="B4" s="130"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="107"/>
       <c r="E4" s="11" t="s">
         <v>104</v>
       </c>
@@ -7666,15 +7813,15 @@
         <v>0.2</v>
       </c>
       <c r="G4" s="93"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="144"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="135"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="110"/>
-      <c r="B5" s="117"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="125"/>
+      <c r="A5" s="127"/>
+      <c r="B5" s="130"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="107"/>
       <c r="E5" s="11" t="s">
         <v>31</v>
       </c>
@@ -7682,15 +7829,15 @@
         <v>0.2</v>
       </c>
       <c r="G5" s="93"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="144"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="135"/>
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="110"/>
-      <c r="B6" s="117"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="125"/>
+      <c r="A6" s="127"/>
+      <c r="B6" s="130"/>
+      <c r="C6" s="132"/>
+      <c r="D6" s="107"/>
       <c r="E6" s="11" t="s">
         <v>106</v>
       </c>
@@ -7698,16 +7845,16 @@
         <v>0.2</v>
       </c>
       <c r="G6" s="93"/>
-      <c r="H6" s="127"/>
-      <c r="I6" s="144"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="135"/>
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="110"/>
+      <c r="A7" s="127"/>
       <c r="B7" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="115"/>
+      <c r="C7" s="132"/>
       <c r="D7" s="3">
         <v>2</v>
       </c>
@@ -7722,14 +7869,14 @@
         <f t="shared" ref="H7:H16" si="0">G7*F7</f>
         <v>0</v>
       </c>
-      <c r="I7" s="144"/>
+      <c r="I7" s="135"/>
     </row>
     <row r="8" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="111"/>
+      <c r="A8" s="128"/>
       <c r="B8" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="115"/>
+      <c r="C8" s="132"/>
       <c r="D8" s="3">
         <v>2</v>
       </c>
@@ -7744,16 +7891,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="144"/>
+      <c r="I8" s="135"/>
     </row>
     <row r="9" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="120" t="s">
         <v>142</v>
       </c>
       <c r="B9" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="141">
+      <c r="C9" s="156">
         <v>6</v>
       </c>
       <c r="D9" s="19">
@@ -7770,17 +7917,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="133">
+      <c r="I9" s="134">
         <f>(H9*D9+H10*D10)/C9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="119"/>
+      <c r="A10" s="201"/>
       <c r="B10" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="C10" s="122"/>
+      <c r="C10" s="157"/>
       <c r="D10" s="21">
         <v>3</v>
       </c>
@@ -7795,17 +7942,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="134"/>
+      <c r="I10" s="136"/>
       <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="159" t="s">
+      <c r="A11" s="138" t="s">
         <v>78</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="C11" s="141">
+      <c r="C11" s="156">
         <v>4</v>
       </c>
       <c r="D11" s="19">
@@ -7822,18 +7969,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="133">
+      <c r="I11" s="134">
         <f>(H11*D11+H12*D12)/C11</f>
         <v>0</v>
       </c>
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="160"/>
+      <c r="A12" s="139"/>
       <c r="B12" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="121"/>
+      <c r="C12" s="117"/>
       <c r="D12" s="20">
         <v>2</v>
       </c>
@@ -7848,17 +7995,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="144"/>
+      <c r="I12" s="135"/>
       <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="181" t="s">
+      <c r="A13" s="148" t="s">
         <v>79</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="141">
+      <c r="C13" s="156">
         <v>8</v>
       </c>
       <c r="D13" s="19">
@@ -7875,18 +8022,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="133">
+      <c r="I13" s="134">
         <f>(H13*D13+H14*D14+H15*D15)/C13</f>
         <v>0</v>
       </c>
       <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="182"/>
+      <c r="A14" s="149"/>
       <c r="B14" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="121"/>
+      <c r="C14" s="117"/>
       <c r="D14" s="20">
         <v>2</v>
       </c>
@@ -7901,15 +8048,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="144"/>
+      <c r="I14" s="135"/>
       <c r="K14" s="3"/>
     </row>
     <row r="15" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="183"/>
+      <c r="A15" s="150"/>
       <c r="B15" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="122"/>
+      <c r="C15" s="157"/>
       <c r="D15" s="22">
         <v>3</v>
       </c>
@@ -7924,7 +8071,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="134"/>
+      <c r="I15" s="136"/>
       <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -7958,26 +8105,26 @@
       <c r="K16" s="3"/>
     </row>
     <row r="17" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="208" t="s">
+      <c r="A17" s="219" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="209"/>
-      <c r="C17" s="210">
+      <c r="B17" s="220"/>
+      <c r="C17" s="221">
         <f>SUM(C2:C16)</f>
         <v>30</v>
       </c>
-      <c r="D17" s="211"/>
-      <c r="E17" s="149">
+      <c r="D17" s="222"/>
+      <c r="E17" s="123">
         <f>(I2*C2+I9*C9+I11*C11+I13*C13+I16*C16)/C17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="150"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="157" t="str">
+      <c r="F17" s="124"/>
+      <c r="G17" s="124"/>
+      <c r="H17" s="143" t="str">
         <f>IF(OR(I2&lt;10,I9&lt;10,I11&lt;10,I13&lt;10,I16&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I17" s="158"/>
+      <c r="I17" s="144"/>
       <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -7994,6 +8141,19 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C9:C10"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:I1"/>
@@ -8003,19 +8163,6 @@
     <mergeCell ref="D2:D6"/>
     <mergeCell ref="H2:H6"/>
     <mergeCell ref="I2:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="I13:I15"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="H17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="H17">
     <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
@@ -8063,28 +8210,28 @@
       <c r="B1" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="220" t="s">
+      <c r="C1" s="223" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="221"/>
-      <c r="E1" s="192" t="s">
+      <c r="D1" s="224"/>
+      <c r="E1" s="202" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="214"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="214" t="s">
+      <c r="F1" s="218"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="218" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="193"/>
+      <c r="I1" s="203"/>
     </row>
     <row r="2" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="109" t="s">
+      <c r="A2" s="126" t="s">
         <v>81</v>
       </c>
       <c r="B2" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="114">
+      <c r="C2" s="131">
         <v>4</v>
       </c>
       <c r="D2" s="14">
@@ -8101,18 +8248,18 @@
         <f t="shared" ref="H2:H7" si="0">G2*F2</f>
         <v>0</v>
       </c>
-      <c r="I2" s="133">
+      <c r="I2" s="134">
         <f>(H2*D2+H3*D3)/C2</f>
         <v>0</v>
       </c>
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="111"/>
+      <c r="A3" s="128"/>
       <c r="B3" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="116"/>
+      <c r="C3" s="133"/>
       <c r="D3" s="22">
         <v>2</v>
       </c>
@@ -8127,16 +8274,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I3" s="134"/>
+      <c r="I3" s="136"/>
     </row>
     <row r="4" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="159" t="s">
+      <c r="A4" s="138" t="s">
         <v>78</v>
       </c>
       <c r="B4" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="131">
         <v>5</v>
       </c>
       <c r="D4" s="14">
@@ -8153,18 +8300,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I4" s="133">
+      <c r="I4" s="134">
         <f>(H4*D4+H5*D5+H6*D6+H7*D7)/C4</f>
         <v>0</v>
       </c>
       <c r="K4" s="3"/>
     </row>
     <row r="5" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="160"/>
+      <c r="A5" s="139"/>
       <c r="B5" s="65" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="115"/>
+      <c r="C5" s="132"/>
       <c r="D5" s="3">
         <v>1</v>
       </c>
@@ -8179,15 +8326,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="144"/>
+      <c r="I5" s="135"/>
       <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="160"/>
+      <c r="A6" s="139"/>
       <c r="B6" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="115"/>
+      <c r="C6" s="132"/>
       <c r="D6" s="3">
         <v>1</v>
       </c>
@@ -8202,15 +8349,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="144"/>
+      <c r="I6" s="135"/>
       <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="161"/>
+      <c r="A7" s="174"/>
       <c r="B7" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="116"/>
+      <c r="C7" s="133"/>
       <c r="D7" s="22">
         <v>1</v>
       </c>
@@ -8225,17 +8372,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="134"/>
+      <c r="I7" s="136"/>
       <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="218" t="s">
+      <c r="A8" s="225" t="s">
         <v>145</v>
       </c>
       <c r="B8" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="131">
         <v>3</v>
       </c>
       <c r="D8" s="14">
@@ -8252,18 +8399,18 @@
         <f>F8*G8</f>
         <v>0</v>
       </c>
-      <c r="I8" s="133">
+      <c r="I8" s="134">
         <f>(H8*D8+H9*D9)/C8</f>
         <v>0</v>
       </c>
       <c r="K8" s="3"/>
     </row>
     <row r="9" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="219"/>
+      <c r="A9" s="226"/>
       <c r="B9" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="116"/>
+      <c r="C9" s="133"/>
       <c r="D9" s="22">
         <v>2</v>
       </c>
@@ -8278,17 +8425,17 @@
         <f>F9*G9</f>
         <v>0</v>
       </c>
-      <c r="I9" s="134"/>
+      <c r="I9" s="136"/>
       <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="181" t="s">
+      <c r="A10" s="148" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="114">
+      <c r="C10" s="131">
         <v>8</v>
       </c>
       <c r="D10" s="14">
@@ -8305,18 +8452,18 @@
         <f t="shared" ref="H10:H15" si="1">G10*F10</f>
         <v>0</v>
       </c>
-      <c r="I10" s="133">
+      <c r="I10" s="134">
         <f>(H10*D10+H11*D11+H12*D12+H13*D13)/C10</f>
         <v>0</v>
       </c>
       <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="182"/>
+      <c r="A11" s="149"/>
       <c r="B11" s="70" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="115"/>
+      <c r="C11" s="132"/>
       <c r="D11" s="3">
         <v>1</v>
       </c>
@@ -8331,15 +8478,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I11" s="144"/>
+      <c r="I11" s="135"/>
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="182"/>
+      <c r="A12" s="149"/>
       <c r="B12" s="70" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="115"/>
+      <c r="C12" s="132"/>
       <c r="D12" s="3">
         <v>1</v>
       </c>
@@ -8354,15 +8501,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I12" s="144"/>
+      <c r="I12" s="135"/>
       <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="183"/>
+      <c r="A13" s="150"/>
       <c r="B13" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="116"/>
+      <c r="C13" s="133"/>
       <c r="D13" s="22">
         <v>3</v>
       </c>
@@ -8377,7 +8524,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I13" s="134"/>
+      <c r="I13" s="136"/>
       <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -8441,26 +8588,26 @@
       <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="215" t="s">
+      <c r="A16" s="227" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="216"/>
-      <c r="C16" s="215">
+      <c r="B16" s="228"/>
+      <c r="C16" s="227">
         <f>SUM(C2:C15)</f>
         <v>30</v>
       </c>
-      <c r="D16" s="217"/>
-      <c r="E16" s="149">
+      <c r="D16" s="229"/>
+      <c r="E16" s="123">
         <f>(I2*C2+I4*C4+I8*C8+I10*C10+I14*C14+I15*C15)/C16</f>
         <v>0</v>
       </c>
-      <c r="F16" s="150"/>
-      <c r="G16" s="150"/>
-      <c r="H16" s="157" t="str">
+      <c r="F16" s="124"/>
+      <c r="G16" s="124"/>
+      <c r="H16" s="143" t="str">
         <f>IF(OR(I2&lt;10,I4&lt;10,I8&lt;10,I10&lt;10,I14&lt;10,I15&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I16" s="158"/>
+      <c r="I16" s="144"/>
       <c r="K16" s="3"/>
     </row>
     <row r="17" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -8477,18 +8624,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="I4:I7"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="A10:A13"/>
@@ -8496,6 +8631,18 @@
     <mergeCell ref="I10:I13"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="H16:I16"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="I4:I7"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="I2:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="H16">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">

--- a/polytech/StTableur_Polytech_Lyon_Info.xlsx
+++ b/polytech/StTableur_Polytech_Lyon_Info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\__julien__\Ecole\Polytech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E627538-29D4-449B-8109-EECC90A7DE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2428711-F102-4FF1-9374-F05CC7E2137C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2166B340-63E7-40DE-94EE-C7BDCE76DCA3}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="188">
   <si>
     <t>Il y a un onglet par semestre pour les FISE et pour les FISA.</t>
   </si>
@@ -575,9 +575,6 @@
     <t>Développement portoflio compétences</t>
   </si>
   <si>
-    <t>Méctronique, Informatique pour la production</t>
-  </si>
-  <si>
     <t>Signal et Télécommunications</t>
   </si>
   <si>
@@ -647,7 +644,13 @@
     <t>CV</t>
   </si>
   <si>
-    <t>Compétences</t>
+    <t>Mécatronique, Informatique pour la production</t>
+  </si>
+  <si>
+    <t>Ecrit</t>
+  </si>
+  <si>
+    <t>Participation</t>
   </si>
 </sst>
 </file>
@@ -1479,7 +1482,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="230">
+  <cellXfs count="232">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1784,348 +1787,366 @@
     <xf numFmtId="0" fontId="14" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2135,37 +2156,25 @@
     <xf numFmtId="4" fontId="16" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2831,110 +2840,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
     </row>
     <row r="2" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="173" t="s">
+      <c r="A2" s="105" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
     </row>
     <row r="3" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="167" t="s">
+      <c r="A3" s="103" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="167"/>
-      <c r="C3" s="167"/>
-      <c r="D3" s="167"/>
-      <c r="E3" s="167"/>
-      <c r="F3" s="167"/>
-      <c r="G3" s="167"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
     </row>
     <row r="4" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="168"/>
-      <c r="B4" s="168"/>
-      <c r="C4" s="168"/>
-      <c r="D4" s="168"/>
-      <c r="E4" s="168"/>
-      <c r="F4" s="168"/>
-      <c r="G4" s="168"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
     </row>
     <row r="5" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="167"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
-      <c r="F5" s="167"/>
-      <c r="G5" s="167"/>
+      <c r="A5" s="103" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
     </row>
     <row r="6" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="167" t="s">
-        <v>180</v>
-      </c>
-      <c r="B6" s="167"/>
-      <c r="C6" s="167"/>
-      <c r="D6" s="167"/>
-      <c r="E6" s="167"/>
-      <c r="F6" s="167"/>
-      <c r="G6" s="167"/>
+      <c r="A6" s="103" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
     </row>
     <row r="7" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="167" t="s">
+      <c r="A7" s="103" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="167"/>
-      <c r="C7" s="167"/>
-      <c r="D7" s="167"/>
-      <c r="E7" s="167"/>
-      <c r="F7" s="167"/>
-      <c r="G7" s="167"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
     </row>
     <row r="8" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="167" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="167"/>
-      <c r="C8" s="167"/>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="167"/>
+      <c r="A8" s="103" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="103"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
     </row>
     <row r="9" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="168"/>
-      <c r="B9" s="168"/>
-      <c r="C9" s="168"/>
-      <c r="D9" s="168"/>
-      <c r="E9" s="168"/>
-      <c r="F9" s="168"/>
-      <c r="G9" s="168"/>
+      <c r="A9" s="106"/>
+      <c r="B9" s="106"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="106"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="106"/>
     </row>
     <row r="10" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="170" t="s">
+      <c r="A10" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="170"/>
-      <c r="C10" s="170"/>
-      <c r="D10" s="170"/>
-      <c r="E10" s="170"/>
-      <c r="F10" s="170"/>
-      <c r="G10" s="170"/>
+      <c r="B10" s="108"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
     </row>
     <row r="11" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="42" t="s">
@@ -2976,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="77">
-        <f>IF(COUNTA(E13)=0,S8_FISE!E42,E13)</f>
+        <f>IF(COUNTA(E13)=0,S8_FISE!E43,E13)</f>
         <v>0</v>
       </c>
       <c r="F12" s="77">
@@ -3000,24 +3009,24 @@
       <c r="G13" s="92"/>
     </row>
     <row r="14" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="168"/>
-      <c r="B14" s="168"/>
-      <c r="C14" s="168"/>
-      <c r="D14" s="168"/>
-      <c r="E14" s="168"/>
-      <c r="F14" s="168"/>
-      <c r="G14" s="168"/>
+      <c r="A14" s="106"/>
+      <c r="B14" s="106"/>
+      <c r="C14" s="106"/>
+      <c r="D14" s="106"/>
+      <c r="E14" s="106"/>
+      <c r="F14" s="106"/>
+      <c r="G14" s="106"/>
     </row>
     <row r="15" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="171" t="s">
+      <c r="A15" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="171"/>
-      <c r="C15" s="171"/>
-      <c r="D15" s="171"/>
-      <c r="E15" s="171"/>
-      <c r="F15" s="171"/>
-      <c r="G15" s="171"/>
+      <c r="B15" s="109"/>
+      <c r="C15" s="109"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="109"/>
+      <c r="F15" s="109"/>
+      <c r="G15" s="109"/>
     </row>
     <row r="16" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42" t="s">
@@ -3071,24 +3080,24 @@
       <c r="G18" s="92"/>
     </row>
     <row r="19" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="168"/>
-      <c r="B19" s="168"/>
-      <c r="C19" s="168"/>
-      <c r="D19" s="168"/>
-      <c r="E19" s="168"/>
-      <c r="F19" s="168"/>
-      <c r="G19" s="168"/>
+      <c r="A19" s="106"/>
+      <c r="B19" s="106"/>
+      <c r="C19" s="106"/>
+      <c r="D19" s="106"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="106"/>
     </row>
     <row r="20" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="169" t="s">
+      <c r="A20" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="169"/>
-      <c r="C20" s="169"/>
-      <c r="D20" s="169"/>
-      <c r="E20" s="169"/>
-      <c r="F20" s="169"/>
-      <c r="G20" s="169"/>
+      <c r="B20" s="107"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="107"/>
     </row>
     <row r="21" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42" t="s">
@@ -3157,11 +3166,6 @@
     <row r="1048575" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A20:G20"/>
@@ -3171,6 +3175,11 @@
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <conditionalFormatting sqref="B22:G22">
     <cfRule type="cellIs" dxfId="39" priority="28" operator="equal">
@@ -3256,7 +3265,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="4" id="{0544457F-4531-4F9B-8236-88453F06CDCC}">
-            <xm:f>IF(COUNTA(E13)=0,S8_FISE!$H$42="Valide",E13&gt;=10)</xm:f>
+            <xm:f>IF(COUNTA(E13)=0,S8_FISE!$H$43="Valide",E13&gt;=10)</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3321,31 +3330,31 @@
       <c r="B1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="121" t="s">
+      <c r="C1" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="122"/>
-      <c r="E1" s="123" t="s">
+      <c r="D1" s="147"/>
+      <c r="E1" s="150" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="124"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="190" t="s">
+      <c r="F1" s="151"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="148" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="191"/>
+      <c r="I1" s="149"/>
     </row>
     <row r="2" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="199" t="s">
+      <c r="B2" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="131">
+      <c r="C2" s="115">
         <v>8</v>
       </c>
-      <c r="D2" s="151">
+      <c r="D2" s="125">
         <v>4</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -3356,7 +3365,7 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G2" s="93"/>
-      <c r="H2" s="118">
+      <c r="H2" s="136">
         <f>G2*F2+G3*F3+G4*F4+G5*F5+G6*F6+G7*F7</f>
         <v>0</v>
       </c>
@@ -3367,10 +3376,10 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="127"/>
-      <c r="B3" s="200"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="107"/>
+      <c r="A3" s="111"/>
+      <c r="B3" s="114"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="126"/>
       <c r="E3" s="11" t="s">
         <v>124</v>
       </c>
@@ -3379,15 +3388,15 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G3" s="93"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="135"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="145"/>
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="127"/>
-      <c r="B4" s="200"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="107"/>
+      <c r="A4" s="111"/>
+      <c r="B4" s="114"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="126"/>
       <c r="E4" s="11" t="s">
         <v>104</v>
       </c>
@@ -3396,15 +3405,15 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G4" s="93"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="135"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="145"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="127"/>
-      <c r="B5" s="200"/>
-      <c r="C5" s="132"/>
-      <c r="D5" s="107"/>
+      <c r="A5" s="111"/>
+      <c r="B5" s="114"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="126"/>
       <c r="E5" s="11" t="s">
         <v>31</v>
       </c>
@@ -3413,15 +3422,15 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G5" s="93"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="135"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="145"/>
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="127"/>
-      <c r="B6" s="200"/>
-      <c r="C6" s="132"/>
-      <c r="D6" s="107"/>
+      <c r="A6" s="111"/>
+      <c r="B6" s="114"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="126"/>
       <c r="E6" s="11" t="s">
         <v>106</v>
       </c>
@@ -3430,15 +3439,15 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G6" s="93"/>
-      <c r="H6" s="119"/>
-      <c r="I6" s="135"/>
+      <c r="H6" s="128"/>
+      <c r="I6" s="145"/>
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="127"/>
-      <c r="B7" s="200"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="107"/>
+      <c r="A7" s="111"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="126"/>
       <c r="E7" s="11" t="s">
         <v>122</v>
       </c>
@@ -3447,17 +3456,17 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G7" s="93"/>
-      <c r="H7" s="119"/>
-      <c r="I7" s="135"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="145"/>
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="127"/>
-      <c r="B8" s="130" t="s">
+      <c r="A8" s="111"/>
+      <c r="B8" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="132"/>
-      <c r="D8" s="107">
+      <c r="C8" s="116"/>
+      <c r="D8" s="126">
         <v>1</v>
       </c>
       <c r="E8" s="23" t="s">
@@ -3467,17 +3476,17 @@
         <v>0.1</v>
       </c>
       <c r="G8" s="94"/>
-      <c r="H8" s="119">
+      <c r="H8" s="128">
         <f>G8*F8+G9*F9</f>
         <v>0</v>
       </c>
-      <c r="I8" s="135"/>
+      <c r="I8" s="145"/>
     </row>
     <row r="9" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="127"/>
-      <c r="B9" s="130"/>
-      <c r="C9" s="132"/>
-      <c r="D9" s="107"/>
+      <c r="A9" s="111"/>
+      <c r="B9" s="118"/>
+      <c r="C9" s="116"/>
+      <c r="D9" s="126"/>
       <c r="E9" s="12" t="s">
         <v>102</v>
       </c>
@@ -3485,16 +3494,16 @@
         <v>0.9</v>
       </c>
       <c r="G9" s="95"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="135"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="145"/>
     </row>
     <row r="10" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="127"/>
-      <c r="B10" s="130" t="s">
+      <c r="A10" s="111"/>
+      <c r="B10" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="132"/>
-      <c r="D10" s="107">
+      <c r="C10" s="116"/>
+      <c r="D10" s="126">
         <v>3</v>
       </c>
       <c r="E10" s="16" t="s">
@@ -3504,17 +3513,17 @@
         <v>0.5</v>
       </c>
       <c r="G10" s="93"/>
-      <c r="H10" s="119">
+      <c r="H10" s="128">
         <f>G10*F10+G11*F11</f>
         <v>0</v>
       </c>
-      <c r="I10" s="135"/>
+      <c r="I10" s="145"/>
     </row>
     <row r="11" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="128"/>
-      <c r="B11" s="137"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="108"/>
+      <c r="A11" s="112"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="127"/>
       <c r="E11" s="17" t="s">
         <v>102</v>
       </c>
@@ -3522,20 +3531,20 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="96"/>
-      <c r="H11" s="164"/>
-      <c r="I11" s="136"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="135"/>
     </row>
     <row r="12" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="120" t="s">
+      <c r="A12" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="114" t="s">
+      <c r="B12" s="121" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="117">
+      <c r="C12" s="122">
         <v>5</v>
       </c>
-      <c r="D12" s="116">
+      <c r="D12" s="132">
         <v>4</v>
       </c>
       <c r="E12" s="16" t="s">
@@ -3545,7 +3554,7 @@
         <v>0.25</v>
       </c>
       <c r="G12" s="93"/>
-      <c r="H12" s="119">
+      <c r="H12" s="128">
         <f>G12*F12+G13*F13+G14*F14+G15*F15</f>
         <v>0</v>
       </c>
@@ -3555,10 +3564,10 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="120"/>
-      <c r="B13" s="114"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="116"/>
+      <c r="A13" s="119"/>
+      <c r="B13" s="121"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="132"/>
       <c r="E13" s="16" t="s">
         <v>89</v>
       </c>
@@ -3566,14 +3575,14 @@
         <v>0.25</v>
       </c>
       <c r="G13" s="93"/>
-      <c r="H13" s="119"/>
-      <c r="I13" s="135"/>
+      <c r="H13" s="128"/>
+      <c r="I13" s="145"/>
     </row>
     <row r="14" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="120"/>
-      <c r="B14" s="114"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="116"/>
+      <c r="A14" s="119"/>
+      <c r="B14" s="121"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="132"/>
       <c r="E14" s="16" t="s">
         <v>101</v>
       </c>
@@ -3581,14 +3590,14 @@
         <v>0.25</v>
       </c>
       <c r="G14" s="93"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="135"/>
+      <c r="H14" s="128"/>
+      <c r="I14" s="145"/>
     </row>
     <row r="15" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="120"/>
-      <c r="B15" s="114"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="116"/>
+      <c r="A15" s="119"/>
+      <c r="B15" s="121"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="132"/>
       <c r="E15" s="16" t="s">
         <v>102</v>
       </c>
@@ -3596,16 +3605,16 @@
         <v>0.25</v>
       </c>
       <c r="G15" s="93"/>
-      <c r="H15" s="119"/>
-      <c r="I15" s="135"/>
+      <c r="H15" s="128"/>
+      <c r="I15" s="145"/>
     </row>
     <row r="16" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="120"/>
-      <c r="B16" s="114" t="s">
+      <c r="A16" s="119"/>
+      <c r="B16" s="121" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="117"/>
-      <c r="D16" s="116">
+      <c r="C16" s="122"/>
+      <c r="D16" s="132">
         <v>1</v>
       </c>
       <c r="E16" s="15" t="s">
@@ -3615,17 +3624,17 @@
         <v>0.4</v>
       </c>
       <c r="G16" s="94"/>
-      <c r="H16" s="119">
+      <c r="H16" s="128">
         <f>G16*F16+G17*F17</f>
         <v>0</v>
       </c>
-      <c r="I16" s="135"/>
+      <c r="I16" s="145"/>
     </row>
     <row r="17" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="201"/>
-      <c r="B17" s="162"/>
-      <c r="C17" s="157"/>
-      <c r="D17" s="163"/>
+      <c r="A17" s="120"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="133"/>
       <c r="E17" s="17" t="s">
         <v>102</v>
       </c>
@@ -3633,20 +3642,20 @@
         <v>0.6</v>
       </c>
       <c r="G17" s="95"/>
-      <c r="H17" s="164"/>
-      <c r="I17" s="136"/>
+      <c r="H17" s="131"/>
+      <c r="I17" s="135"/>
     </row>
     <row r="18" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="138" t="s">
+      <c r="A18" s="160" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="165" t="s">
+      <c r="B18" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="156">
+      <c r="C18" s="142">
         <v>5</v>
       </c>
-      <c r="D18" s="115">
+      <c r="D18" s="144">
         <v>1</v>
       </c>
       <c r="E18" s="15" t="s">
@@ -3656,7 +3665,7 @@
         <v>0.6</v>
       </c>
       <c r="G18" s="97"/>
-      <c r="H18" s="118">
+      <c r="H18" s="136">
         <f>G18*F18+G19*F19</f>
         <v>0</v>
       </c>
@@ -3666,10 +3675,10 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="139"/>
-      <c r="B19" s="111"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="116"/>
+      <c r="A19" s="161"/>
+      <c r="B19" s="154"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="132"/>
       <c r="E19" s="16" t="s">
         <v>95</v>
       </c>
@@ -3677,16 +3686,16 @@
         <v>0.4</v>
       </c>
       <c r="G19" s="93"/>
-      <c r="H19" s="119"/>
-      <c r="I19" s="135"/>
+      <c r="H19" s="128"/>
+      <c r="I19" s="145"/>
     </row>
     <row r="20" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="139"/>
-      <c r="B20" s="111" t="s">
+      <c r="A20" s="161"/>
+      <c r="B20" s="154" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="117"/>
-      <c r="D20" s="116">
+      <c r="C20" s="122"/>
+      <c r="D20" s="132">
         <v>2</v>
       </c>
       <c r="E20" s="15" t="s">
@@ -3696,17 +3705,17 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="94"/>
-      <c r="H20" s="119">
+      <c r="H20" s="128">
         <f>G20*F20+G21*F21</f>
         <v>0</v>
       </c>
-      <c r="I20" s="135"/>
+      <c r="I20" s="145"/>
     </row>
     <row r="21" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="139"/>
-      <c r="B21" s="111"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="116"/>
+      <c r="A21" s="161"/>
+      <c r="B21" s="154"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="132"/>
       <c r="E21" s="17" t="s">
         <v>102</v>
       </c>
@@ -3714,16 +3723,16 @@
         <v>0.5</v>
       </c>
       <c r="G21" s="95"/>
-      <c r="H21" s="119"/>
-      <c r="I21" s="135"/>
+      <c r="H21" s="128"/>
+      <c r="I21" s="145"/>
     </row>
     <row r="22" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="139"/>
-      <c r="B22" s="111" t="s">
+      <c r="A22" s="161"/>
+      <c r="B22" s="154" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="117"/>
-      <c r="D22" s="116">
+      <c r="C22" s="122"/>
+      <c r="D22" s="132">
         <v>2</v>
       </c>
       <c r="E22" s="16" t="s">
@@ -3733,17 +3742,17 @@
         <v>0.4</v>
       </c>
       <c r="G22" s="93"/>
-      <c r="H22" s="119">
+      <c r="H22" s="128">
         <f>G22*F22+G23*F23+G24*F24</f>
         <v>0</v>
       </c>
-      <c r="I22" s="135"/>
+      <c r="I22" s="145"/>
     </row>
     <row r="23" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="139"/>
-      <c r="B23" s="111"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="116"/>
+      <c r="A23" s="161"/>
+      <c r="B23" s="154"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="132"/>
       <c r="E23" s="16" t="s">
         <v>98</v>
       </c>
@@ -3751,14 +3760,14 @@
         <v>0.3</v>
       </c>
       <c r="G23" s="93"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="135"/>
+      <c r="H23" s="128"/>
+      <c r="I23" s="145"/>
     </row>
     <row r="24" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="174"/>
-      <c r="B24" s="112"/>
-      <c r="C24" s="157"/>
-      <c r="D24" s="163"/>
+      <c r="A24" s="162"/>
+      <c r="B24" s="155"/>
+      <c r="C24" s="123"/>
+      <c r="D24" s="133"/>
       <c r="E24" s="17" t="s">
         <v>99</v>
       </c>
@@ -3766,20 +3775,20 @@
         <v>0.3</v>
       </c>
       <c r="G24" s="96"/>
-      <c r="H24" s="164"/>
-      <c r="I24" s="136"/>
+      <c r="H24" s="131"/>
+      <c r="I24" s="135"/>
     </row>
     <row r="25" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="183" t="s">
+      <c r="A25" s="175" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="186" t="s">
+      <c r="B25" s="178" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="105">
+      <c r="C25" s="143">
         <v>4</v>
       </c>
-      <c r="D25" s="107">
+      <c r="D25" s="126">
         <v>2</v>
       </c>
       <c r="E25" s="16" t="s">
@@ -3789,7 +3798,7 @@
         <v>0.4</v>
       </c>
       <c r="G25" s="93"/>
-      <c r="H25" s="119">
+      <c r="H25" s="128">
         <f>F25*G25+F26*G26</f>
         <v>0</v>
       </c>
@@ -3799,10 +3808,10 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="184"/>
-      <c r="B26" s="187"/>
-      <c r="C26" s="106"/>
-      <c r="D26" s="188"/>
+      <c r="A26" s="176"/>
+      <c r="B26" s="179"/>
+      <c r="C26" s="180"/>
+      <c r="D26" s="181"/>
       <c r="E26" s="16" t="s">
         <v>102</v>
       </c>
@@ -3810,16 +3819,16 @@
         <v>0.6</v>
       </c>
       <c r="G26" s="93"/>
-      <c r="H26" s="119"/>
-      <c r="I26" s="135"/>
+      <c r="H26" s="128"/>
+      <c r="I26" s="145"/>
     </row>
     <row r="27" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="184"/>
-      <c r="B27" s="189" t="s">
+      <c r="A27" s="176"/>
+      <c r="B27" s="157" t="s">
         <v>127</v>
       </c>
-      <c r="C27" s="106"/>
-      <c r="D27" s="116">
+      <c r="C27" s="180"/>
+      <c r="D27" s="132">
         <v>2</v>
       </c>
       <c r="E27" s="15" t="s">
@@ -3829,17 +3838,17 @@
         <v>0.4</v>
       </c>
       <c r="G27" s="94"/>
-      <c r="H27" s="119">
+      <c r="H27" s="128">
         <f>F27*G27+F28*G28</f>
         <v>0</v>
       </c>
-      <c r="I27" s="135"/>
+      <c r="I27" s="145"/>
     </row>
     <row r="28" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="185"/>
-      <c r="B28" s="189"/>
-      <c r="C28" s="179"/>
-      <c r="D28" s="116"/>
+      <c r="A28" s="177"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="167"/>
+      <c r="D28" s="132"/>
       <c r="E28" s="17" t="s">
         <v>102</v>
       </c>
@@ -3847,17 +3856,17 @@
         <v>0.6</v>
       </c>
       <c r="G28" s="95"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="136"/>
+      <c r="H28" s="128"/>
+      <c r="I28" s="135"/>
     </row>
     <row r="29" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="145" t="s">
+      <c r="A29" s="171" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="104">
+      <c r="C29" s="173">
         <v>3</v>
       </c>
       <c r="D29" s="14">
@@ -3880,11 +3889,11 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="146"/>
+      <c r="A30" s="172"/>
       <c r="B30" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="147"/>
+      <c r="C30" s="174"/>
       <c r="D30" s="22">
         <v>1</v>
       </c>
@@ -3899,19 +3908,19 @@
         <f>G30*F30</f>
         <v>0</v>
       </c>
-      <c r="I30" s="136"/>
+      <c r="I30" s="135"/>
     </row>
     <row r="31" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="192" t="s">
+      <c r="A31" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="195" t="s">
+      <c r="B31" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="156">
+      <c r="C31" s="142">
         <v>4</v>
       </c>
-      <c r="D31" s="115">
+      <c r="D31" s="144">
         <v>2</v>
       </c>
       <c r="E31" s="16" t="s">
@@ -3921,7 +3930,7 @@
         <v>0.75</v>
       </c>
       <c r="G31" s="93"/>
-      <c r="H31" s="118">
+      <c r="H31" s="136">
         <f>G31*F31+G32*F32</f>
         <v>0</v>
       </c>
@@ -3931,10 +3940,10 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="193"/>
-      <c r="B32" s="196"/>
-      <c r="C32" s="117"/>
-      <c r="D32" s="116"/>
+      <c r="A32" s="138"/>
+      <c r="B32" s="141"/>
+      <c r="C32" s="122"/>
+      <c r="D32" s="132"/>
       <c r="E32" s="16" t="s">
         <v>148</v>
       </c>
@@ -3942,16 +3951,16 @@
         <v>0.25</v>
       </c>
       <c r="G32" s="93"/>
-      <c r="H32" s="119"/>
-      <c r="I32" s="135"/>
+      <c r="H32" s="128"/>
+      <c r="I32" s="145"/>
     </row>
     <row r="33" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="193"/>
-      <c r="B33" s="196" t="s">
+      <c r="A33" s="138"/>
+      <c r="B33" s="141" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="117"/>
-      <c r="D33" s="116">
+      <c r="C33" s="122"/>
+      <c r="D33" s="132">
         <v>1.5</v>
       </c>
       <c r="E33" s="15" t="s">
@@ -3961,17 +3970,17 @@
         <v>0.5</v>
       </c>
       <c r="G33" s="94"/>
-      <c r="H33" s="119">
+      <c r="H33" s="128">
         <f>G33*F33+G34*F34</f>
         <v>0</v>
       </c>
-      <c r="I33" s="135"/>
+      <c r="I33" s="145"/>
     </row>
     <row r="34" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="193"/>
-      <c r="B34" s="196"/>
-      <c r="C34" s="117"/>
-      <c r="D34" s="116"/>
+      <c r="A34" s="138"/>
+      <c r="B34" s="141"/>
+      <c r="C34" s="122"/>
+      <c r="D34" s="132"/>
       <c r="E34" s="17" t="s">
         <v>94</v>
       </c>
@@ -3979,15 +3988,15 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="95"/>
-      <c r="H34" s="119"/>
-      <c r="I34" s="135"/>
+      <c r="H34" s="128"/>
+      <c r="I34" s="145"/>
     </row>
     <row r="35" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="194"/>
+      <c r="A35" s="139"/>
       <c r="B35" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="105"/>
+      <c r="C35" s="143"/>
       <c r="D35" s="9">
         <v>0.5</v>
       </c>
@@ -4002,19 +4011,19 @@
         <f>G35*F35</f>
         <v>0</v>
       </c>
-      <c r="I35" s="136"/>
+      <c r="I35" s="135"/>
     </row>
     <row r="36" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="175" t="s">
+      <c r="A36" s="163" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="177" t="s">
+      <c r="B36" s="165" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="179">
-        <v>1</v>
-      </c>
-      <c r="D36" s="197">
+      <c r="C36" s="167">
+        <v>1</v>
+      </c>
+      <c r="D36" s="129">
         <v>1</v>
       </c>
       <c r="E36" s="15" t="s">
@@ -4024,7 +4033,7 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="97"/>
-      <c r="H36" s="118">
+      <c r="H36" s="136">
         <f>G36*F36+G37*F37</f>
         <v>0</v>
       </c>
@@ -4034,10 +4043,10 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="176"/>
-      <c r="B37" s="178"/>
-      <c r="C37" s="105"/>
-      <c r="D37" s="198"/>
+      <c r="A37" s="164"/>
+      <c r="B37" s="166"/>
+      <c r="C37" s="143"/>
+      <c r="D37" s="130"/>
       <c r="E37" s="17" t="s">
         <v>92</v>
       </c>
@@ -4045,30 +4054,30 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="96"/>
-      <c r="H37" s="164"/>
-      <c r="I37" s="136"/>
+      <c r="H37" s="131"/>
+      <c r="I37" s="135"/>
     </row>
     <row r="38" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="180" t="s">
+      <c r="A38" s="168" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="181"/>
-      <c r="C38" s="182">
+      <c r="B38" s="169"/>
+      <c r="C38" s="170">
         <f>SUM(C2:C36)</f>
         <v>30</v>
       </c>
-      <c r="D38" s="180"/>
-      <c r="E38" s="123">
+      <c r="D38" s="168"/>
+      <c r="E38" s="150">
         <f>(I2*C2+I12*C12+I18*C18+I25*C25+I29*C29+I31*C31+I36*C36)/C38</f>
         <v>0</v>
       </c>
-      <c r="F38" s="124"/>
-      <c r="G38" s="124"/>
-      <c r="H38" s="143" t="str">
+      <c r="F38" s="151"/>
+      <c r="G38" s="151"/>
+      <c r="H38" s="158" t="str">
         <f>IF(OR(I2&lt;10,I12&lt;10,I18&lt;10,I25&lt;10,I29&lt;10,I31&lt;10,I36&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I38" s="144"/>
+      <c r="I38" s="159"/>
     </row>
     <row r="39" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H39" s="62"/>
@@ -4076,36 +4085,27 @@
     </row>
   </sheetData>
   <mergeCells count="67">
-    <mergeCell ref="A2:A11"/>
-    <mergeCell ref="B2:B7"/>
-    <mergeCell ref="C2:C11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="C12:C17"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D2:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="D12:D15"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="I31:I35"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="I25:I28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="I18:I24"/>
+    <mergeCell ref="B20:B21"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="E1:G1"/>
@@ -4122,27 +4122,36 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="I2:I11"/>
     <mergeCell ref="H2:H7"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="I18:I24"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="I25:I28"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="I31:I35"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="D2:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="A2:A11"/>
+    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="C2:C11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="C12:C17"/>
+    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <conditionalFormatting sqref="H38">
     <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
@@ -4190,31 +4199,31 @@
       <c r="B1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="121" t="s">
+      <c r="C1" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="122"/>
-      <c r="E1" s="123" t="s">
+      <c r="D1" s="147"/>
+      <c r="E1" s="150" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="124"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="202" t="s">
+      <c r="F1" s="151"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="193" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="203"/>
+      <c r="I1" s="194"/>
     </row>
     <row r="2" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="110" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="199" t="s">
+      <c r="B2" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="131">
+      <c r="C2" s="115">
         <v>7</v>
       </c>
-      <c r="D2" s="151">
+      <c r="D2" s="125">
         <v>2</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -4224,7 +4233,7 @@
         <v>0.5</v>
       </c>
       <c r="G2" s="93"/>
-      <c r="H2" s="118">
+      <c r="H2" s="136">
         <f>G2*F2+G3*F3</f>
         <v>0</v>
       </c>
@@ -4235,10 +4244,10 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="127"/>
-      <c r="B3" s="200"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="107"/>
+      <c r="A3" s="111"/>
+      <c r="B3" s="114"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="126"/>
       <c r="E3" s="11" t="s">
         <v>102</v>
       </c>
@@ -4246,17 +4255,17 @@
         <v>0.5</v>
       </c>
       <c r="G3" s="93"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="135"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="145"/>
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="127"/>
-      <c r="B4" s="130" t="s">
+      <c r="A4" s="111"/>
+      <c r="B4" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="132"/>
-      <c r="D4" s="107">
+      <c r="C4" s="116"/>
+      <c r="D4" s="126">
         <v>2</v>
       </c>
       <c r="E4" s="23" t="s">
@@ -4266,17 +4275,17 @@
         <v>0.5</v>
       </c>
       <c r="G4" s="94"/>
-      <c r="H4" s="119">
+      <c r="H4" s="128">
         <f>G4*F4+G5*F5</f>
         <v>0</v>
       </c>
-      <c r="I4" s="135"/>
+      <c r="I4" s="145"/>
     </row>
     <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="127"/>
-      <c r="B5" s="130"/>
-      <c r="C5" s="132"/>
-      <c r="D5" s="107"/>
+      <c r="A5" s="111"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="126"/>
       <c r="E5" s="12" t="s">
         <v>99</v>
       </c>
@@ -4284,16 +4293,16 @@
         <v>0.5</v>
       </c>
       <c r="G5" s="95"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="135"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="145"/>
     </row>
     <row r="6" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="127"/>
-      <c r="B6" s="130" t="s">
+      <c r="A6" s="111"/>
+      <c r="B6" s="118" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="132"/>
-      <c r="D6" s="107">
+      <c r="C6" s="116"/>
+      <c r="D6" s="126">
         <v>3</v>
       </c>
       <c r="E6" s="16" t="s">
@@ -4303,17 +4312,17 @@
         <v>0.33333333333333337</v>
       </c>
       <c r="G6" s="93"/>
-      <c r="H6" s="119">
+      <c r="H6" s="128">
         <f>G6*F6+G7*F7</f>
         <v>0</v>
       </c>
-      <c r="I6" s="135"/>
+      <c r="I6" s="145"/>
     </row>
     <row r="7" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="128"/>
-      <c r="B7" s="137"/>
-      <c r="C7" s="133"/>
-      <c r="D7" s="108"/>
+      <c r="A7" s="112"/>
+      <c r="B7" s="124"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="127"/>
       <c r="E7" s="17" t="s">
         <v>102</v>
       </c>
@@ -4321,20 +4330,20 @@
         <v>0.66666666666666674</v>
       </c>
       <c r="G7" s="96"/>
-      <c r="H7" s="164"/>
-      <c r="I7" s="136"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="135"/>
     </row>
     <row r="8" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="120" t="s">
+      <c r="A8" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="114" t="s">
+      <c r="B8" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="117">
+      <c r="C8" s="122">
         <v>3</v>
       </c>
-      <c r="D8" s="116">
+      <c r="D8" s="132">
         <v>2</v>
       </c>
       <c r="E8" s="15" t="s">
@@ -4344,7 +4353,7 @@
         <v>0.4</v>
       </c>
       <c r="G8" s="94"/>
-      <c r="H8" s="119">
+      <c r="H8" s="128">
         <f>G8*F8+G9*F9</f>
         <v>0</v>
       </c>
@@ -4354,10 +4363,10 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="120"/>
-      <c r="B9" s="114"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="116"/>
+      <c r="A9" s="119"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="122"/>
+      <c r="D9" s="132"/>
       <c r="E9" s="17" t="s">
         <v>102</v>
       </c>
@@ -4365,15 +4374,15 @@
         <v>0.6</v>
       </c>
       <c r="G9" s="95"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="135"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="145"/>
     </row>
     <row r="10" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="120"/>
+      <c r="A10" s="119"/>
       <c r="B10" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="C10" s="117"/>
+      <c r="C10" s="122"/>
       <c r="D10" s="20">
         <v>1</v>
       </c>
@@ -4388,20 +4397,20 @@
         <f>G10*F10</f>
         <v>0</v>
       </c>
-      <c r="I10" s="135"/>
+      <c r="I10" s="145"/>
       <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="138" t="s">
+      <c r="A11" s="160" t="s">
         <v>134</v>
       </c>
-      <c r="B11" s="165" t="s">
+      <c r="B11" s="153" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="156">
+      <c r="C11" s="142">
         <v>5</v>
       </c>
-      <c r="D11" s="115">
+      <c r="D11" s="144">
         <v>2</v>
       </c>
       <c r="E11" s="15" t="s">
@@ -4411,7 +4420,7 @@
         <v>0.4</v>
       </c>
       <c r="G11" s="97"/>
-      <c r="H11" s="118">
+      <c r="H11" s="136">
         <f>G11*F11+G12*F12+G13*F13+G14*F14</f>
         <v>0</v>
       </c>
@@ -4422,10 +4431,10 @@
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="139"/>
-      <c r="B12" s="111"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="116"/>
+      <c r="A12" s="161"/>
+      <c r="B12" s="154"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="132"/>
       <c r="E12" s="16" t="s">
         <v>114</v>
       </c>
@@ -4433,15 +4442,15 @@
         <v>0.2</v>
       </c>
       <c r="G12" s="93"/>
-      <c r="H12" s="119"/>
-      <c r="I12" s="135"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="145"/>
       <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="139"/>
-      <c r="B13" s="111"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="116"/>
+      <c r="A13" s="161"/>
+      <c r="B13" s="154"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="132"/>
       <c r="E13" s="16" t="s">
         <v>115</v>
       </c>
@@ -4449,15 +4458,15 @@
         <v>0.2</v>
       </c>
       <c r="G13" s="93"/>
-      <c r="H13" s="119"/>
-      <c r="I13" s="135"/>
+      <c r="H13" s="128"/>
+      <c r="I13" s="145"/>
       <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="139"/>
-      <c r="B14" s="111"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="116"/>
+      <c r="A14" s="161"/>
+      <c r="B14" s="154"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="132"/>
       <c r="E14" s="16" t="s">
         <v>116</v>
       </c>
@@ -4465,17 +4474,17 @@
         <v>0.2</v>
       </c>
       <c r="G14" s="93"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="135"/>
+      <c r="H14" s="128"/>
+      <c r="I14" s="145"/>
       <c r="K14" s="3"/>
     </row>
     <row r="15" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="139"/>
-      <c r="B15" s="111" t="s">
+      <c r="A15" s="161"/>
+      <c r="B15" s="154" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="117"/>
-      <c r="D15" s="116">
+      <c r="C15" s="122"/>
+      <c r="D15" s="132">
         <v>1</v>
       </c>
       <c r="E15" s="15" t="s">
@@ -4485,18 +4494,18 @@
         <v>0.1</v>
       </c>
       <c r="G15" s="94"/>
-      <c r="H15" s="119">
+      <c r="H15" s="128">
         <f>G15*F15+G16*F16+G17*F17</f>
         <v>0</v>
       </c>
-      <c r="I15" s="135"/>
+      <c r="I15" s="145"/>
       <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="139"/>
-      <c r="B16" s="111"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="116"/>
+      <c r="A16" s="161"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="132"/>
       <c r="E16" s="16" t="s">
         <v>89</v>
       </c>
@@ -4504,15 +4513,15 @@
         <v>0.3</v>
       </c>
       <c r="G16" s="98"/>
-      <c r="H16" s="119"/>
-      <c r="I16" s="135"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="145"/>
       <c r="K16" s="3"/>
     </row>
     <row r="17" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="139"/>
-      <c r="B17" s="111"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="116"/>
+      <c r="A17" s="161"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="132"/>
       <c r="E17" s="17" t="s">
         <v>118</v>
       </c>
@@ -4520,17 +4529,17 @@
         <v>0.6</v>
       </c>
       <c r="G17" s="95"/>
-      <c r="H17" s="119"/>
-      <c r="I17" s="135"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="145"/>
       <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="139"/>
-      <c r="B18" s="111" t="s">
+      <c r="A18" s="161"/>
+      <c r="B18" s="154" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="117"/>
-      <c r="D18" s="116">
+      <c r="C18" s="122"/>
+      <c r="D18" s="132">
         <v>1</v>
       </c>
       <c r="E18" s="15" t="s">
@@ -4540,18 +4549,18 @@
         <v>0.2</v>
       </c>
       <c r="G18" s="94"/>
-      <c r="H18" s="119">
+      <c r="H18" s="128">
         <f>G18*F18+G19*F19+G20*F20</f>
         <v>0</v>
       </c>
-      <c r="I18" s="135"/>
+      <c r="I18" s="145"/>
       <c r="K18" s="3"/>
     </row>
     <row r="19" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="139"/>
-      <c r="B19" s="111"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="116"/>
+      <c r="A19" s="161"/>
+      <c r="B19" s="154"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="132"/>
       <c r="E19" s="16" t="s">
         <v>98</v>
       </c>
@@ -4559,15 +4568,15 @@
         <v>0.3</v>
       </c>
       <c r="G19" s="98"/>
-      <c r="H19" s="119"/>
-      <c r="I19" s="135"/>
+      <c r="H19" s="128"/>
+      <c r="I19" s="145"/>
       <c r="K19" s="3"/>
     </row>
     <row r="20" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="139"/>
-      <c r="B20" s="111"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="116"/>
+      <c r="A20" s="161"/>
+      <c r="B20" s="154"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="132"/>
       <c r="E20" s="17" t="s">
         <v>99</v>
       </c>
@@ -4575,17 +4584,17 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="95"/>
-      <c r="H20" s="119"/>
-      <c r="I20" s="135"/>
+      <c r="H20" s="128"/>
+      <c r="I20" s="145"/>
       <c r="K20" s="3"/>
     </row>
     <row r="21" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="139"/>
-      <c r="B21" s="111" t="s">
+      <c r="A21" s="161"/>
+      <c r="B21" s="154" t="s">
         <v>132</v>
       </c>
-      <c r="C21" s="117"/>
-      <c r="D21" s="116">
+      <c r="C21" s="122"/>
+      <c r="D21" s="132">
         <v>1</v>
       </c>
       <c r="E21" s="16" t="s">
@@ -4595,18 +4604,18 @@
         <v>0.2</v>
       </c>
       <c r="G21" s="93"/>
-      <c r="H21" s="119">
+      <c r="H21" s="128">
         <f>G21*F21+G22*F22+G23*F23</f>
         <v>0</v>
       </c>
-      <c r="I21" s="135"/>
+      <c r="I21" s="145"/>
       <c r="K21" s="3"/>
     </row>
     <row r="22" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="139"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="116"/>
+      <c r="A22" s="161"/>
+      <c r="B22" s="154"/>
+      <c r="C22" s="122"/>
+      <c r="D22" s="132"/>
       <c r="E22" s="16" t="s">
         <v>119</v>
       </c>
@@ -4614,15 +4623,15 @@
         <v>0.4</v>
       </c>
       <c r="G22" s="93"/>
-      <c r="H22" s="119"/>
-      <c r="I22" s="135"/>
+      <c r="H22" s="128"/>
+      <c r="I22" s="145"/>
       <c r="K22" s="3"/>
     </row>
     <row r="23" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="174"/>
-      <c r="B23" s="205"/>
-      <c r="C23" s="157"/>
-      <c r="D23" s="163"/>
+      <c r="A23" s="162"/>
+      <c r="B23" s="192"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="133"/>
       <c r="E23" s="17" t="s">
         <v>120</v>
       </c>
@@ -4630,21 +4639,21 @@
         <v>0.4</v>
       </c>
       <c r="G23" s="96"/>
-      <c r="H23" s="164"/>
-      <c r="I23" s="136"/>
+      <c r="H23" s="131"/>
+      <c r="I23" s="135"/>
       <c r="K23" s="3"/>
     </row>
     <row r="24" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="183" t="s">
+      <c r="A24" s="175" t="s">
         <v>137</v>
       </c>
-      <c r="B24" s="186" t="s">
+      <c r="B24" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="105">
+      <c r="C24" s="143">
         <v>6</v>
       </c>
-      <c r="D24" s="107">
+      <c r="D24" s="126">
         <v>3</v>
       </c>
       <c r="E24" s="16" t="s">
@@ -4654,21 +4663,21 @@
         <v>0.2</v>
       </c>
       <c r="G24" s="93"/>
-      <c r="H24" s="119">
+      <c r="H24" s="128">
         <f>F24*G24+F25*G25+F26*G26</f>
         <v>0</v>
       </c>
-      <c r="I24" s="135">
+      <c r="I24" s="145">
         <f>(H24*D24+H27*D27)/C24</f>
         <v>0</v>
       </c>
       <c r="K24" s="3"/>
     </row>
     <row r="25" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="183"/>
-      <c r="B25" s="186"/>
-      <c r="C25" s="105"/>
-      <c r="D25" s="107"/>
+      <c r="A25" s="175"/>
+      <c r="B25" s="178"/>
+      <c r="C25" s="143"/>
+      <c r="D25" s="126"/>
       <c r="E25" s="16" t="s">
         <v>146</v>
       </c>
@@ -4676,15 +4685,15 @@
         <v>0.4</v>
       </c>
       <c r="G25" s="93"/>
-      <c r="H25" s="119"/>
-      <c r="I25" s="135"/>
+      <c r="H25" s="128"/>
+      <c r="I25" s="145"/>
       <c r="K25" s="3"/>
     </row>
     <row r="26" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="184"/>
-      <c r="B26" s="187"/>
-      <c r="C26" s="106"/>
-      <c r="D26" s="188"/>
+      <c r="A26" s="176"/>
+      <c r="B26" s="179"/>
+      <c r="C26" s="180"/>
+      <c r="D26" s="181"/>
       <c r="E26" s="16" t="s">
         <v>102</v>
       </c>
@@ -4692,17 +4701,17 @@
         <v>0.4</v>
       </c>
       <c r="G26" s="93"/>
-      <c r="H26" s="119"/>
-      <c r="I26" s="135"/>
+      <c r="H26" s="128"/>
+      <c r="I26" s="145"/>
       <c r="K26" s="3"/>
     </row>
     <row r="27" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="184"/>
-      <c r="B27" s="189" t="s">
+      <c r="A27" s="176"/>
+      <c r="B27" s="157" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="106"/>
-      <c r="D27" s="116">
+      <c r="C27" s="180"/>
+      <c r="D27" s="132">
         <v>3</v>
       </c>
       <c r="E27" s="15" t="s">
@@ -4713,18 +4722,18 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="G27" s="94"/>
-      <c r="H27" s="119">
+      <c r="H27" s="128">
         <f>F27*G27+F28*G28+F29*G29</f>
         <v>0</v>
       </c>
-      <c r="I27" s="135"/>
+      <c r="I27" s="145"/>
       <c r="K27" s="3"/>
     </row>
     <row r="28" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="185"/>
-      <c r="B28" s="189"/>
-      <c r="C28" s="179"/>
-      <c r="D28" s="116"/>
+      <c r="A28" s="177"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="167"/>
+      <c r="D28" s="132"/>
       <c r="E28" s="16" t="s">
         <v>112</v>
       </c>
@@ -4733,15 +4742,15 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="G28" s="98"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="135"/>
+      <c r="H28" s="128"/>
+      <c r="I28" s="145"/>
       <c r="K28" s="3"/>
     </row>
     <row r="29" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="185"/>
-      <c r="B29" s="189"/>
-      <c r="C29" s="179"/>
-      <c r="D29" s="116"/>
+      <c r="A29" s="177"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="167"/>
+      <c r="D29" s="132"/>
       <c r="E29" s="17" t="s">
         <v>102</v>
       </c>
@@ -4750,21 +4759,21 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="G29" s="95"/>
-      <c r="H29" s="119"/>
-      <c r="I29" s="135"/>
+      <c r="H29" s="128"/>
+      <c r="I29" s="145"/>
       <c r="K29" s="3"/>
     </row>
     <row r="30" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="102" t="s">
+      <c r="A30" s="188" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="160" t="s">
+      <c r="B30" s="190" t="s">
         <v>138</v>
       </c>
-      <c r="C30" s="156">
-        <v>1</v>
-      </c>
-      <c r="D30" s="151">
+      <c r="C30" s="142">
+        <v>1</v>
+      </c>
+      <c r="D30" s="125">
         <v>1</v>
       </c>
       <c r="E30" s="15" t="s">
@@ -4774,7 +4783,7 @@
         <v>0.5</v>
       </c>
       <c r="G30" s="97"/>
-      <c r="H30" s="118">
+      <c r="H30" s="136">
         <f>G30*F30+G31*F31</f>
         <v>0</v>
       </c>
@@ -4785,10 +4794,10 @@
       <c r="K30" s="3"/>
     </row>
     <row r="31" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="204"/>
-      <c r="B31" s="166"/>
-      <c r="C31" s="157"/>
-      <c r="D31" s="108"/>
+      <c r="A31" s="189"/>
+      <c r="B31" s="191"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="127"/>
       <c r="E31" s="17" t="s">
         <v>107</v>
       </c>
@@ -4796,18 +4805,18 @@
         <v>0.5</v>
       </c>
       <c r="G31" s="96"/>
-      <c r="H31" s="164"/>
-      <c r="I31" s="136"/>
+      <c r="H31" s="131"/>
+      <c r="I31" s="135"/>
       <c r="K31" s="3"/>
     </row>
     <row r="32" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="145" t="s">
+      <c r="A32" s="171" t="s">
         <v>35</v>
       </c>
       <c r="B32" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="104">
+      <c r="C32" s="173">
         <v>3</v>
       </c>
       <c r="D32" s="14">
@@ -4831,11 +4840,11 @@
       <c r="K32" s="3"/>
     </row>
     <row r="33" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="146"/>
+      <c r="A33" s="172"/>
       <c r="B33" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="147"/>
+      <c r="C33" s="174"/>
       <c r="D33" s="22">
         <v>1</v>
       </c>
@@ -4850,20 +4859,20 @@
         <f>G33*F33</f>
         <v>0</v>
       </c>
-      <c r="I33" s="136"/>
+      <c r="I33" s="135"/>
       <c r="K33" s="3"/>
     </row>
     <row r="34" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="182" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="195" t="s">
+      <c r="B34" s="140" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="156">
+      <c r="C34" s="142">
         <v>4</v>
       </c>
-      <c r="D34" s="115">
+      <c r="D34" s="144">
         <v>1</v>
       </c>
       <c r="E34" s="15" t="s">
@@ -4873,7 +4882,7 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="97"/>
-      <c r="H34" s="118">
+      <c r="H34" s="136">
         <f>G34*F34+G35*F35</f>
         <v>0</v>
       </c>
@@ -4884,10 +4893,10 @@
       <c r="K34" s="3"/>
     </row>
     <row r="35" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="149"/>
-      <c r="B35" s="196"/>
-      <c r="C35" s="117"/>
-      <c r="D35" s="116"/>
+      <c r="A35" s="183"/>
+      <c r="B35" s="141"/>
+      <c r="C35" s="122"/>
+      <c r="D35" s="132"/>
       <c r="E35" s="16" t="s">
         <v>109</v>
       </c>
@@ -4895,17 +4904,17 @@
         <v>0.5</v>
       </c>
       <c r="G35" s="93"/>
-      <c r="H35" s="119"/>
-      <c r="I35" s="135"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="145"/>
       <c r="K35" s="3"/>
     </row>
     <row r="36" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="149"/>
-      <c r="B36" s="196" t="s">
+      <c r="A36" s="183"/>
+      <c r="B36" s="141" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="117"/>
-      <c r="D36" s="116">
+      <c r="C36" s="122"/>
+      <c r="D36" s="132">
         <v>2.5</v>
       </c>
       <c r="E36" s="15" t="s">
@@ -4915,18 +4924,18 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="94"/>
-      <c r="H36" s="119">
+      <c r="H36" s="128">
         <f>G36*F36+G37*F37</f>
         <v>0</v>
       </c>
-      <c r="I36" s="135"/>
+      <c r="I36" s="145"/>
       <c r="K36" s="3"/>
     </row>
     <row r="37" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="149"/>
-      <c r="B37" s="196"/>
-      <c r="C37" s="117"/>
-      <c r="D37" s="116"/>
+      <c r="A37" s="183"/>
+      <c r="B37" s="141"/>
+      <c r="C37" s="122"/>
+      <c r="D37" s="132"/>
       <c r="E37" s="17" t="s">
         <v>148</v>
       </c>
@@ -4934,16 +4943,16 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="95"/>
-      <c r="H37" s="119"/>
-      <c r="I37" s="135"/>
+      <c r="H37" s="128"/>
+      <c r="I37" s="145"/>
       <c r="K37" s="3"/>
     </row>
     <row r="38" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="150"/>
+      <c r="A38" s="184"/>
       <c r="B38" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="157"/>
+      <c r="C38" s="123"/>
       <c r="D38" s="22">
         <v>0.5</v>
       </c>
@@ -4958,7 +4967,7 @@
         <f>G38*F38</f>
         <v>0</v>
       </c>
-      <c r="I38" s="136"/>
+      <c r="I38" s="135"/>
       <c r="K38" s="3"/>
     </row>
     <row r="39" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -4992,26 +5001,26 @@
       <c r="K39" s="3"/>
     </row>
     <row r="40" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="140" t="s">
+      <c r="A40" s="185" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="141"/>
-      <c r="C40" s="140">
+      <c r="B40" s="186"/>
+      <c r="C40" s="185">
         <f>SUM(C2:C39)</f>
         <v>30</v>
       </c>
-      <c r="D40" s="142"/>
-      <c r="E40" s="123">
+      <c r="D40" s="187"/>
+      <c r="E40" s="150">
         <f>(I2*C2+I8*C8+I11*C11+I24*C24+I30*C30+I32*C32+I34*C34+I39*C39)/C40</f>
         <v>0</v>
       </c>
-      <c r="F40" s="124"/>
-      <c r="G40" s="124"/>
-      <c r="H40" s="143" t="str">
+      <c r="F40" s="151"/>
+      <c r="G40" s="151"/>
+      <c r="H40" s="158" t="str">
         <f>IF(OR(I2&lt;10,I8&lt;10,I11&lt;10,I24&lt;10,I30&lt;10,I32&lt;10,I34&lt;10,I39&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I40" s="144"/>
+      <c r="I40" s="159"/>
       <c r="K40" s="3"/>
     </row>
     <row r="41" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -5028,29 +5037,34 @@
     </row>
   </sheetData>
   <mergeCells count="67">
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C24:C29"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="H24:H26"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="H27:H29"/>
-    <mergeCell ref="C11:C23"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="H11:H14"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="I34:I38"/>
-    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A11:A23"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C7"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="I24:I29"/>
+    <mergeCell ref="I11:I23"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B4:B5"/>
@@ -5067,34 +5081,29 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="A24:A29"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="H18:H20"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="I24:I29"/>
-    <mergeCell ref="I11:I23"/>
-    <mergeCell ref="A11:A23"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="I8:I10"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C7"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="I34:I38"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="C24:C29"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="H27:H29"/>
+    <mergeCell ref="C11:C23"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="H11:H14"/>
   </mergeCells>
   <conditionalFormatting sqref="H40">
     <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
@@ -5142,31 +5151,31 @@
       <c r="B1" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="206" t="s">
+      <c r="C1" s="195" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="207"/>
-      <c r="E1" s="123" t="s">
+      <c r="D1" s="196"/>
+      <c r="E1" s="150" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="124"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="123" t="s">
+      <c r="F1" s="151"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="150" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="125"/>
+      <c r="I1" s="152"/>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="208" t="s">
+      <c r="A2" s="197" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="211" t="s">
+      <c r="B2" s="200" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="131">
+      <c r="C2" s="115">
         <v>30</v>
       </c>
-      <c r="D2" s="115">
+      <c r="D2" s="144">
         <v>30</v>
       </c>
       <c r="E2" s="23" t="s">
@@ -5177,7 +5186,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="G2" s="88"/>
-      <c r="H2" s="118">
+      <c r="H2" s="136">
         <f>F2*G2+F3*G3+G4*F4</f>
         <v>0</v>
       </c>
@@ -5187,10 +5196,10 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="209"/>
-      <c r="B3" s="212"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="116"/>
+      <c r="A3" s="198"/>
+      <c r="B3" s="201"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="132"/>
       <c r="E3" s="11" t="s">
         <v>152</v>
       </c>
@@ -5199,14 +5208,14 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="G3" s="89"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="135"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="145"/>
     </row>
     <row r="4" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="210"/>
-      <c r="B4" s="213"/>
-      <c r="C4" s="133"/>
-      <c r="D4" s="163"/>
+      <c r="A4" s="199"/>
+      <c r="B4" s="202"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="133"/>
       <c r="E4" s="17" t="s">
         <v>153</v>
       </c>
@@ -5215,31 +5224,31 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="G4" s="95"/>
-      <c r="H4" s="164"/>
-      <c r="I4" s="136"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="135"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="143" t="s">
+      <c r="A5" s="158" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="144"/>
-      <c r="C5" s="143">
+      <c r="B5" s="159"/>
+      <c r="C5" s="158">
         <f>SUM(C2:C2)</f>
         <v>30</v>
       </c>
-      <c r="D5" s="144"/>
-      <c r="E5" s="123">
+      <c r="D5" s="159"/>
+      <c r="E5" s="150">
         <f>(I2*C2)/C5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="124"/>
-      <c r="G5" s="125"/>
-      <c r="H5" s="143" t="str">
+      <c r="F5" s="151"/>
+      <c r="G5" s="152"/>
+      <c r="H5" s="158" t="str">
         <f>IF(OR(I2&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I5" s="144"/>
+      <c r="I5" s="159"/>
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -5608,7 +5617,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA6D249-F910-483A-9894-B4C0568AF5EA}">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.140625" defaultRowHeight="30.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="35.140625" style="3" customWidth="1"/>
@@ -5628,31 +5637,31 @@
       <c r="B1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="121" t="s">
+      <c r="C1" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="122"/>
-      <c r="E1" s="123" t="s">
+      <c r="D1" s="147"/>
+      <c r="E1" s="150" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="124"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="123" t="s">
+      <c r="F1" s="151"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="150" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="125"/>
+      <c r="I1" s="152"/>
     </row>
     <row r="2" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="110" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="212" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="131">
+      <c r="C2" s="115">
         <v>10</v>
       </c>
-      <c r="D2" s="115">
+      <c r="D2" s="144">
         <v>2</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -5663,21 +5672,21 @@
         <v>0.13333333333333333</v>
       </c>
       <c r="G2" s="93"/>
-      <c r="H2" s="118">
+      <c r="H2" s="136">
         <f>G2*F2+G3*F3+G4*F4+G5*F5</f>
         <v>0</v>
       </c>
       <c r="I2" s="134">
-        <f>(H2*D2+H6*D6+H8*D8+H11*D11)/C2</f>
+        <f>(H2*D2+H6*D6+H10*D10+H13*D13)/C2</f>
         <v>0</v>
       </c>
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="127"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="116"/>
+      <c r="A3" s="111"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="132"/>
       <c r="E3" s="11" t="s">
         <v>99</v>
       </c>
@@ -5686,32 +5695,32 @@
         <v>0.31111111111111112</v>
       </c>
       <c r="G3" s="93"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="135"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="145"/>
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="127"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="116"/>
+      <c r="A4" s="111"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="132"/>
       <c r="E4" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F4" s="25">
         <f>75/225</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="G4" s="93"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="135"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="145"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="127"/>
-      <c r="B5" s="130"/>
-      <c r="C5" s="132"/>
-      <c r="D5" s="116"/>
+      <c r="A5" s="111"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="132"/>
       <c r="E5" s="11" t="s">
         <v>89</v>
       </c>
@@ -5720,579 +5729,601 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="G5" s="93"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="135"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="145"/>
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="127"/>
-      <c r="B6" s="130" t="s">
+      <c r="A6" s="111"/>
+      <c r="B6" s="118" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="132"/>
-      <c r="D6" s="107">
+      <c r="C6" s="116"/>
+      <c r="D6" s="126">
         <v>3</v>
       </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="24"/>
+      <c r="E6" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="24">
+        <v>0.1</v>
+      </c>
       <c r="G6" s="94"/>
-      <c r="H6" s="109">
-        <f>G6*F6+G7*F7</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="135"/>
+      <c r="H6" s="213">
+        <f>G6*F6+G7*F7+G8*F8+G9*F9</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="145"/>
     </row>
     <row r="7" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="127"/>
-      <c r="B7" s="130"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="12" t="s">
+      <c r="A7" s="111"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="98"/>
+      <c r="H7" s="213"/>
+      <c r="I7" s="145"/>
+    </row>
+    <row r="8" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="111"/>
+      <c r="B8" s="118"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="126"/>
+      <c r="E8" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="98"/>
+      <c r="H8" s="213"/>
+      <c r="I8" s="145"/>
+    </row>
+    <row r="9" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="111"/>
+      <c r="B9" s="118"/>
+      <c r="C9" s="116"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="135"/>
-    </row>
-    <row r="8" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="127"/>
-      <c r="B8" s="130" t="s">
+      <c r="F9" s="26">
+        <v>0.4</v>
+      </c>
+      <c r="G9" s="95"/>
+      <c r="H9" s="213"/>
+      <c r="I9" s="145"/>
+    </row>
+    <row r="10" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="111"/>
+      <c r="B10" s="118" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="132"/>
-      <c r="D8" s="116">
+      <c r="C10" s="116"/>
+      <c r="D10" s="132">
         <v>3</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E10" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F10" s="24">
         <v>0.2</v>
       </c>
-      <c r="G8" s="94"/>
-      <c r="H8" s="119">
-        <f>G8*F8+G9*F9+G10*F10</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="135"/>
-    </row>
-    <row r="9" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="127"/>
-      <c r="B9" s="130"/>
-      <c r="C9" s="132"/>
-      <c r="D9" s="116"/>
-      <c r="E9" s="11" t="s">
+      <c r="G10" s="94"/>
+      <c r="H10" s="128">
+        <f>G10*F10+G11*F11+G12*F12</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="145"/>
+    </row>
+    <row r="11" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="111"/>
+      <c r="B11" s="118"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F11" s="25">
         <v>0.4</v>
       </c>
-      <c r="G9" s="98"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="135"/>
-    </row>
-    <row r="10" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="127"/>
-      <c r="B10" s="130"/>
-      <c r="C10" s="132"/>
-      <c r="D10" s="116"/>
-      <c r="E10" s="16" t="s">
+      <c r="G11" s="98"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="145"/>
+    </row>
+    <row r="12" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="111"/>
+      <c r="B12" s="118"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F12" s="25">
         <v>0.4</v>
       </c>
-      <c r="G10" s="98"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="135"/>
-    </row>
-    <row r="11" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="127"/>
-      <c r="B11" s="130" t="s">
+      <c r="G12" s="98"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="145"/>
+    </row>
+    <row r="13" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="111"/>
+      <c r="B13" s="118" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="132"/>
-      <c r="D11" s="107">
+      <c r="C13" s="116"/>
+      <c r="D13" s="126">
         <v>2</v>
       </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="109">
-        <f>G11*F11+G12*F12</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="135"/>
-    </row>
-    <row r="12" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="128"/>
-      <c r="B12" s="137"/>
-      <c r="C12" s="133"/>
-      <c r="D12" s="108"/>
-      <c r="E12" s="17" t="s">
+      <c r="E13" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F13" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="G13" s="94"/>
+      <c r="H13" s="213">
+        <f>G13*F13+G14*F14</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="145"/>
+    </row>
+    <row r="14" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="112"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="26"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="136"/>
-    </row>
-    <row r="13" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="120" t="s">
+      <c r="F14" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="95"/>
+      <c r="H14" s="211"/>
+      <c r="I14" s="135"/>
+    </row>
+    <row r="15" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="113" t="s">
+      <c r="B15" s="215" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="117">
+      <c r="C15" s="122">
         <v>4</v>
       </c>
-      <c r="D13" s="115">
+      <c r="D15" s="144">
         <v>2</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E15" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="F15" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="94"/>
+      <c r="H15" s="136">
+        <f>G15*F15+G16*F16+G17*F17+G18*F18</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="134">
+        <f>(H15*D15+H19*D19)/C15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="119"/>
+      <c r="B16" s="121"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F16" s="25">
         <v>0.2</v>
       </c>
-      <c r="G13" s="94"/>
-      <c r="H13" s="118">
-        <f>G13*F13+G14*F14+G15*F15+G16*F16</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="134">
-        <f>(H13*D13+H17*D17)/C13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="120"/>
-      <c r="B14" s="114"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="16" t="s">
+      <c r="G16" s="98"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="145"/>
+    </row>
+    <row r="17" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="119"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F17" s="25">
         <v>0.2</v>
       </c>
-      <c r="G14" s="98"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="135"/>
-    </row>
-    <row r="15" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="120"/>
-      <c r="B15" s="114"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="F15" s="25">
+      <c r="G17" s="98"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="145"/>
+    </row>
+    <row r="18" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="119"/>
+      <c r="B18" s="121"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="132"/>
+      <c r="E18" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" s="26">
+        <v>0.4</v>
+      </c>
+      <c r="G18" s="95"/>
+      <c r="H18" s="128"/>
+      <c r="I18" s="145"/>
+    </row>
+    <row r="19" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="119"/>
+      <c r="B19" s="121" t="s">
+        <v>156</v>
+      </c>
+      <c r="C19" s="122"/>
+      <c r="D19" s="132">
+        <v>2</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="F19" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="G19" s="93"/>
+      <c r="H19" s="128">
+        <f>G19*F19+G20*F20+G21*F21</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="145"/>
+    </row>
+    <row r="20" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="119"/>
+      <c r="B20" s="121"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="132"/>
+      <c r="E20" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="G20" s="93"/>
+      <c r="H20" s="128"/>
+      <c r="I20" s="145"/>
+    </row>
+    <row r="21" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="119"/>
+      <c r="B21" s="156"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="133"/>
+      <c r="E21" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" s="25">
+        <v>0.4</v>
+      </c>
+      <c r="G21" s="93"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="145"/>
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="160" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="153" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="142">
+        <v>5</v>
+      </c>
+      <c r="D22" s="144">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="F22" s="24">
+        <v>0.1</v>
+      </c>
+      <c r="G22" s="97"/>
+      <c r="H22" s="136">
+        <f>G22*F22+G23*F23+G24*F24+G25*F25</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="134">
+        <f>(H22*D22+H26*D26+H28*D28)/C22</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="161"/>
+      <c r="B23" s="154"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23" s="25">
         <v>0.2</v>
       </c>
-      <c r="G15" s="98"/>
-      <c r="H15" s="119"/>
-      <c r="I15" s="135"/>
-    </row>
-    <row r="16" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="120"/>
-      <c r="B16" s="114"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="116"/>
-      <c r="E16" s="17" t="s">
+      <c r="G23" s="93"/>
+      <c r="H23" s="128"/>
+      <c r="I23" s="145"/>
+      <c r="K23" s="3"/>
+    </row>
+    <row r="24" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="161"/>
+      <c r="B24" s="154"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="132"/>
+      <c r="E24" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="G24" s="93"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="145"/>
+      <c r="K24" s="3"/>
+    </row>
+    <row r="25" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="161"/>
+      <c r="B25" s="154"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F25" s="25">
         <v>0.4</v>
       </c>
-      <c r="G16" s="95"/>
-      <c r="H16" s="119"/>
-      <c r="I16" s="135"/>
-    </row>
-    <row r="17" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="120"/>
-      <c r="B17" s="114" t="s">
-        <v>156</v>
-      </c>
-      <c r="C17" s="117"/>
-      <c r="D17" s="116">
+      <c r="G25" s="93"/>
+      <c r="H25" s="128"/>
+      <c r="I25" s="145"/>
+      <c r="K25" s="3"/>
+    </row>
+    <row r="26" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="161"/>
+      <c r="B26" s="154" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="122"/>
+      <c r="D26" s="132">
         <v>2</v>
       </c>
-      <c r="E17" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="E26" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="G26" s="94"/>
+      <c r="H26" s="128">
+        <f>G26*F26+G27*F27</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="145"/>
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="161"/>
+      <c r="B27" s="154"/>
+      <c r="C27" s="122"/>
+      <c r="D27" s="132"/>
+      <c r="E27" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="25">
+        <v>0.4</v>
+      </c>
+      <c r="G27" s="98"/>
+      <c r="H27" s="128"/>
+      <c r="I27" s="145"/>
+      <c r="K27" s="3"/>
+    </row>
+    <row r="28" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="161"/>
+      <c r="B28" s="154" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="122"/>
+      <c r="D28" s="126">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F28" s="24">
+        <f>1/3</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G28" s="94"/>
+      <c r="H28" s="213">
+        <f>G28*F28+G29*F29</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="145"/>
+      <c r="K28" s="3"/>
+    </row>
+    <row r="29" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="161"/>
+      <c r="B29" s="155"/>
+      <c r="C29" s="122"/>
+      <c r="D29" s="127"/>
+      <c r="E29" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F29" s="26">
+        <f>2/3</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G29" s="95"/>
+      <c r="H29" s="211"/>
+      <c r="I29" s="145"/>
+      <c r="K29" s="3"/>
+    </row>
+    <row r="30" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="188" t="s">
+        <v>158</v>
+      </c>
+      <c r="B30" s="190" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="173">
+        <v>3</v>
+      </c>
+      <c r="D30" s="144">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="F30" s="24">
         <v>0.3</v>
       </c>
-      <c r="G17" s="93"/>
-      <c r="H17" s="119">
-        <f>G17*F17+G18*F18+G19*F19</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="135"/>
-    </row>
-    <row r="18" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="120"/>
-      <c r="B18" s="114"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F18" s="25">
+      <c r="G30" s="94"/>
+      <c r="H30" s="136">
+        <f>F30*G30+G31*F31+G32*F32</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="134">
+        <f>(H30*D30+H33*D33)/C30</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="3"/>
+    </row>
+    <row r="31" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="214"/>
+      <c r="B31" s="204"/>
+      <c r="C31" s="143"/>
+      <c r="D31" s="132"/>
+      <c r="E31" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F31" s="25">
         <v>0.3</v>
       </c>
-      <c r="G18" s="93"/>
-      <c r="H18" s="119"/>
-      <c r="I18" s="135"/>
-    </row>
-    <row r="19" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="120"/>
-      <c r="B19" s="162"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="163"/>
-      <c r="E19" s="16" t="s">
+      <c r="G31" s="98"/>
+      <c r="H31" s="128"/>
+      <c r="I31" s="145"/>
+      <c r="K31" s="3"/>
+    </row>
+    <row r="32" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="214"/>
+      <c r="B32" s="204"/>
+      <c r="C32" s="143"/>
+      <c r="D32" s="132"/>
+      <c r="E32" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F32" s="26">
         <v>0.4</v>
       </c>
-      <c r="G19" s="93"/>
-      <c r="H19" s="164"/>
-      <c r="I19" s="135"/>
-      <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="138" t="s">
-        <v>157</v>
-      </c>
-      <c r="B20" s="165" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="156">
-        <v>5</v>
-      </c>
-      <c r="D20" s="115">
+      <c r="G32" s="95"/>
+      <c r="H32" s="128"/>
+      <c r="I32" s="145"/>
+      <c r="K32" s="3"/>
+    </row>
+    <row r="33" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="189"/>
+      <c r="B33" s="85" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="123"/>
+      <c r="D33" s="21">
+        <v>1</v>
+      </c>
+      <c r="E33" s="54" t="s">
+        <v>187</v>
+      </c>
+      <c r="F33" s="55">
+        <v>1</v>
+      </c>
+      <c r="G33" s="99"/>
+      <c r="H33" s="12">
+        <f>G33*F33</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="135"/>
+      <c r="K33" s="3"/>
+    </row>
+    <row r="34" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="205" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="102" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="143">
+        <v>3</v>
+      </c>
+      <c r="D34" s="3">
         <v>2</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="F20" s="24">
-        <v>0.1</v>
-      </c>
-      <c r="G20" s="97"/>
-      <c r="H20" s="118">
-        <f>G20*F20+G21*F21+G22*F22+G23*F23</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="134">
-        <f>(H20*D20+H24*D24+H26*D26)/C20</f>
-        <v>0</v>
-      </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="139"/>
-      <c r="B21" s="111"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="116"/>
-      <c r="E21" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="F21" s="25">
-        <v>0.2</v>
-      </c>
-      <c r="G21" s="93"/>
-      <c r="H21" s="119"/>
-      <c r="I21" s="135"/>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="139"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="116"/>
-      <c r="E22" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="F22" s="25">
-        <v>0.3</v>
-      </c>
-      <c r="G22" s="93"/>
-      <c r="H22" s="119"/>
-      <c r="I22" s="135"/>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="139"/>
-      <c r="B23" s="111"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="116"/>
-      <c r="E23" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="F23" s="25">
-        <v>0.4</v>
-      </c>
-      <c r="G23" s="93"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="135"/>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="139"/>
-      <c r="B24" s="111" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="117"/>
-      <c r="D24" s="116">
-        <v>2</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24" s="24"/>
-      <c r="G24" s="94"/>
-      <c r="H24" s="119">
-        <f>G24*F24+G25*F25</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="135"/>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="139"/>
-      <c r="B25" s="111"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="116"/>
-      <c r="E25" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F25" s="25"/>
-      <c r="G25" s="98"/>
-      <c r="H25" s="119"/>
-      <c r="I25" s="135"/>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="139"/>
-      <c r="B26" s="111" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="117"/>
-      <c r="D26" s="107">
-        <v>1</v>
-      </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="94"/>
-      <c r="H26" s="109">
-        <f>G26*F26+G27*F27</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="135"/>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="139"/>
-      <c r="B27" s="112"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="108"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="95"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="135"/>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="102" t="s">
-        <v>158</v>
-      </c>
-      <c r="B28" s="160" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="104">
-        <v>3</v>
-      </c>
-      <c r="D28" s="115">
-        <v>2</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F28" s="25">
-        <v>0.3</v>
-      </c>
-      <c r="G28" s="98"/>
-      <c r="H28" s="118">
-        <f>F28*G28+G29*F29+G30*F30</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="134">
-        <f>(H28*D28+H31*D31)/C28</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="103"/>
-      <c r="B29" s="161"/>
-      <c r="C29" s="105"/>
-      <c r="D29" s="116"/>
-      <c r="E29" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="F29" s="25">
-        <v>0.3</v>
-      </c>
-      <c r="G29" s="98"/>
-      <c r="H29" s="119"/>
-      <c r="I29" s="135"/>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="103"/>
-      <c r="B30" s="161"/>
-      <c r="C30" s="105"/>
-      <c r="D30" s="116"/>
-      <c r="E30" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="F30" s="26">
-        <v>0.4</v>
-      </c>
-      <c r="G30" s="95"/>
-      <c r="H30" s="119"/>
-      <c r="I30" s="135"/>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="103"/>
-      <c r="B31" s="161" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="105"/>
-      <c r="D31" s="116">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="94"/>
-      <c r="H31" s="119">
-        <f>G31*F31+F32*G32</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="135"/>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="103"/>
-      <c r="B32" s="166"/>
-      <c r="C32" s="106"/>
-      <c r="D32" s="163"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="95"/>
-      <c r="H32" s="164"/>
-      <c r="I32" s="135"/>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="145" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" s="104">
-        <v>3</v>
-      </c>
-      <c r="D33" s="14">
-        <v>2</v>
-      </c>
-      <c r="E33" s="16" t="s">
+      <c r="E34" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="F33" s="25">
-        <v>1</v>
-      </c>
-      <c r="G33" s="93"/>
-      <c r="H33" s="23">
-        <f t="shared" ref="H33:H39" si="0">G33*F33</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="134">
-        <f>(H33*D33+H34*D34)/C33</f>
-        <v>0</v>
-      </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="146"/>
-      <c r="B34" s="30" t="s">
+      <c r="F34" s="25">
+        <v>1</v>
+      </c>
+      <c r="G34" s="93"/>
+      <c r="H34" s="11">
+        <f t="shared" ref="H34:H40" si="0">G34*F34</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="145">
+        <f>(H34*D34+H35*D35)/C34</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="3"/>
+    </row>
+    <row r="35" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="172"/>
+      <c r="B35" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="147"/>
-      <c r="D34" s="22">
-        <v>1</v>
-      </c>
-      <c r="E34" s="54" t="s">
+      <c r="C35" s="174"/>
+      <c r="D35" s="22">
+        <v>1</v>
+      </c>
+      <c r="E35" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="55">
-        <v>1</v>
-      </c>
-      <c r="G34" s="99"/>
-      <c r="H34" s="12">
+      <c r="F35" s="55">
+        <v>1</v>
+      </c>
+      <c r="G35" s="99"/>
+      <c r="H35" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I34" s="136"/>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="148" t="s">
+      <c r="I35" s="135"/>
+      <c r="K35" s="3"/>
+    </row>
+    <row r="36" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="182" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="69" t="s">
+      <c r="B36" s="69" t="s">
         <v>159</v>
       </c>
-      <c r="C35" s="151">
+      <c r="C36" s="125">
         <v>4</v>
       </c>
-      <c r="D35" s="19">
-        <v>1</v>
-      </c>
-      <c r="E35" s="54" t="s">
-        <v>182</v>
-      </c>
-      <c r="F35" s="55">
-        <v>1</v>
-      </c>
-      <c r="G35" s="99"/>
-      <c r="H35" s="23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="134">
-        <f>(H35*D35+H36*D36+H37*D37+H39*D39)/C35</f>
-        <v>0</v>
-      </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="36" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="149"/>
-      <c r="B36" s="70" t="s">
-        <v>179</v>
-      </c>
-      <c r="C36" s="107"/>
-      <c r="D36" s="3">
-        <v>1.5</v>
+      <c r="D36" s="19">
+        <v>1</v>
       </c>
       <c r="E36" s="54" t="s">
         <v>181</v>
@@ -6300,228 +6331,251 @@
       <c r="F36" s="55">
         <v>1</v>
       </c>
-      <c r="G36" s="94"/>
-      <c r="H36" s="11">
+      <c r="G36" s="99"/>
+      <c r="H36" s="23">
+        <f>G36*F36</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="134">
+        <f>(H36*D36+H37*D37+H38*D38+H40*D40)/C36</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="3"/>
+    </row>
+    <row r="37" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="183"/>
+      <c r="B37" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="C37" s="126"/>
+      <c r="D37" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="E37" s="54" t="s">
+        <v>180</v>
+      </c>
+      <c r="F37" s="55">
+        <v>1</v>
+      </c>
+      <c r="G37" s="94"/>
+      <c r="H37" s="11">
+        <f>G37*F37</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="145"/>
+      <c r="K37" s="3"/>
+    </row>
+    <row r="38" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="183"/>
+      <c r="B38" s="203" t="s">
+        <v>160</v>
+      </c>
+      <c r="C38" s="126"/>
+      <c r="D38" s="132">
+        <v>1</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="F38" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="G38" s="94"/>
+      <c r="H38" s="128">
+        <f>G38*F38+G39*F39</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="145"/>
+      <c r="K38" s="3"/>
+    </row>
+    <row r="39" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="183"/>
+      <c r="B39" s="203"/>
+      <c r="C39" s="126"/>
+      <c r="D39" s="132"/>
+      <c r="E39" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F39" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="G39" s="95"/>
+      <c r="H39" s="128"/>
+      <c r="I39" s="145"/>
+      <c r="K39" s="3"/>
+    </row>
+    <row r="40" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="184"/>
+      <c r="B40" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="127"/>
+      <c r="D40" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="25">
+        <v>1</v>
+      </c>
+      <c r="G40" s="98"/>
+      <c r="H40" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I36" s="135"/>
-      <c r="K36" s="3"/>
-    </row>
-    <row r="37" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="149"/>
-      <c r="B37" s="159" t="s">
-        <v>160</v>
-      </c>
-      <c r="C37" s="107"/>
-      <c r="D37" s="116">
-        <v>1</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="F37" s="24">
+      <c r="I40" s="135"/>
+      <c r="K40" s="3"/>
+    </row>
+    <row r="41" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="206" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="208" t="s">
+        <v>161</v>
+      </c>
+      <c r="C41" s="142">
+        <v>1</v>
+      </c>
+      <c r="D41" s="125">
+        <v>1</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="F41" s="24">
         <v>0.5</v>
       </c>
-      <c r="G37" s="94"/>
-      <c r="H37" s="119">
-        <f>G37*F37+G38*F38</f>
-        <v>0</v>
-      </c>
-      <c r="I37" s="135"/>
-      <c r="K37" s="3"/>
-    </row>
-    <row r="38" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="149"/>
-      <c r="B38" s="159"/>
-      <c r="C38" s="107"/>
-      <c r="D38" s="116"/>
-      <c r="E38" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="F38" s="26">
+      <c r="G41" s="94"/>
+      <c r="H41" s="210">
+        <f>G41*F41+G42*F42</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="134">
+        <f>(H41*D41)/C41</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="3"/>
+    </row>
+    <row r="42" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="207"/>
+      <c r="B42" s="209"/>
+      <c r="C42" s="123"/>
+      <c r="D42" s="127"/>
+      <c r="E42" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="F42" s="26">
         <v>0.5</v>
       </c>
-      <c r="G38" s="95"/>
-      <c r="H38" s="119"/>
-      <c r="I38" s="135"/>
-      <c r="K38" s="3"/>
-    </row>
-    <row r="39" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="150"/>
-      <c r="B39" s="71" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="108"/>
-      <c r="D39" s="22">
-        <v>0.5</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F39" s="25">
-        <v>1</v>
-      </c>
-      <c r="G39" s="98"/>
-      <c r="H39" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="136"/>
-      <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="152" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="154" t="s">
-        <v>161</v>
-      </c>
-      <c r="C40" s="156">
-        <v>1</v>
-      </c>
-      <c r="D40" s="151">
-        <v>1</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="F40" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="G40" s="94"/>
-      <c r="H40" s="158">
-        <f>G40*F40+G41*F41</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="134">
-        <f>(H40*D40)/C40</f>
-        <v>0</v>
-      </c>
-      <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="153"/>
-      <c r="B41" s="155"/>
-      <c r="C41" s="157"/>
-      <c r="D41" s="108"/>
-      <c r="E41" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="F41" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="G41" s="95"/>
-      <c r="H41" s="110"/>
-      <c r="I41" s="136"/>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="140" t="s">
+      <c r="G42" s="95"/>
+      <c r="H42" s="211"/>
+      <c r="I42" s="135"/>
+      <c r="K42" s="3"/>
+    </row>
+    <row r="43" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="185" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="141"/>
-      <c r="C42" s="140">
-        <f>SUM(C2:C40)</f>
+      <c r="B43" s="186"/>
+      <c r="C43" s="185">
+        <f>SUM(C2:C41)</f>
         <v>30</v>
       </c>
-      <c r="D42" s="142"/>
-      <c r="E42" s="123">
-        <f>(I2*C2+I13*C13+I20*C20+I28*C28+I33*C33+I35*C35+I40*C40)/C42</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="124"/>
-      <c r="G42" s="124"/>
-      <c r="H42" s="143" t="str">
-        <f>IF(OR(I2&lt;10,I13&lt;10,I20&lt;10,I28&lt;10,I33&lt;10,I35&lt;10,I40&lt;10),"Valide pas","Valide")</f>
+      <c r="D43" s="187"/>
+      <c r="E43" s="150">
+        <f>(I2*C2+I15*C15+I22*C22+I30*C30+I34*C34+I36*C36+I41*C41)/C43</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="151"/>
+      <c r="G43" s="151"/>
+      <c r="H43" s="158" t="str">
+        <f>IF(OR(I2&lt;10,I15&lt;10,I22&lt;10,I30&lt;10,I34&lt;10,I36&lt;10,I41&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I42" s="144"/>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="62"/>
-      <c r="I43" s="62"/>
+      <c r="I43" s="159"/>
       <c r="K43" s="3"/>
     </row>
+    <row r="44" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="62"/>
+      <c r="I44" s="62"/>
+      <c r="K44" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="67">
-    <mergeCell ref="I28:I32"/>
-    <mergeCell ref="I13:I19"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="H28:H30"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="C20:C27"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="E42:G42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A35:A39"/>
-    <mergeCell ref="C35:C39"/>
-    <mergeCell ref="I35:I39"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="I20:I27"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="A20:A27"/>
+  <mergeCells count="64">
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="D15:D18"/>
+    <mergeCell ref="C15:C21"/>
+    <mergeCell ref="H15:H18"/>
+    <mergeCell ref="A15:A21"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A22:A29"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="A2:A14"/>
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C12"/>
+    <mergeCell ref="C2:C14"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="H2:H5"/>
-    <mergeCell ref="I2:I12"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A28:A32"/>
-    <mergeCell ref="C28:C32"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I2:I14"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="D6:D9"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="A36:A40"/>
+    <mergeCell ref="C36:C40"/>
+    <mergeCell ref="I36:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="I30:I33"/>
+    <mergeCell ref="I15:I21"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="H30:H32"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="C22:C29"/>
+    <mergeCell ref="I22:I29"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="D26:D27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="D13:D16"/>
-    <mergeCell ref="C13:C19"/>
-    <mergeCell ref="H13:H16"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="H20:H23"/>
   </mergeCells>
-  <conditionalFormatting sqref="H42">
+  <conditionalFormatting sqref="H43">
     <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"Valide pas"</formula>
     </cfRule>
@@ -6529,7 +6583,7 @@
       <formula>"Valide"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I40 E42">
+  <conditionalFormatting sqref="I2:I41 E43">
     <cfRule type="cellIs" dxfId="17" priority="3" operator="lessThan">
       <formula>10</formula>
     </cfRule>
@@ -6567,28 +6621,28 @@
       <c r="B1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="121" t="s">
+      <c r="C1" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="122"/>
-      <c r="E1" s="123" t="s">
+      <c r="D1" s="147"/>
+      <c r="E1" s="150" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="124"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="202" t="s">
+      <c r="F1" s="151"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="193" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="203"/>
+      <c r="I1" s="194"/>
     </row>
     <row r="2" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="110" t="s">
         <v>65</v>
       </c>
       <c r="B2" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="131">
+      <c r="C2" s="115">
         <v>6</v>
       </c>
       <c r="D2" s="14">
@@ -6612,11 +6666,11 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="127"/>
+      <c r="A3" s="111"/>
       <c r="B3" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="132"/>
+      <c r="C3" s="116"/>
       <c r="D3" s="3">
         <v>1</v>
       </c>
@@ -6631,14 +6685,14 @@
         <f t="shared" ref="H3:H25" si="0">G3*F3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="135"/>
+      <c r="I3" s="145"/>
     </row>
     <row r="4" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="127"/>
+      <c r="A4" s="111"/>
       <c r="B4" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="C4" s="132"/>
+        <v>185</v>
+      </c>
+      <c r="C4" s="116"/>
       <c r="D4" s="3">
         <v>2</v>
       </c>
@@ -6653,14 +6707,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I4" s="135"/>
+      <c r="I4" s="145"/>
     </row>
     <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="128"/>
+      <c r="A5" s="112"/>
       <c r="B5" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C5" s="133"/>
+        <v>162</v>
+      </c>
+      <c r="C5" s="117"/>
       <c r="D5" s="22">
         <v>2</v>
       </c>
@@ -6675,16 +6729,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="136"/>
+      <c r="I5" s="135"/>
     </row>
     <row r="6" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="120" t="s">
+      <c r="A6" s="119" t="s">
         <v>68</v>
       </c>
       <c r="B6" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="117">
+      <c r="C6" s="122">
         <v>4</v>
       </c>
       <c r="D6" s="3">
@@ -6707,11 +6761,11 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="120"/>
+      <c r="A7" s="119"/>
       <c r="B7" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="117"/>
+      <c r="C7" s="122"/>
       <c r="D7" s="3">
         <v>1</v>
       </c>
@@ -6726,14 +6780,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="135"/>
+      <c r="I7" s="145"/>
     </row>
     <row r="8" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="120"/>
+      <c r="A8" s="119"/>
       <c r="B8" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="117"/>
+      <c r="C8" s="122"/>
       <c r="D8" s="3">
         <v>1</v>
       </c>
@@ -6748,14 +6802,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="135"/>
+      <c r="I8" s="145"/>
     </row>
     <row r="9" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="120"/>
+      <c r="A9" s="119"/>
       <c r="B9" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="117"/>
+      <c r="C9" s="122"/>
       <c r="D9" s="3">
         <v>1</v>
       </c>
@@ -6770,17 +6824,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="136"/>
+      <c r="I9" s="135"/>
       <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="138" t="s">
+      <c r="A10" s="160" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="B10" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="C10" s="156">
+      <c r="C10" s="142">
         <v>2</v>
       </c>
       <c r="D10" s="19">
@@ -6804,11 +6858,11 @@
       <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="174"/>
+      <c r="A11" s="162"/>
       <c r="B11" s="81" t="s">
-        <v>167</v>
-      </c>
-      <c r="C11" s="157"/>
+        <v>166</v>
+      </c>
+      <c r="C11" s="123"/>
       <c r="D11" s="21">
         <v>1</v>
       </c>
@@ -6823,17 +6877,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="136"/>
+      <c r="I11" s="135"/>
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="183" t="s">
-        <v>166</v>
+      <c r="A12" s="175" t="s">
+        <v>165</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="214">
+      <c r="C12" s="216">
         <v>6</v>
       </c>
       <c r="D12" s="20">
@@ -6850,18 +6904,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="135">
+      <c r="I12" s="145">
         <f>(H12*D12+H13*D13+H14*D14)/C12</f>
         <v>0</v>
       </c>
       <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="183"/>
+      <c r="A13" s="175"/>
       <c r="B13" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="C13" s="214"/>
+        <v>167</v>
+      </c>
+      <c r="C13" s="216"/>
       <c r="D13" s="20">
         <v>2</v>
       </c>
@@ -6876,15 +6930,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="135"/>
+      <c r="I13" s="145"/>
       <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="184"/>
+      <c r="A14" s="176"/>
       <c r="B14" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="215"/>
+      <c r="C14" s="217"/>
       <c r="D14" s="21">
         <v>2</v>
       </c>
@@ -6899,17 +6953,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="135"/>
+      <c r="I14" s="145"/>
       <c r="K14" s="3"/>
     </row>
     <row r="15" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="102" t="s">
+      <c r="A15" s="188" t="s">
+        <v>168</v>
+      </c>
+      <c r="B15" s="84" t="s">
         <v>169</v>
       </c>
-      <c r="B15" s="84" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="156">
+      <c r="C15" s="142">
         <v>4</v>
       </c>
       <c r="D15" s="14">
@@ -6933,11 +6987,11 @@
       <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="103"/>
+      <c r="A16" s="214"/>
       <c r="B16" s="101" t="s">
-        <v>171</v>
-      </c>
-      <c r="C16" s="117"/>
+        <v>170</v>
+      </c>
+      <c r="C16" s="122"/>
       <c r="D16" s="3">
         <v>1</v>
       </c>
@@ -6952,15 +7006,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="135"/>
+      <c r="I16" s="145"/>
       <c r="K16" s="3"/>
     </row>
     <row r="17" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="204"/>
+      <c r="A17" s="189"/>
       <c r="B17" s="85" t="s">
-        <v>172</v>
-      </c>
-      <c r="C17" s="157"/>
+        <v>171</v>
+      </c>
+      <c r="C17" s="123"/>
       <c r="D17" s="22">
         <v>1</v>
       </c>
@@ -6975,17 +7029,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="136"/>
+      <c r="I17" s="135"/>
       <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="145" t="s">
+      <c r="A18" s="171" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="104">
+      <c r="C18" s="173">
         <v>3</v>
       </c>
       <c r="D18" s="14">
@@ -7009,11 +7063,11 @@
       <c r="K18" s="3"/>
     </row>
     <row r="19" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="146"/>
+      <c r="A19" s="172"/>
       <c r="B19" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="147"/>
+      <c r="C19" s="174"/>
       <c r="D19" s="22">
         <v>1</v>
       </c>
@@ -7028,17 +7082,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="136"/>
+      <c r="I19" s="135"/>
       <c r="K19" s="3"/>
     </row>
     <row r="20" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="148" t="s">
+      <c r="A20" s="182" t="s">
         <v>38</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="C20" s="156">
+        <v>173</v>
+      </c>
+      <c r="C20" s="142">
         <v>4</v>
       </c>
       <c r="D20" s="14">
@@ -7062,11 +7116,11 @@
       <c r="K20" s="3"/>
     </row>
     <row r="21" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="149"/>
+      <c r="A21" s="183"/>
       <c r="B21" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="117"/>
+      <c r="C21" s="122"/>
       <c r="D21" s="3">
         <v>1</v>
       </c>
@@ -7081,15 +7135,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I21" s="135"/>
+      <c r="I21" s="145"/>
       <c r="K21" s="3"/>
     </row>
     <row r="22" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="149"/>
+      <c r="A22" s="183"/>
       <c r="B22" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="117"/>
+      <c r="C22" s="122"/>
       <c r="D22" s="3">
         <v>1</v>
       </c>
@@ -7104,15 +7158,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="135"/>
+      <c r="I22" s="145"/>
       <c r="K22" s="3"/>
     </row>
     <row r="23" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="149"/>
+      <c r="A23" s="183"/>
       <c r="B23" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="117"/>
+      <c r="C23" s="122"/>
       <c r="D23" s="3">
         <v>1</v>
       </c>
@@ -7127,15 +7181,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I23" s="135"/>
+      <c r="I23" s="145"/>
       <c r="K23" s="3"/>
     </row>
     <row r="24" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="150"/>
+      <c r="A24" s="184"/>
       <c r="B24" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="157"/>
+      <c r="C24" s="123"/>
       <c r="D24" s="22">
         <v>0.5</v>
       </c>
@@ -7150,7 +7204,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I24" s="136"/>
+      <c r="I24" s="135"/>
       <c r="K24" s="3"/>
     </row>
     <row r="25" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -7158,7 +7212,7 @@
         <v>42</v>
       </c>
       <c r="B25" s="58" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C25" s="52">
         <v>1</v>
@@ -7184,26 +7238,26 @@
       <c r="K25" s="3"/>
     </row>
     <row r="26" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="140" t="s">
+      <c r="A26" s="185" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="141"/>
-      <c r="C26" s="140">
+      <c r="B26" s="186"/>
+      <c r="C26" s="185">
         <f>SUM(C2:C25)</f>
         <v>30</v>
       </c>
-      <c r="D26" s="142"/>
-      <c r="E26" s="123">
+      <c r="D26" s="187"/>
+      <c r="E26" s="150">
         <f>(I2*C2+I6*C6+I10*C10+I12*C12+I15*C15+I18*C18+I20*C20+I25*C25)/C26</f>
         <v>0</v>
       </c>
-      <c r="F26" s="124"/>
-      <c r="G26" s="124"/>
-      <c r="H26" s="143" t="str">
+      <c r="F26" s="151"/>
+      <c r="G26" s="151"/>
+      <c r="H26" s="158" t="str">
         <f>IF(OR(I2&lt;10,I6&lt;10,I10&lt;10,I12&lt;10,I15&lt;10,I18&lt;10,I20&lt;10,I25&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I26" s="144"/>
+      <c r="I26" s="159"/>
       <c r="K26" s="3"/>
     </row>
     <row r="27" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -7220,6 +7274,21 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="I2:I5"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="I6:I9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="C6:C9"/>
     <mergeCell ref="I15:I17"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="C26:D26"/>
@@ -7233,21 +7302,6 @@
     <mergeCell ref="A20:A24"/>
     <mergeCell ref="C20:C24"/>
     <mergeCell ref="I20:I24"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="I12:I14"/>
-    <mergeCell ref="I6:I9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="I2:I5"/>
   </mergeCells>
   <conditionalFormatting sqref="H26">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -7295,19 +7349,19 @@
       <c r="B1" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="206" t="s">
+      <c r="C1" s="195" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="207"/>
-      <c r="E1" s="123" t="s">
+      <c r="D1" s="196"/>
+      <c r="E1" s="150" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="124"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="123" t="s">
+      <c r="F1" s="151"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="150" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="125"/>
+      <c r="I1" s="152"/>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="86" t="s">
@@ -7339,26 +7393,26 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="143" t="s">
+      <c r="A3" s="158" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="143">
+      <c r="B3" s="159"/>
+      <c r="C3" s="158">
         <f>SUM(C2:C2)</f>
         <v>30</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="123">
+      <c r="D3" s="159"/>
+      <c r="E3" s="150">
         <f>(I2*C2)/C3</f>
         <v>0</v>
       </c>
-      <c r="F3" s="124"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="143" t="str">
+      <c r="F3" s="151"/>
+      <c r="G3" s="152"/>
+      <c r="H3" s="158" t="str">
         <f>IF(OR(I2&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I3" s="144"/>
+      <c r="I3" s="159"/>
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -7741,31 +7795,31 @@
       <c r="B1" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="216" t="s">
+      <c r="C1" s="222" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="217"/>
-      <c r="E1" s="123" t="s">
+      <c r="D1" s="223"/>
+      <c r="E1" s="150" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="124"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="218" t="s">
+      <c r="F1" s="151"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="224" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="203"/>
+      <c r="I1" s="194"/>
     </row>
     <row r="2" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="110" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="212" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="131">
+      <c r="C2" s="115">
         <v>8</v>
       </c>
-      <c r="D2" s="151">
+      <c r="D2" s="125">
         <v>4</v>
       </c>
       <c r="E2" s="23" t="s">
@@ -7775,7 +7829,7 @@
         <v>0.2</v>
       </c>
       <c r="G2" s="97"/>
-      <c r="H2" s="118">
+      <c r="H2" s="136">
         <f>G2*F2+G3*F3+G4*F4+G5*F5+G6*F6</f>
         <v>0</v>
       </c>
@@ -7786,10 +7840,10 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="127"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="107"/>
+      <c r="A3" s="111"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="126"/>
       <c r="E3" s="11" t="s">
         <v>124</v>
       </c>
@@ -7797,15 +7851,15 @@
         <v>0.2</v>
       </c>
       <c r="G3" s="93"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="135"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="145"/>
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="127"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="107"/>
+      <c r="A4" s="111"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="126"/>
       <c r="E4" s="11" t="s">
         <v>104</v>
       </c>
@@ -7813,15 +7867,15 @@
         <v>0.2</v>
       </c>
       <c r="G4" s="93"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="135"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="145"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="127"/>
-      <c r="B5" s="130"/>
-      <c r="C5" s="132"/>
-      <c r="D5" s="107"/>
+      <c r="A5" s="111"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="126"/>
       <c r="E5" s="11" t="s">
         <v>31</v>
       </c>
@@ -7829,15 +7883,15 @@
         <v>0.2</v>
       </c>
       <c r="G5" s="93"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="135"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="145"/>
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="127"/>
-      <c r="B6" s="130"/>
-      <c r="C6" s="132"/>
-      <c r="D6" s="107"/>
+      <c r="A6" s="111"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="126"/>
       <c r="E6" s="11" t="s">
         <v>106</v>
       </c>
@@ -7845,16 +7899,16 @@
         <v>0.2</v>
       </c>
       <c r="G6" s="93"/>
-      <c r="H6" s="119"/>
-      <c r="I6" s="135"/>
+      <c r="H6" s="128"/>
+      <c r="I6" s="145"/>
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="127"/>
+      <c r="A7" s="111"/>
       <c r="B7" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="132"/>
+      <c r="C7" s="116"/>
       <c r="D7" s="3">
         <v>2</v>
       </c>
@@ -7869,14 +7923,14 @@
         <f t="shared" ref="H7:H16" si="0">G7*F7</f>
         <v>0</v>
       </c>
-      <c r="I7" s="135"/>
+      <c r="I7" s="145"/>
     </row>
     <row r="8" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="128"/>
+      <c r="A8" s="112"/>
       <c r="B8" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="132"/>
+      <c r="C8" s="116"/>
       <c r="D8" s="3">
         <v>2</v>
       </c>
@@ -7891,16 +7945,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="135"/>
+      <c r="I8" s="145"/>
     </row>
     <row r="9" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="120" t="s">
+      <c r="A9" s="119" t="s">
         <v>142</v>
       </c>
       <c r="B9" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="156">
+      <c r="C9" s="142">
         <v>6</v>
       </c>
       <c r="D9" s="19">
@@ -7923,11 +7977,11 @@
       </c>
     </row>
     <row r="10" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="201"/>
+      <c r="A10" s="120"/>
       <c r="B10" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="C10" s="157"/>
+      <c r="C10" s="123"/>
       <c r="D10" s="21">
         <v>3</v>
       </c>
@@ -7942,17 +7996,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="136"/>
+      <c r="I10" s="135"/>
       <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="138" t="s">
+      <c r="A11" s="160" t="s">
         <v>78</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="C11" s="156">
+      <c r="C11" s="142">
         <v>4</v>
       </c>
       <c r="D11" s="19">
@@ -7976,11 +8030,11 @@
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="139"/>
+      <c r="A12" s="161"/>
       <c r="B12" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="117"/>
+      <c r="C12" s="122"/>
       <c r="D12" s="20">
         <v>2</v>
       </c>
@@ -7995,17 +8049,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="135"/>
+      <c r="I12" s="145"/>
       <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="148" t="s">
+      <c r="A13" s="182" t="s">
         <v>79</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="156">
+      <c r="C13" s="142">
         <v>8</v>
       </c>
       <c r="D13" s="19">
@@ -8029,11 +8083,11 @@
       <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="149"/>
+      <c r="A14" s="183"/>
       <c r="B14" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="117"/>
+      <c r="C14" s="122"/>
       <c r="D14" s="20">
         <v>2</v>
       </c>
@@ -8048,15 +8102,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="135"/>
+      <c r="I14" s="145"/>
       <c r="K14" s="3"/>
     </row>
     <row r="15" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="150"/>
+      <c r="A15" s="184"/>
       <c r="B15" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="157"/>
+      <c r="C15" s="123"/>
       <c r="D15" s="22">
         <v>3</v>
       </c>
@@ -8071,7 +8125,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="136"/>
+      <c r="I15" s="135"/>
       <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -8105,26 +8159,26 @@
       <c r="K16" s="3"/>
     </row>
     <row r="17" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="219" t="s">
+      <c r="A17" s="218" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="220"/>
-      <c r="C17" s="221">
+      <c r="B17" s="219"/>
+      <c r="C17" s="220">
         <f>SUM(C2:C16)</f>
         <v>30</v>
       </c>
-      <c r="D17" s="222"/>
-      <c r="E17" s="123">
+      <c r="D17" s="221"/>
+      <c r="E17" s="150">
         <f>(I2*C2+I9*C9+I11*C11+I13*C13+I16*C16)/C17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="124"/>
-      <c r="G17" s="124"/>
-      <c r="H17" s="143" t="str">
+      <c r="F17" s="151"/>
+      <c r="G17" s="151"/>
+      <c r="H17" s="158" t="str">
         <f>IF(OR(I2&lt;10,I9&lt;10,I11&lt;10,I13&lt;10,I16&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I17" s="144"/>
+      <c r="I17" s="159"/>
       <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -8141,19 +8195,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="I13:I15"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C9:C10"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:I1"/>
@@ -8163,6 +8204,19 @@
     <mergeCell ref="D2:D6"/>
     <mergeCell ref="H2:H6"/>
     <mergeCell ref="I2:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="H17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="H17">
     <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
@@ -8210,28 +8264,28 @@
       <c r="B1" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="223" t="s">
+      <c r="C1" s="230" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="224"/>
-      <c r="E1" s="202" t="s">
+      <c r="D1" s="231"/>
+      <c r="E1" s="193" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="218"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="218" t="s">
+      <c r="F1" s="224"/>
+      <c r="G1" s="194"/>
+      <c r="H1" s="224" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="203"/>
+      <c r="I1" s="194"/>
     </row>
     <row r="2" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="110" t="s">
         <v>81</v>
       </c>
       <c r="B2" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="131">
+      <c r="C2" s="115">
         <v>4</v>
       </c>
       <c r="D2" s="14">
@@ -8255,11 +8309,11 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="128"/>
+      <c r="A3" s="112"/>
       <c r="B3" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="133"/>
+      <c r="C3" s="117"/>
       <c r="D3" s="22">
         <v>2</v>
       </c>
@@ -8274,16 +8328,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I3" s="136"/>
+      <c r="I3" s="135"/>
     </row>
     <row r="4" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="160" t="s">
         <v>78</v>
       </c>
       <c r="B4" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="131">
+      <c r="C4" s="115">
         <v>5</v>
       </c>
       <c r="D4" s="14">
@@ -8307,11 +8361,11 @@
       <c r="K4" s="3"/>
     </row>
     <row r="5" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="139"/>
+      <c r="A5" s="161"/>
       <c r="B5" s="65" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="132"/>
+      <c r="C5" s="116"/>
       <c r="D5" s="3">
         <v>1</v>
       </c>
@@ -8326,15 +8380,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="135"/>
+      <c r="I5" s="145"/>
       <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="139"/>
+      <c r="A6" s="161"/>
       <c r="B6" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="132"/>
+      <c r="C6" s="116"/>
       <c r="D6" s="3">
         <v>1</v>
       </c>
@@ -8349,15 +8403,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="135"/>
+      <c r="I6" s="145"/>
       <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="174"/>
+      <c r="A7" s="162"/>
       <c r="B7" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="133"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="22">
         <v>1</v>
       </c>
@@ -8372,17 +8426,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="136"/>
+      <c r="I7" s="135"/>
       <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="225" t="s">
+      <c r="A8" s="228" t="s">
         <v>145</v>
       </c>
       <c r="B8" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="131">
+      <c r="C8" s="115">
         <v>3</v>
       </c>
       <c r="D8" s="14">
@@ -8406,11 +8460,11 @@
       <c r="K8" s="3"/>
     </row>
     <row r="9" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="226"/>
+      <c r="A9" s="229"/>
       <c r="B9" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="133"/>
+      <c r="C9" s="117"/>
       <c r="D9" s="22">
         <v>2</v>
       </c>
@@ -8425,17 +8479,17 @@
         <f>F9*G9</f>
         <v>0</v>
       </c>
-      <c r="I9" s="136"/>
+      <c r="I9" s="135"/>
       <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="148" t="s">
+      <c r="A10" s="182" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="131">
+      <c r="C10" s="115">
         <v>8</v>
       </c>
       <c r="D10" s="14">
@@ -8459,11 +8513,11 @@
       <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="149"/>
+      <c r="A11" s="183"/>
       <c r="B11" s="70" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="132"/>
+      <c r="C11" s="116"/>
       <c r="D11" s="3">
         <v>1</v>
       </c>
@@ -8478,15 +8532,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I11" s="135"/>
+      <c r="I11" s="145"/>
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="149"/>
+      <c r="A12" s="183"/>
       <c r="B12" s="70" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="132"/>
+      <c r="C12" s="116"/>
       <c r="D12" s="3">
         <v>1</v>
       </c>
@@ -8501,15 +8555,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I12" s="135"/>
+      <c r="I12" s="145"/>
       <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="150"/>
+      <c r="A13" s="184"/>
       <c r="B13" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="133"/>
+      <c r="C13" s="117"/>
       <c r="D13" s="22">
         <v>3</v>
       </c>
@@ -8524,7 +8578,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I13" s="136"/>
+      <c r="I13" s="135"/>
       <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -8588,26 +8642,26 @@
       <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="227" t="s">
+      <c r="A16" s="225" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="228"/>
-      <c r="C16" s="227">
+      <c r="B16" s="226"/>
+      <c r="C16" s="225">
         <f>SUM(C2:C15)</f>
         <v>30</v>
       </c>
-      <c r="D16" s="229"/>
-      <c r="E16" s="123">
+      <c r="D16" s="227"/>
+      <c r="E16" s="150">
         <f>(I2*C2+I4*C4+I8*C8+I10*C10+I14*C14+I15*C15)/C16</f>
         <v>0</v>
       </c>
-      <c r="F16" s="124"/>
-      <c r="G16" s="124"/>
-      <c r="H16" s="143" t="str">
+      <c r="F16" s="151"/>
+      <c r="G16" s="151"/>
+      <c r="H16" s="158" t="str">
         <f>IF(OR(I2&lt;10,I4&lt;10,I8&lt;10,I10&lt;10,I14&lt;10,I15&lt;10),"Valide pas","Valide")</f>
         <v>Valide pas</v>
       </c>
-      <c r="I16" s="144"/>
+      <c r="I16" s="159"/>
       <c r="K16" s="3"/>
     </row>
     <row r="17" spans="1:11" s="7" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -8624,6 +8678,18 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="I4:I7"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="A10:A13"/>
@@ -8631,18 +8697,6 @@
     <mergeCell ref="I10:I13"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="H16:I16"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="I4:I7"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="I2:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="H16">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
